--- a/DocsOriginales/BitacoraMQuiazua_template.xlsx
+++ b/DocsOriginales/BitacoraMQuiazua_template.xlsx
@@ -237,7 +237,6 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color indexed="64"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">Proyecto Productivo:</t>
@@ -245,7 +244,6 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color indexed="64"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">Proyecto Productivo, Sena - Empresa, Sena Proveedor Sena, Producción de Centros,Proyecto productivo bajo enfoque empresarial o de investigación, desarrollo e innovación I+D+i y Proyectos Ruta Emprendedora SENA, Proyecto productivo prácticas en la economia popular y/o campesina, Proyecto productivo  a través de convocatorias SENNOVA.
@@ -255,7 +253,6 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color indexed="64"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">Contrato vínculo formativo</t>
@@ -263,7 +260,6 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color indexed="64"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">: Apoyo a una unidad productiva familiar, De apoyo a una institución estatal nacional, territorial, o a una ONG, o a una entidad sin ánimo de lucro, Asesoría a pymes,Vinculo formativo  prácticas en la economia popular y/o campesina )- Resolución 623 de 2020, emanada por el Mintrabajo, pasantía se denomina Vínculo Formativo.
@@ -273,7 +269,6 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color indexed="64"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">*Vínculo laboral o contractual: </t>
@@ -281,7 +276,6 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color indexed="64"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">Vínculo laboral (regular) o Vínculo laboral por medio de prácticas en la economia popular y/o campesina
@@ -291,7 +285,6 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color indexed="64"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">Contrato de aprendizaje: </t>
@@ -299,7 +292,6 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color indexed="64"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">Contrato de aprendizaje (regular),contrato de aprendizaje a través de convocatorias SENNOVA ,contrato de aprendizaje por medio de prácticas en la economia popular y/o campesina 
@@ -309,7 +301,6 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color indexed="64"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>Monitoría:</t>
@@ -317,7 +308,6 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color indexed="64"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> Monitoría (regular), Monitoría a través de convocatorias SENNOVA, otra
@@ -681,7 +671,6 @@
         <b/>
         <i/>
         <sz val="11"/>
-        <color indexed="64"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">Persona con rol de aprendiz: </t>
@@ -690,7 +679,6 @@
       <rPr>
         <i/>
         <sz val="11"/>
-        <color indexed="64"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">recuerde diligenciar completamente el formato bitácora y entregarlo o subirlo al espacio asignado para este</t>
@@ -704,7 +692,6 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color indexed="64"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>Nota:</t>
@@ -712,7 +699,6 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color indexed="64"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> Los datos proporcionados serán tratados de acuerdo con la Política de Tratamiento de Datos Personales del SENA y a la Ley 1581 de 2012</t>
@@ -820,7 +806,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="37">
+  <fonts count="33">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -878,12 +864,6 @@
     </font>
     <font>
       <sz val="11.000000"/>
-      <color indexed="64"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11.000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -895,12 +875,6 @@
     </font>
     <font>
       <sz val="12.000000"/>
-      <color indexed="64"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11.000000"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -923,7 +897,6 @@
     <font>
       <b/>
       <sz val="11.000000"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -953,11 +926,6 @@
     </font>
     <font>
       <sz val="10.000000"/>
-      <color indexed="64"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10.000000"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -970,13 +938,6 @@
       <b/>
       <i/>
       <sz val="11.000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11.000000"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1063,7 +1024,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="65"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -1077,7 +1037,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="89">
+  <borders count="65">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -1256,15 +1216,240 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
       <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
         <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="none"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -1274,467 +1459,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="none"/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="none"/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
@@ -1772,19 +1496,6 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
@@ -1797,21 +1508,6 @@
         <color auto="1"/>
       </top>
       <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -1876,21 +1572,6 @@
       <diagonal style="none"/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -2061,47 +1742,6 @@
       <right style="none"/>
       <top style="none"/>
       <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="none"/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal style="none"/>
     </border>
     <border>
@@ -2184,7 +1824,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="286">
+  <cellXfs count="277">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="3" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2263,25 +1903,25 @@
     <xf fontId="7" fillId="0" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="8" fillId="4" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="8" fillId="4" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="8" fillId="4" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="8" fillId="4" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="8" fillId="4" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="8" fillId="4" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="9" fillId="0" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="9" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="9" fillId="0" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="9" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
@@ -2292,16 +1932,7 @@
     </xf>
     <xf fontId="2" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="2" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="2" fillId="4" borderId="21" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf fontId="10" fillId="0" borderId="22" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf fontId="10" fillId="0" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf fontId="10" fillId="0" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
+    <xf fontId="2" fillId="4" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="10" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
@@ -2320,38 +1951,62 @@
     <xf fontId="10" fillId="0" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="11" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="4" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="8" fillId="4" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="8" fillId="4" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="8" fillId="4" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="11" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="12" fillId="5" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="12" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="12" fillId="5" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf fontId="11" fillId="0" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf fontId="11" fillId="0" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="25" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="26" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="27" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="8" fillId="4" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="8" fillId="4" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="8" fillId="4" borderId="28" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="8" fillId="4" borderId="27" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="12" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf fontId="4" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="2" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -2359,46 +2014,13 @@
     <xf fontId="2" fillId="0" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="28" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="2" fillId="0" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="27" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="13" fillId="5" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="13" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="13" fillId="5" borderId="12" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf fontId="14" fillId="0" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="30" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="31" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="32" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="33" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="15" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="13" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="15" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="13" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2406,7 +2028,7 @@
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="16" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="14" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf fontId="9" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2415,7 +2037,7 @@
     <xf fontId="9" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="34" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="21" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="9" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2424,376 +2046,373 @@
     <xf fontId="9" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="35" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="22" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="7" fillId="0" borderId="36" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="7" fillId="0" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="7" fillId="0" borderId="37" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="7" fillId="0" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="7" fillId="0" borderId="38" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="7" fillId="0" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="7" fillId="0" borderId="39" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="7" fillId="0" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="17" fillId="0" borderId="40" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="18" fillId="5" borderId="41" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="15" fillId="0" borderId="25" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="16" fillId="5" borderId="26" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf fontId="9" fillId="0" borderId="40" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="42" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="9" fillId="0" borderId="25" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="27" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="9" fillId="0" borderId="43" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="9" fillId="0" borderId="21" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="36" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="44" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="2" fillId="0" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="37" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="44" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="32" numFmtId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="19" numFmtId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="45" numFmtId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="1" fillId="0" borderId="28" numFmtId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="9" fillId="0" borderId="46" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="47" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="48" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="49" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="50" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="51" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="9" fillId="0" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="30" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="31" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="32" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="33" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="39" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="9" fillId="0" borderId="52" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="53" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="54" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="55" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="56" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="16" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="37" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="38" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="19" fillId="0" borderId="38" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="9" fillId="0" borderId="34" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="35" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="36" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="37" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="14" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="17" fillId="0" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="19" fillId="0" borderId="39" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="54" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="17" fillId="0" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="31" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="37" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="38" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="20" fillId="0" borderId="38" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="8" fillId="4" borderId="46" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="18" fillId="0" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="4" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="8" fillId="4" borderId="47" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="8" fillId="4" borderId="30" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="8" fillId="4" borderId="49" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="8" fillId="4" borderId="32" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="9" fillId="2" borderId="57" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="50" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="9" fillId="2" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="33" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="9" fillId="2" borderId="44" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="8" fillId="6" borderId="36" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="8" fillId="6" borderId="58" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="9" fillId="2" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="6" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="6" borderId="38" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="8" fillId="6" borderId="58" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="8" fillId="6" borderId="59" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="8" fillId="6" borderId="38" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="6" borderId="39" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="8" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="21" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="19" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="8" fillId="4" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf fontId="8" fillId="4" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="8" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="7" borderId="40" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="35" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="7" borderId="40" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="7" borderId="41" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="42" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="7" borderId="41" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="42" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="7" borderId="41" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="7" borderId="41" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="42" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="7" borderId="41" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="7" borderId="41" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="28" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="2" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="7" borderId="40" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="2" borderId="35" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="7" borderId="43" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="2" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="7" borderId="41" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="2" borderId="42" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="31" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="7" borderId="43" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="2" borderId="44" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="45" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="2" borderId="24" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="7" borderId="43" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="4" borderId="34" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="4" borderId="27" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf fontId="8" fillId="4" borderId="21" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="8" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="8" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="20" fillId="4" borderId="46" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf fontId="20" fillId="4" borderId="47" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="4" borderId="48" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="4" borderId="48" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="7" borderId="60" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf fontId="8" fillId="4" borderId="49" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="50" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="51" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="52" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="4" fillId="0" borderId="53" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="7" borderId="60" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="7" borderId="61" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="62" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="7" borderId="61" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="62" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="7" borderId="61" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="7" borderId="61" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="62" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="7" borderId="61" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="7" borderId="61" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="37" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="63" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="2" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="7" borderId="60" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="2" borderId="53" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="7" borderId="64" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="2" borderId="38" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="7" borderId="61" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="2" borderId="62" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf fontId="4" fillId="0" borderId="44" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="4" fillId="0" borderId="54" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="7" borderId="64" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="37" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="2" borderId="65" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="66" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="2" borderId="37" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="7" borderId="64" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="8" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf fontId="8" fillId="4" borderId="52" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf fontId="8" fillId="4" borderId="42" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="8" fillId="4" borderId="34" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="22" fillId="4" borderId="67" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf fontId="22" fillId="4" borderId="68" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="8" fillId="4" borderId="69" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="8" fillId="4" borderId="69" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="8" fillId="4" borderId="70" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="71" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="72" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="73" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="74" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="65" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="75" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="66" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="45" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="4" fillId="0" borderId="9" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="76" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="77" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="35" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="67" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="68" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="69" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="70" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="78" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="8" fillId="6" borderId="46" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="8" fillId="6" borderId="47" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="55" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="56" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="22" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="46" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="47" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="48" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="49" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="57" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="6" borderId="29" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="6" borderId="30" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf fontId="8" fillId="6" borderId="47" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="8" fillId="6" borderId="49" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="8" fillId="6" borderId="30" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="8" fillId="6" borderId="32" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="8" fillId="4" borderId="6" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2802,229 +2421,223 @@
     <xf fontId="8" fillId="4" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="8" fillId="4" borderId="8" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="21" fillId="0" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="21" fillId="0" borderId="56" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="21" fillId="0" borderId="22" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="21" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="21" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="21" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="26" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="31" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="27" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="22" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="22" fillId="0" borderId="37" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="22" fillId="0" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="22" fillId="0" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="22" fillId="0" borderId="48" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="22" fillId="0" borderId="58" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="59" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="23" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="23" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="23" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="58" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="58" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="24" fillId="0" borderId="58" numFmtId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="58" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="9" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="8" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="23" fillId="0" borderId="79" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="24" fillId="0" borderId="77" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="24" fillId="0" borderId="35" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="24" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="23" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="24" fillId="0" borderId="21" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="80" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="8" fillId="6" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="8" fillId="6" borderId="37" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="19" fillId="4" borderId="53" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="19" fillId="4" borderId="60" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="19" fillId="4" borderId="61" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="23" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="25" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="26" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="81" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="42" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="25" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="25" fillId="0" borderId="56" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="25" fillId="0" borderId="30" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="25" fillId="0" borderId="32" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="25" fillId="0" borderId="69" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="25" fillId="0" borderId="82" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="83" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="26" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="27" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf fontId="26" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="82" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="27" fillId="0" borderId="62" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="27" fillId="0" borderId="38" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="27" fillId="0" borderId="39" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="62" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="38" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="39" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="28" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="27" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="26" fillId="0" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="26" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="26" fillId="0" borderId="42" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="27" fillId="0" borderId="60" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="28" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="28" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="9" fillId="0" borderId="82" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="28" fillId="0" borderId="82" numFmtId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="82" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="14" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="8" fillId="6" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="8" fillId="6" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="8" fillId="6" borderId="56" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="21" fillId="4" borderId="74" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="21" fillId="4" borderId="84" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="21" fillId="4" borderId="85" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="36" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf fontId="27" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="27" fillId="0" borderId="60" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf fontId="29" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf fontId="26" fillId="0" borderId="63" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="26" fillId="0" borderId="55" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="26" fillId="0" borderId="63" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="26" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="26" fillId="0" borderId="55" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="26" fillId="0" borderId="64" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="26" fillId="0" borderId="60" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="26" fillId="0" borderId="44" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="26" fillId="0" borderId="64" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="26" fillId="0" borderId="60" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="26" fillId="0" borderId="44" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf fontId="30" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="30" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="30" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="31" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf fontId="32" fillId="0" borderId="60" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="30" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="31" fillId="0" borderId="86" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="31" fillId="0" borderId="58" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="31" fillId="0" borderId="59" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="86" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="58" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="59" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="32" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="31" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf fontId="30" fillId="0" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="30" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="30" fillId="0" borderId="62" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="31" fillId="0" borderId="84" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf fontId="32" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="32" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="31" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="31" fillId="0" borderId="84" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="33" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="30" fillId="0" borderId="87" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="30" fillId="0" borderId="76" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="30" fillId="0" borderId="87" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="30" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="30" fillId="0" borderId="76" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="30" fillId="0" borderId="88" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="30" fillId="0" borderId="84" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="30" fillId="0" borderId="65" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="30" fillId="0" borderId="88" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="30" fillId="0" borderId="84" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="30" fillId="0" borderId="65" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf fontId="34" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf fontId="34" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf fontId="34" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf fontId="35" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf fontId="36" fillId="0" borderId="84" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="36" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="32" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3349,15 +2962,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>301626</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>17937</xdr:rowOff>
+      <xdr:colOff>301625</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>189387</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1782763</xdr:colOff>
+      <xdr:colOff>1782762</xdr:colOff>
       <xdr:row>67</xdr:row>
-      <xdr:rowOff>140441</xdr:rowOff>
+      <xdr:rowOff>92815</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3372,8 +2985,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2746376" y="19433062"/>
-          <a:ext cx="1484312" cy="881328"/>
+          <a:off x="2635250" y="19448937"/>
+          <a:ext cx="1481136" cy="884503"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3385,11 +2998,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1104900</xdr:colOff>
+      <xdr:colOff>1104899</xdr:colOff>
       <xdr:row>67</xdr:row>
       <xdr:rowOff>19049</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1831108" cy="990599"/>
+    <xdr:ext cx="1831107" cy="990599"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1197666786" name=""/>
@@ -4118,52 +3731,52 @@
       <c r="E14" s="42"/>
     </row>
     <row r="15" ht="21.75" customHeight="1">
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="45"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="42"/>
     </row>
     <row r="16" ht="21.75" customHeight="1">
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="45"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="42"/>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="48"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="45"/>
     </row>
     <row r="18" ht="21.75" customHeight="1">
-      <c r="B18" s="43" t="s">
+      <c r="B18" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="44"/>
-      <c r="D18" s="44"/>
-      <c r="E18" s="45"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="42"/>
     </row>
     <row r="19" ht="21.75" customHeight="1">
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="45"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="42"/>
     </row>
     <row r="20" ht="21.75" customHeight="1">
-      <c r="B20" s="49" t="s">
+      <c r="B20" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="51"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="42"/>
     </row>
     <row r="21" ht="27" customHeight="1">
       <c r="B21" s="31" t="s">
@@ -4184,401 +3797,401 @@
       <c r="E22" s="30"/>
     </row>
     <row r="23" ht="5.25" customHeight="1">
-      <c r="B23" s="52"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="54"/>
+      <c r="B23" s="46"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="48"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="B24" s="55" t="s">
+      <c r="B24" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="56" t="s">
+      <c r="C24" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="57" t="s">
+      <c r="D24" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="58"/>
-      <c r="F24" s="59"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="53"/>
     </row>
     <row r="25">
-      <c r="B25" s="60" t="s">
+      <c r="B25" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="61" t="s">
+      <c r="C25" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="62"/>
-      <c r="E25" s="63"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="57"/>
     </row>
     <row r="26" ht="31">
-      <c r="B26" s="64" t="s">
+      <c r="B26" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="65" t="s">
+      <c r="C26" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="62"/>
-      <c r="E26" s="63"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="57"/>
     </row>
     <row r="27" ht="43.5">
-      <c r="B27" s="66" t="s">
+      <c r="B27" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="61" t="s">
+      <c r="C27" s="55" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="62"/>
-      <c r="E27" s="63"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="57"/>
     </row>
     <row r="28" ht="21" customHeight="1">
-      <c r="B28" s="60" t="s">
+      <c r="B28" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="61" t="s">
+      <c r="C28" s="55" t="s">
         <v>33</v>
       </c>
-      <c r="D28" s="62"/>
-      <c r="E28" s="63"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="57"/>
     </row>
     <row r="29" ht="44.25" customHeight="1">
-      <c r="B29" s="60" t="s">
+      <c r="B29" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="61" t="s">
+      <c r="C29" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="D29" s="62" t="s">
+      <c r="D29" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="E29" s="63" t="s">
+      <c r="E29" s="57" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="30" ht="36.75" customHeight="1">
-      <c r="B30" s="60" t="s">
+      <c r="B30" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="61" t="s">
+      <c r="C30" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="D30" s="62" t="s">
+      <c r="D30" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="E30" s="63" t="s">
+      <c r="E30" s="57" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="31" ht="29">
-      <c r="B31" s="60" t="s">
+      <c r="B31" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="C31" s="61" t="s">
+      <c r="C31" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="62"/>
-      <c r="E31" s="63"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="57"/>
     </row>
     <row r="32" ht="65.25" customHeight="1">
-      <c r="B32" s="60" t="s">
+      <c r="B32" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="C32" s="61" t="s">
+      <c r="C32" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="62" t="s">
+      <c r="D32" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E32" s="63" t="s">
+      <c r="E32" s="57" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="33" ht="72.5">
-      <c r="B33" s="60" t="s">
+      <c r="B33" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="61" t="s">
+      <c r="C33" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="D33" s="62"/>
-      <c r="E33" s="63"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="57"/>
     </row>
     <row r="34" ht="43.5">
-      <c r="B34" s="60" t="s">
+      <c r="B34" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="C34" s="61" t="s">
+      <c r="C34" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="62"/>
-      <c r="E34" s="63"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="57"/>
     </row>
     <row r="35" ht="58">
-      <c r="B35" s="60" t="s">
+      <c r="B35" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="C35" s="61" t="s">
+      <c r="C35" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="62"/>
-      <c r="E35" s="63"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="57"/>
     </row>
     <row r="36" ht="43.5">
-      <c r="B36" s="60" t="s">
+      <c r="B36" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="61" t="s">
+      <c r="C36" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="D36" s="62"/>
-      <c r="E36" s="63"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="57"/>
     </row>
     <row r="37" ht="43.5">
-      <c r="B37" s="60" t="s">
+      <c r="B37" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="C37" s="61" t="s">
+      <c r="C37" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="D37" s="62"/>
-      <c r="E37" s="63"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="57"/>
     </row>
     <row r="38" ht="43.5">
-      <c r="B38" s="60" t="s">
+      <c r="B38" s="54" t="s">
         <v>55</v>
       </c>
-      <c r="C38" s="61" t="s">
+      <c r="C38" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="D38" s="62"/>
-      <c r="E38" s="63"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="57"/>
     </row>
     <row r="39" ht="43.5">
-      <c r="B39" s="60" t="s">
+      <c r="B39" s="54" t="s">
         <v>32</v>
       </c>
-      <c r="C39" s="61" t="s">
+      <c r="C39" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="D39" s="62"/>
-      <c r="E39" s="63"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="57"/>
     </row>
     <row r="40" ht="58">
-      <c r="B40" s="60" t="s">
+      <c r="B40" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="61" t="s">
+      <c r="C40" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="D40" s="62"/>
-      <c r="E40" s="63"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="57"/>
     </row>
     <row r="41" ht="43.5">
-      <c r="B41" s="60" t="s">
+      <c r="B41" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="C41" s="61" t="s">
+      <c r="C41" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="D41" s="62"/>
-      <c r="E41" s="63"/>
+      <c r="D41" s="56"/>
+      <c r="E41" s="57"/>
     </row>
     <row r="42" ht="43.5">
-      <c r="B42" s="60" t="s">
+      <c r="B42" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="C42" s="61" t="s">
+      <c r="C42" s="55" t="s">
         <v>62</v>
       </c>
-      <c r="D42" s="62"/>
-      <c r="E42" s="63"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="57"/>
     </row>
     <row r="43" ht="409.5">
-      <c r="B43" s="60" t="s">
+      <c r="B43" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="C43" s="67" t="s">
+      <c r="C43" s="61" t="s">
         <v>64</v>
       </c>
-      <c r="D43" s="62" t="s">
+      <c r="D43" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="E43" s="63" t="s">
+      <c r="E43" s="57" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="44" ht="29">
-      <c r="B44" s="60" t="s">
+      <c r="B44" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="C44" s="61" t="s">
+      <c r="C44" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="D44" s="62"/>
-      <c r="E44" s="63"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="57"/>
     </row>
     <row r="45" ht="29">
-      <c r="B45" s="60" t="s">
+      <c r="B45" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="C45" s="61" t="s">
+      <c r="C45" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="D45" s="62"/>
-      <c r="E45" s="63"/>
+      <c r="D45" s="56"/>
+      <c r="E45" s="57"/>
     </row>
     <row r="46" ht="29">
-      <c r="B46" s="60" t="s">
+      <c r="B46" s="54" t="s">
         <v>70</v>
       </c>
-      <c r="C46" s="61" t="s">
+      <c r="C46" s="55" t="s">
         <v>71</v>
       </c>
-      <c r="D46" s="62"/>
-      <c r="E46" s="63"/>
+      <c r="D46" s="56"/>
+      <c r="E46" s="57"/>
     </row>
     <row r="47" ht="127.5" customHeight="1">
-      <c r="B47" s="60" t="s">
+      <c r="B47" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="C47" s="61" t="s">
+      <c r="C47" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="D47" s="62" t="s">
+      <c r="D47" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="E47" s="63" t="s">
+      <c r="E47" s="57" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="48" ht="43.5">
-      <c r="B48" s="60" t="s">
+      <c r="B48" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="C48" s="61" t="s">
+      <c r="C48" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="D48" s="62"/>
-      <c r="E48" s="63"/>
+      <c r="D48" s="56"/>
+      <c r="E48" s="57"/>
     </row>
     <row r="49" ht="146.25" customHeight="1">
-      <c r="B49" s="60" t="s">
+      <c r="B49" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="C49" s="61" t="s">
+      <c r="C49" s="55" t="s">
         <v>78</v>
       </c>
-      <c r="D49" s="62" t="s">
+      <c r="D49" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="E49" s="63" t="s">
+      <c r="E49" s="57" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="50" ht="339.75" customHeight="1">
-      <c r="B50" s="60" t="s">
+      <c r="B50" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="C50" s="68" t="s">
+      <c r="C50" s="62" t="s">
         <v>81</v>
       </c>
-      <c r="D50" s="62" t="s">
+      <c r="D50" s="56" t="s">
         <v>82</v>
       </c>
-      <c r="E50" s="63" t="s">
+      <c r="E50" s="57" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="51" ht="84.75" customHeight="1">
-      <c r="B51" s="60" t="s">
+      <c r="B51" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="C51" s="68" t="s">
+      <c r="C51" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="D51" s="62" t="s">
+      <c r="D51" s="56" t="s">
         <v>86</v>
       </c>
-      <c r="E51" s="63" t="s">
+      <c r="E51" s="57" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="52" ht="72.5">
-      <c r="B52" s="60" t="s">
+      <c r="B52" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="C52" s="61" t="s">
+      <c r="C52" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="D52" s="62"/>
-      <c r="E52" s="63"/>
+      <c r="D52" s="56"/>
+      <c r="E52" s="57"/>
     </row>
     <row r="53" ht="72.5">
-      <c r="B53" s="60" t="s">
+      <c r="B53" s="54" t="s">
         <v>89</v>
       </c>
-      <c r="C53" s="68" t="s">
+      <c r="C53" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="D53" s="62"/>
-      <c r="E53" s="63"/>
+      <c r="D53" s="56"/>
+      <c r="E53" s="57"/>
     </row>
     <row r="54" ht="43.5">
-      <c r="B54" s="60" t="s">
+      <c r="B54" s="54" t="s">
         <v>91</v>
       </c>
-      <c r="C54" s="68" t="s">
+      <c r="C54" s="62" t="s">
         <v>92</v>
       </c>
-      <c r="D54" s="62"/>
-      <c r="E54" s="63"/>
+      <c r="D54" s="56"/>
+      <c r="E54" s="57"/>
     </row>
     <row r="55" ht="72.5">
-      <c r="B55" s="60" t="s">
+      <c r="B55" s="54" t="s">
         <v>93</v>
       </c>
-      <c r="C55" s="61" t="s">
+      <c r="C55" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="D55" s="62"/>
-      <c r="E55" s="63"/>
+      <c r="D55" s="56"/>
+      <c r="E55" s="57"/>
     </row>
     <row r="56" ht="72.5">
-      <c r="B56" s="69" t="s">
+      <c r="B56" s="63" t="s">
         <v>95</v>
       </c>
-      <c r="C56" s="61" t="s">
+      <c r="C56" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="D56" s="62"/>
-      <c r="E56" s="63"/>
+      <c r="D56" s="56"/>
+      <c r="E56" s="57"/>
     </row>
     <row r="57" ht="37.5" customHeight="1">
-      <c r="B57" s="70" t="s">
+      <c r="B57" s="64" t="s">
         <v>96</v>
       </c>
-      <c r="C57" s="71" t="s">
+      <c r="C57" s="65" t="s">
         <v>97</v>
       </c>
-      <c r="D57" s="72" t="s">
+      <c r="D57" s="66" t="s">
         <v>98</v>
       </c>
-      <c r="E57" s="73" t="s">
+      <c r="E57" s="67" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="74"/>
-      <c r="C58" s="74"/>
-      <c r="D58" s="75"/>
-      <c r="E58" s="75"/>
+      <c r="B58" s="68"/>
+      <c r="C58" s="68"/>
+      <c r="D58" s="69"/>
+      <c r="E58" s="69"/>
     </row>
     <row r="59">
-      <c r="B59" s="76"/>
-      <c r="C59" s="76"/>
-      <c r="D59" s="75"/>
-      <c r="E59" s="75"/>
+      <c r="B59" s="70"/>
+      <c r="C59" s="70"/>
+      <c r="D59" s="69"/>
+      <c r="E59" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="54">
@@ -4649,83 +4262,83 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="77" width="2.26953125"/>
-    <col customWidth="1" min="2" max="4" style="78" width="32.7265625"/>
-    <col customWidth="1" min="5" max="5" style="78" width="36.453125"/>
-    <col customWidth="1" min="6" max="7" style="78" width="32.7265625"/>
-    <col customWidth="1" min="8" max="8" style="78" width="8.453125"/>
-    <col customWidth="1" min="9" max="9" style="78" width="6.453125"/>
-    <col customWidth="1" min="10" max="15" style="78" width="5.7265625"/>
-    <col customWidth="1" min="16" max="16" style="78" width="4.7265625"/>
-    <col customWidth="1" min="17" max="17" style="78" width="5.81640625"/>
-    <col customWidth="1" min="18" max="18" style="78" width="7.453125"/>
-    <col customWidth="1" min="19" max="19" style="78" width="7.1796875"/>
-    <col customWidth="1" min="20" max="21" style="78" width="5.7265625"/>
-    <col customWidth="1" min="22" max="22" style="78" width="5"/>
-    <col customWidth="1" min="23" max="23" style="78" width="6.453125"/>
-    <col customWidth="1" min="24" max="24" style="78" width="8.1796875"/>
-    <col customWidth="1" min="25" max="25" style="78" width="5.1796875"/>
-    <col customWidth="1" min="26" max="26" style="79" width="24.453125"/>
-    <col min="27" max="16384" style="77" width="11.453125"/>
+    <col customWidth="1" min="1" max="1" style="71" width="2.26953125"/>
+    <col customWidth="1" min="2" max="4" style="72" width="32.7265625"/>
+    <col customWidth="1" min="5" max="5" style="72" width="36.453125"/>
+    <col customWidth="1" min="6" max="7" style="72" width="32.7265625"/>
+    <col customWidth="1" min="8" max="8" style="72" width="8.453125"/>
+    <col customWidth="1" min="9" max="9" style="72" width="6.453125"/>
+    <col customWidth="1" min="10" max="15" style="72" width="5.7265625"/>
+    <col customWidth="1" min="16" max="16" style="72" width="4.7265625"/>
+    <col customWidth="1" min="17" max="17" style="72" width="5.81640625"/>
+    <col customWidth="1" min="18" max="18" style="72" width="7.453125"/>
+    <col customWidth="1" min="19" max="19" style="72" width="7.1796875"/>
+    <col customWidth="1" min="20" max="21" style="72" width="5.7265625"/>
+    <col customWidth="1" min="22" max="22" style="72" width="5"/>
+    <col customWidth="1" min="23" max="23" style="72" width="6.453125"/>
+    <col customWidth="1" min="24" max="24" style="72" width="8.1796875"/>
+    <col customWidth="1" min="25" max="25" style="72" width="5.1796875"/>
+    <col customWidth="1" min="26" max="26" style="73" width="24.453125"/>
+    <col min="27" max="16384" style="71" width="11.453125"/>
   </cols>
   <sheetData>
     <row r="1" ht="29.25" customHeight="1">
-      <c r="B1" s="80"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="82" t="s">
+      <c r="B1" s="74"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="79"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="77"/>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="77"/>
-      <c r="R1" s="77"/>
-      <c r="S1" s="77"/>
-      <c r="T1" s="77"/>
-      <c r="U1" s="77"/>
-      <c r="V1" s="77"/>
-      <c r="W1" s="77"/>
-      <c r="X1" s="77"/>
-      <c r="Y1" s="77"/>
-      <c r="Z1" s="77"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="71"/>
+      <c r="P1" s="71"/>
+      <c r="Q1" s="71"/>
+      <c r="R1" s="71"/>
+      <c r="S1" s="71"/>
+      <c r="T1" s="71"/>
+      <c r="U1" s="71"/>
+      <c r="V1" s="71"/>
+      <c r="W1" s="71"/>
+      <c r="X1" s="71"/>
+      <c r="Y1" s="71"/>
+      <c r="Z1" s="71"/>
     </row>
     <row r="2" ht="29.25" customHeight="1">
-      <c r="B2" s="83"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="85" t="s">
+      <c r="B2" s="77"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="79"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
-      <c r="W2" s="77"/>
-      <c r="X2" s="77"/>
-      <c r="Y2" s="77"/>
-      <c r="Z2" s="77"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="71"/>
+      <c r="P2" s="71"/>
+      <c r="Q2" s="71"/>
+      <c r="R2" s="71"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="71"/>
+      <c r="U2" s="71"/>
+      <c r="V2" s="71"/>
+      <c r="W2" s="71"/>
+      <c r="X2" s="71"/>
+      <c r="Y2" s="71"/>
+      <c r="Z2" s="71"/>
     </row>
     <row r="3" ht="24" customHeight="1">
       <c r="B3" s="9" t="s">
@@ -4736,25 +4349,25 @@
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
       <c r="G3" s="11"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="77"/>
-      <c r="L3" s="77"/>
-      <c r="M3" s="77"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="77"/>
-      <c r="T3" s="77"/>
-      <c r="U3" s="77"/>
-      <c r="V3" s="77"/>
-      <c r="W3" s="77"/>
-      <c r="X3" s="77"/>
-      <c r="Y3" s="77"/>
-      <c r="Z3" s="77"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
+      <c r="O3" s="71"/>
+      <c r="P3" s="71"/>
+      <c r="Q3" s="71"/>
+      <c r="R3" s="71"/>
+      <c r="S3" s="71"/>
+      <c r="T3" s="71"/>
+      <c r="U3" s="71"/>
+      <c r="V3" s="71"/>
+      <c r="W3" s="71"/>
+      <c r="X3" s="71"/>
+      <c r="Y3" s="71"/>
+      <c r="Z3" s="71"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="B4" s="12" t="s">
@@ -4765,25 +4378,25 @@
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
       <c r="G4" s="14"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
-      <c r="M4" s="77"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="77"/>
-      <c r="P4" s="77"/>
-      <c r="Q4" s="77"/>
-      <c r="R4" s="77"/>
-      <c r="S4" s="77"/>
-      <c r="T4" s="77"/>
-      <c r="U4" s="77"/>
-      <c r="V4" s="77"/>
-      <c r="W4" s="77"/>
-      <c r="X4" s="77"/>
-      <c r="Y4" s="77"/>
-      <c r="Z4" s="77"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="71"/>
+      <c r="K4" s="71"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="71"/>
+      <c r="O4" s="71"/>
+      <c r="P4" s="71"/>
+      <c r="Q4" s="71"/>
+      <c r="R4" s="71"/>
+      <c r="S4" s="71"/>
+      <c r="T4" s="71"/>
+      <c r="U4" s="71"/>
+      <c r="V4" s="71"/>
+      <c r="W4" s="71"/>
+      <c r="X4" s="71"/>
+      <c r="Y4" s="71"/>
+      <c r="Z4" s="71"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="B5" s="9" t="s">
@@ -4794,25 +4407,25 @@
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
       <c r="G5" s="11"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="77"/>
-      <c r="L5" s="77"/>
-      <c r="M5" s="77"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
-      <c r="W5" s="77"/>
-      <c r="X5" s="77"/>
-      <c r="Y5" s="77"/>
-      <c r="Z5" s="77"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
+      <c r="P5" s="71"/>
+      <c r="Q5" s="71"/>
+      <c r="R5" s="71"/>
+      <c r="S5" s="71"/>
+      <c r="T5" s="71"/>
+      <c r="U5" s="71"/>
+      <c r="V5" s="71"/>
+      <c r="W5" s="71"/>
+      <c r="X5" s="71"/>
+      <c r="Y5" s="71"/>
+      <c r="Z5" s="71"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="B6" s="12" t="s">
@@ -4823,25 +4436,25 @@
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
       <c r="G6" s="14"/>
-      <c r="H6" s="79"/>
-      <c r="I6" s="79"/>
-      <c r="J6" s="77"/>
-      <c r="K6" s="77"/>
-      <c r="L6" s="77"/>
-      <c r="M6" s="77"/>
-      <c r="N6" s="77"/>
-      <c r="O6" s="77"/>
-      <c r="P6" s="77"/>
-      <c r="Q6" s="77"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="77"/>
-      <c r="T6" s="77"/>
-      <c r="U6" s="77"/>
-      <c r="V6" s="77"/>
-      <c r="W6" s="77"/>
-      <c r="X6" s="77"/>
-      <c r="Y6" s="77"/>
-      <c r="Z6" s="77"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="71"/>
+      <c r="O6" s="71"/>
+      <c r="P6" s="71"/>
+      <c r="Q6" s="71"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="71"/>
+      <c r="V6" s="71"/>
+      <c r="W6" s="71"/>
+      <c r="X6" s="71"/>
+      <c r="Y6" s="71"/>
+      <c r="Z6" s="71"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="B7" s="9" t="s">
@@ -4852,2017 +4465,2017 @@
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="77"/>
-      <c r="I7" s="77"/>
-      <c r="J7" s="77"/>
-      <c r="K7" s="77"/>
-      <c r="L7" s="77"/>
-      <c r="M7" s="77"/>
-      <c r="N7" s="77"/>
-      <c r="O7" s="77"/>
-      <c r="P7" s="77"/>
-      <c r="Q7" s="77"/>
-      <c r="R7" s="77"/>
-      <c r="S7" s="77"/>
-      <c r="T7" s="77"/>
-      <c r="U7" s="77"/>
-      <c r="V7" s="77"/>
-      <c r="W7" s="77"/>
-      <c r="X7" s="77"/>
-      <c r="Y7" s="77"/>
-      <c r="Z7" s="77"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="71"/>
+      <c r="O7" s="71"/>
+      <c r="P7" s="71"/>
+      <c r="Q7" s="71"/>
+      <c r="R7" s="71"/>
+      <c r="S7" s="71"/>
+      <c r="T7" s="71"/>
+      <c r="U7" s="71"/>
+      <c r="V7" s="71"/>
+      <c r="W7" s="71"/>
+      <c r="X7" s="71"/>
+      <c r="Y7" s="71"/>
+      <c r="Z7" s="71"/>
     </row>
     <row r="8" ht="36.75" customHeight="1">
-      <c r="B8" s="86" t="s">
+      <c r="B8" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="87"/>
-      <c r="D8" s="88" t="s">
+      <c r="C8" s="81"/>
+      <c r="D8" s="82" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="87"/>
-      <c r="F8" s="88" t="s">
+      <c r="E8" s="81"/>
+      <c r="F8" s="82" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="89"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="77"/>
-      <c r="J8" s="77"/>
-      <c r="K8" s="77"/>
-      <c r="L8" s="77"/>
-      <c r="M8" s="77"/>
-      <c r="N8" s="77"/>
-      <c r="O8" s="77"/>
-      <c r="P8" s="77"/>
-      <c r="Q8" s="77"/>
-      <c r="R8" s="77"/>
-      <c r="S8" s="77"/>
-      <c r="T8" s="77"/>
-      <c r="U8" s="77"/>
-      <c r="V8" s="77"/>
-      <c r="W8" s="77"/>
-      <c r="X8" s="77"/>
-      <c r="Y8" s="77"/>
-      <c r="Z8" s="77"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="71"/>
+      <c r="I8" s="71"/>
+      <c r="J8" s="71"/>
+      <c r="K8" s="71"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="71"/>
+      <c r="N8" s="71"/>
+      <c r="O8" s="71"/>
+      <c r="P8" s="71"/>
+      <c r="Q8" s="71"/>
+      <c r="R8" s="71"/>
+      <c r="S8" s="71"/>
+      <c r="T8" s="71"/>
+      <c r="U8" s="71"/>
+      <c r="V8" s="71"/>
+      <c r="W8" s="71"/>
+      <c r="X8" s="71"/>
+      <c r="Y8" s="71"/>
+      <c r="Z8" s="71"/>
     </row>
     <row r="9" ht="9" customHeight="1">
-      <c r="B9" s="84"/>
-      <c r="C9" s="90"/>
-      <c r="D9" s="90"/>
-      <c r="E9" s="90"/>
-      <c r="F9" s="90"/>
-      <c r="G9" s="90"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="77"/>
-      <c r="K9" s="77"/>
-      <c r="L9" s="77"/>
-      <c r="M9" s="77"/>
-      <c r="N9" s="77"/>
-      <c r="O9" s="77"/>
-      <c r="P9" s="77"/>
-      <c r="Q9" s="77"/>
-      <c r="R9" s="77"/>
-      <c r="S9" s="77"/>
-      <c r="T9" s="77"/>
-      <c r="U9" s="77"/>
-      <c r="V9" s="77"/>
-      <c r="W9" s="77"/>
-      <c r="X9" s="77"/>
-      <c r="Y9" s="77"/>
-      <c r="Z9" s="77"/>
-    </row>
-    <row r="10" s="78" customFormat="1" ht="29.25" customHeight="1">
-      <c r="B10" s="80" t="s">
+      <c r="B9" s="78"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="84"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="84"/>
+      <c r="G9" s="84"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="71"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="71"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="71"/>
+      <c r="S9" s="71"/>
+      <c r="T9" s="71"/>
+      <c r="U9" s="71"/>
+      <c r="V9" s="71"/>
+      <c r="W9" s="71"/>
+      <c r="X9" s="71"/>
+      <c r="Y9" s="71"/>
+      <c r="Z9" s="71"/>
+    </row>
+    <row r="10" s="72" customFormat="1" ht="29.25" customHeight="1">
+      <c r="B10" s="74" t="s">
         <v>100</v>
       </c>
-      <c r="C10" s="91" t="s">
+      <c r="C10" s="85" t="s">
         <v>101</v>
       </c>
-      <c r="D10" s="92" t="s">
+      <c r="D10" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="93" t="s">
+      <c r="E10" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="94" t="s">
+      <c r="F10" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="95" t="s">
+      <c r="G10" s="89" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="96" t="s">
+      <c r="B11" s="90" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="97" t="s">
+      <c r="C11" s="91" t="s">
         <v>103</v>
       </c>
-      <c r="D11" s="98">
+      <c r="D11" s="92">
         <v>1000271734</v>
       </c>
-      <c r="E11" s="99">
+      <c r="E11" s="93">
         <v>3144382573</v>
       </c>
-      <c r="F11" s="100" t="s">
+      <c r="F11" s="94" t="s">
         <v>104</v>
       </c>
-      <c r="G11" s="101" t="s">
+      <c r="G11" s="95" t="s">
         <v>105</v>
       </c>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="77"/>
-      <c r="K11" s="77"/>
-      <c r="L11" s="77"/>
-      <c r="M11" s="77"/>
-      <c r="N11" s="77"/>
-      <c r="O11" s="77"/>
-      <c r="P11" s="77"/>
-      <c r="Q11" s="77"/>
-      <c r="R11" s="77"/>
-      <c r="S11" s="77"/>
-      <c r="T11" s="77"/>
-      <c r="U11" s="77"/>
-      <c r="V11" s="77"/>
-      <c r="W11" s="77"/>
-      <c r="X11" s="77"/>
-      <c r="Y11" s="77"/>
-      <c r="Z11" s="77"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="71"/>
+      <c r="L11" s="71"/>
+      <c r="M11" s="71"/>
+      <c r="N11" s="71"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="71"/>
+      <c r="S11" s="71"/>
+      <c r="T11" s="71"/>
+      <c r="U11" s="71"/>
+      <c r="V11" s="71"/>
+      <c r="W11" s="71"/>
+      <c r="X11" s="71"/>
+      <c r="Y11" s="71"/>
+      <c r="Z11" s="71"/>
     </row>
     <row r="12" ht="9" customHeight="1">
-      <c r="B12" s="90"/>
-      <c r="D12" s="90"/>
-      <c r="E12" s="84"/>
-      <c r="F12" s="84"/>
-      <c r="G12" s="90"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="77"/>
-      <c r="K12" s="77"/>
-      <c r="L12" s="77"/>
-      <c r="M12" s="77"/>
-      <c r="N12" s="77"/>
-      <c r="O12" s="77"/>
-      <c r="P12" s="77"/>
-      <c r="Q12" s="77"/>
-      <c r="R12" s="77"/>
-      <c r="S12" s="77"/>
-      <c r="T12" s="77"/>
-      <c r="U12" s="77"/>
-      <c r="V12" s="77"/>
-      <c r="W12" s="77"/>
-      <c r="X12" s="77"/>
-      <c r="Y12" s="77"/>
-      <c r="Z12" s="77"/>
+      <c r="B12" s="84"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="71"/>
+      <c r="K12" s="71"/>
+      <c r="L12" s="71"/>
+      <c r="M12" s="71"/>
+      <c r="N12" s="71"/>
+      <c r="O12" s="71"/>
+      <c r="P12" s="71"/>
+      <c r="Q12" s="71"/>
+      <c r="R12" s="71"/>
+      <c r="S12" s="71"/>
+      <c r="T12" s="71"/>
+      <c r="U12" s="71"/>
+      <c r="V12" s="71"/>
+      <c r="W12" s="71"/>
+      <c r="X12" s="71"/>
+      <c r="Y12" s="71"/>
+      <c r="Z12" s="71"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="B13" s="102" t="s">
+      <c r="B13" s="96" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="103"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="104" t="s">
+      <c r="C13" s="97"/>
+      <c r="D13" s="97"/>
+      <c r="E13" s="98" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="103"/>
-      <c r="G13" s="105"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="84"/>
-      <c r="J13" s="84"/>
-      <c r="L13" s="84"/>
-      <c r="M13" s="84"/>
-      <c r="N13" s="84"/>
-      <c r="O13" s="84"/>
-      <c r="P13" s="84"/>
-      <c r="Q13" s="84"/>
-      <c r="R13" s="84"/>
-      <c r="S13" s="84"/>
-      <c r="T13" s="84"/>
-      <c r="U13" s="84"/>
-      <c r="V13" s="84"/>
-      <c r="W13" s="84"/>
-      <c r="X13" s="84"/>
-      <c r="Y13" s="84"/>
+      <c r="F13" s="97"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="78"/>
+      <c r="I13" s="78"/>
+      <c r="J13" s="78"/>
+      <c r="L13" s="78"/>
+      <c r="M13" s="78"/>
+      <c r="N13" s="78"/>
+      <c r="O13" s="78"/>
+      <c r="P13" s="78"/>
+      <c r="Q13" s="78"/>
+      <c r="R13" s="78"/>
+      <c r="S13" s="78"/>
+      <c r="T13" s="78"/>
+      <c r="U13" s="78"/>
+      <c r="V13" s="78"/>
+      <c r="W13" s="78"/>
+      <c r="X13" s="78"/>
+      <c r="Y13" s="78"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="96">
+      <c r="B14" s="90">
         <v>2996234</v>
       </c>
-      <c r="C14" s="106"/>
-      <c r="D14" s="106"/>
-      <c r="E14" s="107" t="s">
+      <c r="C14" s="100"/>
+      <c r="D14" s="100"/>
+      <c r="E14" s="101" t="s">
         <v>107</v>
       </c>
-      <c r="F14" s="106"/>
-      <c r="G14" s="108"/>
-      <c r="H14" s="90"/>
-      <c r="I14" s="90"/>
-      <c r="J14" s="90"/>
-      <c r="L14" s="90"/>
-      <c r="M14" s="90"/>
-      <c r="N14" s="90"/>
-      <c r="O14" s="90"/>
-      <c r="P14" s="90"/>
-      <c r="Q14" s="90"/>
-      <c r="R14" s="90"/>
-      <c r="S14" s="90"/>
-      <c r="T14" s="90"/>
-      <c r="U14" s="90"/>
-      <c r="V14" s="90"/>
-      <c r="W14" s="90"/>
-      <c r="X14" s="90"/>
-      <c r="Y14" s="90"/>
+      <c r="F14" s="100"/>
+      <c r="G14" s="102"/>
+      <c r="H14" s="84"/>
+      <c r="I14" s="84"/>
+      <c r="J14" s="84"/>
+      <c r="L14" s="84"/>
+      <c r="M14" s="84"/>
+      <c r="N14" s="84"/>
+      <c r="O14" s="84"/>
+      <c r="P14" s="84"/>
+      <c r="Q14" s="84"/>
+      <c r="R14" s="84"/>
+      <c r="S14" s="84"/>
+      <c r="T14" s="84"/>
+      <c r="U14" s="84"/>
+      <c r="V14" s="84"/>
+      <c r="W14" s="84"/>
+      <c r="X14" s="84"/>
+      <c r="Y14" s="84"/>
     </row>
     <row r="15" ht="9.75" customHeight="1">
-      <c r="B15" s="109"/>
-      <c r="C15" s="109"/>
-      <c r="D15" s="109"/>
-      <c r="E15" s="109"/>
-      <c r="F15" s="109"/>
-      <c r="G15" s="109"/>
-      <c r="H15" s="109"/>
-      <c r="I15" s="109"/>
-      <c r="J15" s="109"/>
-      <c r="K15" s="109"/>
-      <c r="L15" s="109"/>
-      <c r="M15" s="109"/>
-      <c r="N15" s="109"/>
-      <c r="O15" s="109"/>
-      <c r="P15" s="109"/>
-      <c r="Q15" s="109"/>
-      <c r="R15" s="109"/>
-      <c r="S15" s="109"/>
-      <c r="T15" s="109"/>
-      <c r="U15" s="109"/>
-      <c r="V15" s="109"/>
-      <c r="W15" s="109"/>
-      <c r="X15" s="109"/>
-      <c r="Y15" s="109"/>
-    </row>
-    <row r="16" s="78" customFormat="1" ht="50.25" customHeight="1">
-      <c r="B16" s="80" t="s">
+      <c r="B15" s="103"/>
+      <c r="C15" s="103"/>
+      <c r="D15" s="103"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="103"/>
+      <c r="G15" s="103"/>
+      <c r="H15" s="103"/>
+      <c r="I15" s="103"/>
+      <c r="J15" s="103"/>
+      <c r="K15" s="103"/>
+      <c r="L15" s="103"/>
+      <c r="M15" s="103"/>
+      <c r="N15" s="103"/>
+      <c r="O15" s="103"/>
+      <c r="P15" s="103"/>
+      <c r="Q15" s="103"/>
+      <c r="R15" s="103"/>
+      <c r="S15" s="103"/>
+      <c r="T15" s="103"/>
+      <c r="U15" s="103"/>
+      <c r="V15" s="103"/>
+      <c r="W15" s="103"/>
+      <c r="X15" s="103"/>
+      <c r="Y15" s="103"/>
+    </row>
+    <row r="16" s="72" customFormat="1" ht="50.25" customHeight="1">
+      <c r="B16" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="C16" s="110"/>
-      <c r="D16" s="111" t="s">
+      <c r="C16" s="104"/>
+      <c r="D16" s="105" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="112" t="s">
+      <c r="E16" s="98" t="s">
         <v>109</v>
       </c>
-      <c r="F16" s="113" t="s">
+      <c r="F16" s="106" t="s">
         <v>51</v>
       </c>
-      <c r="G16" s="114"/>
-      <c r="H16" s="90"/>
-      <c r="I16" s="90"/>
-      <c r="K16" s="84"/>
-      <c r="L16" s="84"/>
-      <c r="U16" s="84"/>
-      <c r="V16" s="84"/>
-      <c r="W16" s="84"/>
-      <c r="X16" s="84"/>
-      <c r="Y16" s="84"/>
-      <c r="Z16" s="115"/>
+      <c r="G16" s="107"/>
+      <c r="H16" s="84"/>
+      <c r="I16" s="84"/>
+      <c r="K16" s="78"/>
+      <c r="L16" s="78"/>
+      <c r="U16" s="78"/>
+      <c r="V16" s="78"/>
+      <c r="W16" s="78"/>
+      <c r="X16" s="78"/>
+      <c r="Y16" s="78"/>
+      <c r="Z16" s="108"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="96" t="s">
+      <c r="B17" s="90" t="s">
         <v>110</v>
       </c>
-      <c r="C17" s="116"/>
-      <c r="D17" s="98">
+      <c r="C17" s="109"/>
+      <c r="D17" s="92">
         <v>900761625</v>
       </c>
-      <c r="E17" s="117">
+      <c r="E17" s="110">
         <v>1</v>
       </c>
-      <c r="F17" s="118" t="s">
+      <c r="F17" s="111" t="s">
         <v>111</v>
       </c>
-      <c r="G17" s="119" t="s">
+      <c r="G17" s="112" t="s">
         <v>112</v>
       </c>
-      <c r="H17" s="90"/>
-      <c r="I17" s="90"/>
-      <c r="K17" s="90"/>
-      <c r="L17" s="90"/>
-      <c r="U17" s="90"/>
-      <c r="V17" s="90"/>
-      <c r="W17" s="90"/>
-      <c r="X17" s="90"/>
-      <c r="Y17" s="90"/>
+      <c r="H17" s="84"/>
+      <c r="I17" s="84"/>
+      <c r="K17" s="84"/>
+      <c r="L17" s="84"/>
+      <c r="U17" s="84"/>
+      <c r="V17" s="84"/>
+      <c r="W17" s="84"/>
+      <c r="X17" s="84"/>
+      <c r="Y17" s="84"/>
     </row>
     <row r="18" ht="10" customHeight="1">
-      <c r="B18" s="109"/>
-      <c r="C18" s="109"/>
-      <c r="D18" s="109"/>
-      <c r="E18" s="109"/>
-      <c r="F18" s="109"/>
-      <c r="G18" s="109"/>
-      <c r="H18" s="109"/>
-      <c r="I18" s="109"/>
-      <c r="J18" s="109"/>
-      <c r="K18" s="109"/>
-      <c r="L18" s="109"/>
-      <c r="M18" s="109"/>
-      <c r="N18" s="109"/>
-      <c r="O18" s="109"/>
-      <c r="P18" s="109"/>
-      <c r="Q18" s="109"/>
-      <c r="R18" s="109"/>
-      <c r="S18" s="109"/>
-      <c r="T18" s="109"/>
-      <c r="U18" s="109"/>
-      <c r="V18" s="109"/>
-      <c r="W18" s="109"/>
-      <c r="X18" s="109"/>
-      <c r="Y18" s="109"/>
-    </row>
-    <row r="19" s="78" customFormat="1" ht="28.5">
-      <c r="B19" s="80" t="s">
+      <c r="B18" s="103"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="103"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="103"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="103"/>
+      <c r="I18" s="103"/>
+      <c r="J18" s="103"/>
+      <c r="K18" s="103"/>
+      <c r="L18" s="103"/>
+      <c r="M18" s="103"/>
+      <c r="N18" s="103"/>
+      <c r="O18" s="103"/>
+      <c r="P18" s="103"/>
+      <c r="Q18" s="103"/>
+      <c r="R18" s="103"/>
+      <c r="S18" s="103"/>
+      <c r="T18" s="103"/>
+      <c r="U18" s="103"/>
+      <c r="V18" s="103"/>
+      <c r="W18" s="103"/>
+      <c r="X18" s="103"/>
+      <c r="Y18" s="103"/>
+    </row>
+    <row r="19" s="72" customFormat="1" ht="28.5">
+      <c r="B19" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="110"/>
-      <c r="D19" s="103" t="s">
+      <c r="C19" s="104"/>
+      <c r="D19" s="97" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="112" t="s">
+      <c r="E19" s="98" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="120" t="s">
+      <c r="F19" s="113" t="s">
         <v>58</v>
       </c>
-      <c r="G19" s="105"/>
-      <c r="H19" s="84"/>
-      <c r="L19" s="84"/>
-      <c r="M19" s="84"/>
-      <c r="O19" s="84"/>
-      <c r="P19" s="84"/>
-      <c r="Q19" s="84"/>
-      <c r="R19" s="84"/>
-      <c r="T19" s="84"/>
-      <c r="U19" s="84"/>
-      <c r="V19" s="84"/>
-      <c r="W19" s="84"/>
-      <c r="X19" s="84"/>
-      <c r="Y19" s="84"/>
-      <c r="Z19" s="115"/>
+      <c r="G19" s="99"/>
+      <c r="H19" s="78"/>
+      <c r="L19" s="78"/>
+      <c r="M19" s="78"/>
+      <c r="O19" s="78"/>
+      <c r="P19" s="78"/>
+      <c r="Q19" s="78"/>
+      <c r="R19" s="78"/>
+      <c r="T19" s="78"/>
+      <c r="U19" s="78"/>
+      <c r="V19" s="78"/>
+      <c r="W19" s="78"/>
+      <c r="X19" s="78"/>
+      <c r="Y19" s="78"/>
+      <c r="Z19" s="108"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="96" t="s">
+      <c r="B20" s="90" t="s">
         <v>113</v>
       </c>
-      <c r="C20" s="121"/>
-      <c r="D20" s="106" t="s">
+      <c r="C20" s="114"/>
+      <c r="D20" s="100" t="s">
         <v>114</v>
       </c>
-      <c r="E20" s="122"/>
-      <c r="F20" s="123" t="s">
+      <c r="E20" s="115"/>
+      <c r="F20" s="116" t="s">
         <v>115</v>
       </c>
-      <c r="G20" s="108"/>
-      <c r="H20" s="90"/>
-      <c r="L20" s="90"/>
-      <c r="M20" s="90"/>
-      <c r="O20" s="90"/>
-      <c r="P20" s="90"/>
-      <c r="Q20" s="90"/>
-      <c r="R20" s="90"/>
-      <c r="T20" s="90"/>
-      <c r="U20" s="90"/>
-      <c r="V20" s="90"/>
-      <c r="W20" s="90"/>
-      <c r="X20" s="90"/>
-      <c r="Y20" s="90"/>
+      <c r="G20" s="102"/>
+      <c r="H20" s="84"/>
+      <c r="L20" s="84"/>
+      <c r="M20" s="84"/>
+      <c r="O20" s="84"/>
+      <c r="P20" s="84"/>
+      <c r="Q20" s="84"/>
+      <c r="R20" s="84"/>
+      <c r="T20" s="84"/>
+      <c r="U20" s="84"/>
+      <c r="V20" s="84"/>
+      <c r="W20" s="84"/>
+      <c r="X20" s="84"/>
+      <c r="Y20" s="84"/>
     </row>
     <row r="21" ht="8.25" customHeight="1">
-      <c r="B21" s="109"/>
-      <c r="C21" s="109"/>
-      <c r="D21" s="109"/>
-      <c r="E21" s="109"/>
-      <c r="F21" s="109"/>
-      <c r="G21" s="109"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="109"/>
-      <c r="O21" s="109"/>
-      <c r="P21" s="109"/>
-      <c r="Q21" s="109"/>
-      <c r="R21" s="109"/>
-      <c r="S21" s="109"/>
-      <c r="T21" s="109"/>
-      <c r="U21" s="109"/>
-      <c r="V21" s="109"/>
-      <c r="W21" s="109"/>
-      <c r="X21" s="109"/>
-      <c r="Y21" s="109"/>
+      <c r="B21" s="103"/>
+      <c r="C21" s="103"/>
+      <c r="D21" s="103"/>
+      <c r="E21" s="103"/>
+      <c r="F21" s="103"/>
+      <c r="G21" s="103"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="103"/>
+      <c r="J21" s="103"/>
+      <c r="K21" s="103"/>
+      <c r="L21" s="103"/>
+      <c r="M21" s="103"/>
+      <c r="N21" s="103"/>
+      <c r="O21" s="103"/>
+      <c r="P21" s="103"/>
+      <c r="Q21" s="103"/>
+      <c r="R21" s="103"/>
+      <c r="S21" s="103"/>
+      <c r="T21" s="103"/>
+      <c r="U21" s="103"/>
+      <c r="V21" s="103"/>
+      <c r="W21" s="103"/>
+      <c r="X21" s="103"/>
+      <c r="Y21" s="103"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="124" t="s">
+      <c r="B22" s="117" t="s">
         <v>116</v>
       </c>
-      <c r="C22" s="125"/>
-      <c r="D22" s="125"/>
-      <c r="E22" s="125"/>
-      <c r="F22" s="125"/>
-      <c r="G22" s="126"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
-      <c r="J22" s="77"/>
-      <c r="K22" s="77"/>
-      <c r="L22" s="77"/>
-      <c r="M22" s="77"/>
-      <c r="N22" s="77"/>
-      <c r="O22" s="77"/>
-      <c r="P22" s="77"/>
-      <c r="Q22" s="77"/>
-      <c r="R22" s="77"/>
-      <c r="S22" s="77"/>
-      <c r="T22" s="77"/>
-      <c r="U22" s="77"/>
-      <c r="V22" s="77"/>
-      <c r="W22" s="77"/>
-      <c r="X22" s="77"/>
-      <c r="Y22" s="77"/>
-      <c r="Z22" s="77"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="118"/>
+      <c r="G22" s="119"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="71"/>
+      <c r="K22" s="71"/>
+      <c r="L22" s="71"/>
+      <c r="M22" s="71"/>
+      <c r="N22" s="71"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="71"/>
+      <c r="Q22" s="71"/>
+      <c r="R22" s="71"/>
+      <c r="S22" s="71"/>
+      <c r="T22" s="71"/>
+      <c r="U22" s="71"/>
+      <c r="V22" s="71"/>
+      <c r="W22" s="71"/>
+      <c r="X22" s="71"/>
+      <c r="Y22" s="71"/>
+      <c r="Z22" s="71"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="127" t="s">
+      <c r="B23" s="120" t="s">
         <v>117</v>
       </c>
-      <c r="C23" s="128" t="s">
+      <c r="C23" s="121" t="s">
         <v>118</v>
       </c>
-      <c r="D23" s="106"/>
-      <c r="E23" s="129" t="s">
+      <c r="D23" s="100"/>
+      <c r="E23" s="122" t="s">
         <v>119</v>
       </c>
-      <c r="F23" s="106" t="s">
+      <c r="F23" s="100" t="s">
         <v>120</v>
       </c>
-      <c r="G23" s="108"/>
-      <c r="H23" s="77"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="77"/>
-      <c r="K23" s="77"/>
-      <c r="L23" s="77"/>
-      <c r="M23" s="77"/>
-      <c r="N23" s="77"/>
-      <c r="O23" s="77"/>
-      <c r="P23" s="77"/>
-      <c r="Q23" s="77"/>
-      <c r="R23" s="77"/>
-      <c r="S23" s="77"/>
-      <c r="T23" s="77"/>
-      <c r="U23" s="77"/>
-      <c r="V23" s="77"/>
-      <c r="W23" s="77"/>
-      <c r="X23" s="77"/>
-      <c r="Y23" s="77"/>
-      <c r="Z23" s="77"/>
+      <c r="G23" s="102"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="71"/>
+      <c r="L23" s="71"/>
+      <c r="M23" s="71"/>
+      <c r="N23" s="71"/>
+      <c r="O23" s="71"/>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="71"/>
+      <c r="S23" s="71"/>
+      <c r="T23" s="71"/>
+      <c r="U23" s="71"/>
+      <c r="V23" s="71"/>
+      <c r="W23" s="71"/>
+      <c r="X23" s="71"/>
+      <c r="Y23" s="71"/>
+      <c r="Z23" s="71"/>
     </row>
     <row r="24" ht="10" customHeight="1">
-      <c r="B24" s="109"/>
-      <c r="C24" s="109"/>
-      <c r="D24" s="109"/>
-      <c r="E24" s="109"/>
-      <c r="F24" s="109"/>
-      <c r="G24" s="109"/>
-      <c r="H24" s="109"/>
-      <c r="I24" s="109"/>
-      <c r="J24" s="109"/>
-      <c r="K24" s="109"/>
-      <c r="L24" s="109"/>
-      <c r="M24" s="109"/>
-      <c r="N24" s="109"/>
-      <c r="O24" s="109"/>
-      <c r="P24" s="109"/>
-      <c r="Q24" s="109"/>
-      <c r="R24" s="109"/>
-      <c r="S24" s="109"/>
-      <c r="T24" s="109"/>
-      <c r="U24" s="109"/>
-      <c r="V24" s="109"/>
-      <c r="W24" s="109"/>
-      <c r="X24" s="109"/>
-      <c r="Y24" s="109"/>
+      <c r="B24" s="103"/>
+      <c r="C24" s="103"/>
+      <c r="D24" s="103"/>
+      <c r="E24" s="103"/>
+      <c r="F24" s="103"/>
+      <c r="G24" s="103"/>
+      <c r="H24" s="103"/>
+      <c r="I24" s="103"/>
+      <c r="J24" s="103"/>
+      <c r="K24" s="103"/>
+      <c r="L24" s="103"/>
+      <c r="M24" s="103"/>
+      <c r="N24" s="103"/>
+      <c r="O24" s="103"/>
+      <c r="P24" s="103"/>
+      <c r="Q24" s="103"/>
+      <c r="R24" s="103"/>
+      <c r="S24" s="103"/>
+      <c r="T24" s="103"/>
+      <c r="U24" s="103"/>
+      <c r="V24" s="103"/>
+      <c r="W24" s="103"/>
+      <c r="X24" s="103"/>
+      <c r="Y24" s="103"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="130"/>
-      <c r="C25" s="131" t="s">
+      <c r="B25" s="123"/>
+      <c r="C25" s="124" t="s">
         <v>121</v>
       </c>
-      <c r="D25" s="130"/>
-      <c r="E25" s="132"/>
-      <c r="F25" s="132"/>
-      <c r="G25" s="133"/>
-      <c r="H25" s="134"/>
-      <c r="I25" s="134"/>
-      <c r="J25" s="134"/>
-      <c r="K25" s="135"/>
-      <c r="L25" s="135"/>
-      <c r="M25" s="135"/>
-      <c r="N25" s="135"/>
-      <c r="O25" s="135"/>
-      <c r="P25" s="135"/>
-      <c r="Q25" s="135"/>
-      <c r="R25" s="135"/>
-      <c r="S25" s="135"/>
-      <c r="T25" s="135"/>
-      <c r="U25" s="135"/>
-      <c r="V25" s="135"/>
-      <c r="W25" s="135"/>
-      <c r="X25" s="135"/>
-      <c r="Y25" s="135"/>
+      <c r="D25" s="123"/>
+      <c r="E25" s="125"/>
+      <c r="F25" s="125"/>
+      <c r="G25" s="126"/>
+      <c r="H25" s="127"/>
+      <c r="I25" s="127"/>
+      <c r="J25" s="127"/>
+      <c r="K25" s="128"/>
+      <c r="L25" s="128"/>
+      <c r="M25" s="128"/>
+      <c r="N25" s="128"/>
+      <c r="O25" s="128"/>
+      <c r="P25" s="128"/>
+      <c r="Q25" s="128"/>
+      <c r="R25" s="128"/>
+      <c r="S25" s="128"/>
+      <c r="T25" s="128"/>
+      <c r="U25" s="128"/>
+      <c r="V25" s="128"/>
+      <c r="W25" s="128"/>
+      <c r="X25" s="128"/>
+      <c r="Y25" s="128"/>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="B26" s="136" t="s">
+      <c r="B26" s="129" t="s">
         <v>122</v>
       </c>
-      <c r="C26" s="137" t="s">
+      <c r="C26" s="130" t="s">
         <v>123</v>
       </c>
-      <c r="D26" s="138"/>
-      <c r="E26" s="139" t="s">
+      <c r="D26" s="131"/>
+      <c r="E26" s="132" t="s">
         <v>122</v>
       </c>
-      <c r="F26" s="137" t="s">
+      <c r="F26" s="130" t="s">
         <v>123</v>
       </c>
-      <c r="G26" s="137"/>
-      <c r="H26" s="134"/>
-      <c r="I26" s="134"/>
-      <c r="J26" s="134"/>
-      <c r="K26" s="135"/>
-      <c r="L26" s="135"/>
-      <c r="M26" s="135"/>
-      <c r="N26" s="135"/>
-      <c r="O26" s="135"/>
-      <c r="P26" s="135"/>
-      <c r="Q26" s="135"/>
-      <c r="R26" s="135"/>
-      <c r="S26" s="135"/>
-      <c r="T26" s="135"/>
-      <c r="U26" s="135"/>
-      <c r="V26" s="135"/>
-      <c r="W26" s="135"/>
-      <c r="X26" s="135"/>
-      <c r="Y26" s="135"/>
-    </row>
-    <row r="27" s="140" customFormat="1" ht="25" customHeight="1">
-      <c r="B27" s="141"/>
-      <c r="C27" s="142" t="s">
+      <c r="G26" s="130"/>
+      <c r="H26" s="127"/>
+      <c r="I26" s="127"/>
+      <c r="J26" s="127"/>
+      <c r="K26" s="128"/>
+      <c r="L26" s="128"/>
+      <c r="M26" s="128"/>
+      <c r="N26" s="128"/>
+      <c r="O26" s="128"/>
+      <c r="P26" s="128"/>
+      <c r="Q26" s="128"/>
+      <c r="R26" s="128"/>
+      <c r="S26" s="128"/>
+      <c r="T26" s="128"/>
+      <c r="U26" s="128"/>
+      <c r="V26" s="128"/>
+      <c r="W26" s="128"/>
+      <c r="X26" s="128"/>
+      <c r="Y26" s="128"/>
+    </row>
+    <row r="27" s="133" customFormat="1" ht="25" customHeight="1">
+      <c r="B27" s="134"/>
+      <c r="C27" s="135" t="s">
         <v>124</v>
       </c>
-      <c r="D27" s="143"/>
-      <c r="E27" s="144"/>
-      <c r="F27" s="142" t="s">
+      <c r="D27" s="136"/>
+      <c r="E27" s="137"/>
+      <c r="F27" s="135" t="s">
         <v>125</v>
       </c>
-      <c r="G27" s="145"/>
-      <c r="H27" s="84"/>
-      <c r="I27" s="84"/>
-      <c r="J27" s="90"/>
-      <c r="K27" s="90"/>
-      <c r="L27" s="90"/>
-      <c r="M27" s="90"/>
-      <c r="N27" s="90"/>
-      <c r="O27" s="90"/>
-      <c r="P27" s="90"/>
-      <c r="Q27" s="84"/>
-      <c r="R27" s="84"/>
-      <c r="S27" s="90"/>
-      <c r="T27" s="90"/>
-      <c r="U27" s="90"/>
-      <c r="V27" s="90"/>
-      <c r="Z27" s="146"/>
-    </row>
-    <row r="28" s="140" customFormat="1" ht="25" customHeight="1">
-      <c r="B28" s="147"/>
-      <c r="C28" s="148" t="s">
+      <c r="G27" s="138"/>
+      <c r="H27" s="78"/>
+      <c r="I27" s="78"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="84"/>
+      <c r="O27" s="84"/>
+      <c r="P27" s="84"/>
+      <c r="Q27" s="78"/>
+      <c r="R27" s="78"/>
+      <c r="S27" s="84"/>
+      <c r="T27" s="84"/>
+      <c r="U27" s="84"/>
+      <c r="V27" s="84"/>
+      <c r="Z27" s="139"/>
+    </row>
+    <row r="28" s="133" customFormat="1" ht="25" customHeight="1">
+      <c r="B28" s="140"/>
+      <c r="C28" s="141" t="s">
         <v>126</v>
       </c>
-      <c r="D28" s="149"/>
-      <c r="E28" s="150"/>
-      <c r="F28" s="151" t="s">
+      <c r="D28" s="142"/>
+      <c r="E28" s="143"/>
+      <c r="F28" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="G28" s="152"/>
-      <c r="H28" s="84"/>
-      <c r="I28" s="84"/>
-      <c r="J28" s="90"/>
-      <c r="K28" s="90"/>
-      <c r="L28" s="90"/>
-      <c r="M28" s="90"/>
-      <c r="N28" s="90"/>
-      <c r="O28" s="90"/>
-      <c r="P28" s="90"/>
-      <c r="Q28" s="84"/>
-      <c r="R28" s="84"/>
-      <c r="S28" s="90"/>
-      <c r="T28" s="90"/>
-      <c r="U28" s="90"/>
-      <c r="V28" s="90"/>
-      <c r="Z28" s="146"/>
-    </row>
-    <row r="29" s="140" customFormat="1" ht="34.5" customHeight="1">
-      <c r="B29" s="153"/>
-      <c r="C29" s="148" t="s">
+      <c r="G28" s="145"/>
+      <c r="H28" s="78"/>
+      <c r="I28" s="78"/>
+      <c r="J28" s="84"/>
+      <c r="K28" s="84"/>
+      <c r="L28" s="84"/>
+      <c r="M28" s="84"/>
+      <c r="N28" s="84"/>
+      <c r="O28" s="84"/>
+      <c r="P28" s="84"/>
+      <c r="Q28" s="78"/>
+      <c r="R28" s="78"/>
+      <c r="S28" s="84"/>
+      <c r="T28" s="84"/>
+      <c r="U28" s="84"/>
+      <c r="V28" s="84"/>
+      <c r="Z28" s="139"/>
+    </row>
+    <row r="29" s="133" customFormat="1" ht="34.5" customHeight="1">
+      <c r="B29" s="146"/>
+      <c r="C29" s="141" t="s">
         <v>128</v>
       </c>
-      <c r="D29" s="149"/>
-      <c r="E29" s="153" t="s">
+      <c r="D29" s="142"/>
+      <c r="E29" s="146" t="s">
         <v>129</v>
       </c>
-      <c r="F29" s="151"/>
-      <c r="G29" s="152"/>
-      <c r="H29" s="84"/>
-      <c r="I29" s="84"/>
-      <c r="J29" s="90"/>
-      <c r="K29" s="90"/>
-      <c r="L29" s="90"/>
-      <c r="M29" s="90"/>
-      <c r="N29" s="90"/>
-      <c r="O29" s="90"/>
-      <c r="P29" s="90"/>
-      <c r="Q29" s="84"/>
-      <c r="R29" s="84"/>
-      <c r="S29" s="90"/>
-      <c r="T29" s="90"/>
-      <c r="U29" s="90"/>
-      <c r="V29" s="90"/>
-      <c r="Z29" s="146"/>
-    </row>
-    <row r="30" s="140" customFormat="1" ht="45" customHeight="1">
-      <c r="B30" s="154" t="s">
+      <c r="F29" s="144"/>
+      <c r="G29" s="145"/>
+      <c r="H29" s="78"/>
+      <c r="I29" s="78"/>
+      <c r="J29" s="84"/>
+      <c r="K29" s="84"/>
+      <c r="L29" s="84"/>
+      <c r="M29" s="84"/>
+      <c r="N29" s="84"/>
+      <c r="O29" s="84"/>
+      <c r="P29" s="84"/>
+      <c r="Q29" s="78"/>
+      <c r="R29" s="78"/>
+      <c r="S29" s="84"/>
+      <c r="T29" s="84"/>
+      <c r="U29" s="84"/>
+      <c r="V29" s="84"/>
+      <c r="Z29" s="139"/>
+    </row>
+    <row r="30" s="133" customFormat="1" ht="45" customHeight="1">
+      <c r="B30" s="147" t="s">
         <v>130</v>
       </c>
-      <c r="C30" s="155" t="s">
+      <c r="C30" s="148" t="s">
         <v>131</v>
       </c>
-      <c r="D30" s="149"/>
-      <c r="E30" s="156" t="s">
+      <c r="D30" s="142"/>
+      <c r="E30" s="149" t="s">
         <v>132</v>
       </c>
-      <c r="F30" s="148" t="s">
+      <c r="F30" s="141" t="s">
         <v>133</v>
       </c>
-      <c r="G30" s="149"/>
-      <c r="H30" s="84"/>
-      <c r="I30" s="84"/>
-      <c r="J30" s="90"/>
-      <c r="K30" s="90"/>
-      <c r="L30" s="90"/>
-      <c r="M30" s="90"/>
-      <c r="N30" s="90"/>
-      <c r="O30" s="90"/>
-      <c r="P30" s="90"/>
-      <c r="Q30" s="84"/>
-      <c r="R30" s="84"/>
-      <c r="S30" s="90"/>
-      <c r="T30" s="90"/>
-      <c r="U30" s="90"/>
-      <c r="V30" s="90"/>
-      <c r="Z30" s="146"/>
-    </row>
-    <row r="31" s="140" customFormat="1" ht="45" customHeight="1">
-      <c r="B31" s="157"/>
-      <c r="C31" s="148" t="s">
+      <c r="G30" s="142"/>
+      <c r="H30" s="78"/>
+      <c r="I30" s="78"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="84"/>
+      <c r="O30" s="84"/>
+      <c r="P30" s="84"/>
+      <c r="Q30" s="78"/>
+      <c r="R30" s="78"/>
+      <c r="S30" s="84"/>
+      <c r="T30" s="84"/>
+      <c r="U30" s="84"/>
+      <c r="V30" s="84"/>
+      <c r="Z30" s="139"/>
+    </row>
+    <row r="31" s="133" customFormat="1" ht="45" customHeight="1">
+      <c r="B31" s="150"/>
+      <c r="C31" s="141" t="s">
         <v>134</v>
       </c>
-      <c r="D31" s="158"/>
-      <c r="E31" s="147"/>
-      <c r="F31" s="159" t="s">
+      <c r="D31" s="151"/>
+      <c r="E31" s="140"/>
+      <c r="F31" s="152" t="s">
         <v>135</v>
       </c>
-      <c r="G31" s="160"/>
-      <c r="H31" s="84"/>
-      <c r="I31" s="84"/>
-      <c r="J31" s="161"/>
-      <c r="K31" s="162"/>
-      <c r="L31" s="162"/>
-      <c r="M31" s="162"/>
-      <c r="N31" s="162"/>
-      <c r="O31" s="162"/>
-      <c r="P31" s="90"/>
-      <c r="Q31" s="161"/>
-      <c r="R31" s="161"/>
-      <c r="S31" s="162"/>
-      <c r="T31" s="162"/>
-      <c r="U31" s="162"/>
-      <c r="V31" s="90"/>
-      <c r="W31" s="161"/>
-      <c r="X31" s="161"/>
-      <c r="Y31" s="109"/>
-      <c r="Z31" s="146"/>
-    </row>
-    <row r="32" s="140" customFormat="1" ht="44.25" customHeight="1">
-      <c r="B32" s="157"/>
-      <c r="C32" s="148" t="s">
+      <c r="G31" s="153"/>
+      <c r="H31" s="78"/>
+      <c r="I31" s="78"/>
+      <c r="J31" s="154"/>
+      <c r="K31" s="155"/>
+      <c r="L31" s="155"/>
+      <c r="M31" s="155"/>
+      <c r="N31" s="155"/>
+      <c r="O31" s="155"/>
+      <c r="P31" s="84"/>
+      <c r="Q31" s="154"/>
+      <c r="R31" s="154"/>
+      <c r="S31" s="155"/>
+      <c r="T31" s="155"/>
+      <c r="U31" s="155"/>
+      <c r="V31" s="84"/>
+      <c r="W31" s="154"/>
+      <c r="X31" s="154"/>
+      <c r="Y31" s="103"/>
+      <c r="Z31" s="139"/>
+    </row>
+    <row r="32" s="133" customFormat="1" ht="44.25" customHeight="1">
+      <c r="B32" s="150"/>
+      <c r="C32" s="141" t="s">
         <v>136</v>
       </c>
-      <c r="D32" s="163"/>
-      <c r="E32" s="164"/>
-      <c r="F32" s="165" t="s">
+      <c r="D32" s="156"/>
+      <c r="E32" s="157"/>
+      <c r="F32" s="158" t="s">
         <v>137</v>
       </c>
-      <c r="G32" s="166" t="s">
+      <c r="G32" s="159" t="s">
         <v>138</v>
       </c>
-      <c r="H32" s="84"/>
-      <c r="I32" s="84"/>
-      <c r="J32" s="161"/>
-      <c r="K32" s="162"/>
-      <c r="L32" s="162"/>
-      <c r="M32" s="162"/>
-      <c r="N32" s="162"/>
-      <c r="O32" s="162"/>
-      <c r="P32" s="90"/>
-      <c r="Q32" s="161"/>
-      <c r="R32" s="161"/>
-      <c r="S32" s="162"/>
-      <c r="T32" s="162"/>
-      <c r="U32" s="162"/>
-      <c r="V32" s="90"/>
-      <c r="W32" s="161"/>
-      <c r="X32" s="161"/>
-      <c r="Y32" s="109"/>
-      <c r="Z32" s="146"/>
-    </row>
-    <row r="33" s="140" customFormat="1" ht="35.149999999999999" customHeight="1">
-      <c r="B33" s="167"/>
-      <c r="C33" s="121" t="s">
+      <c r="H32" s="78"/>
+      <c r="I32" s="78"/>
+      <c r="J32" s="154"/>
+      <c r="K32" s="155"/>
+      <c r="L32" s="155"/>
+      <c r="M32" s="155"/>
+      <c r="N32" s="155"/>
+      <c r="O32" s="155"/>
+      <c r="P32" s="84"/>
+      <c r="Q32" s="154"/>
+      <c r="R32" s="154"/>
+      <c r="S32" s="155"/>
+      <c r="T32" s="155"/>
+      <c r="U32" s="155"/>
+      <c r="V32" s="84"/>
+      <c r="W32" s="154"/>
+      <c r="X32" s="154"/>
+      <c r="Y32" s="103"/>
+      <c r="Z32" s="139"/>
+    </row>
+    <row r="33" s="133" customFormat="1" ht="35.149999999999999" customHeight="1">
+      <c r="B33" s="160"/>
+      <c r="C33" s="114" t="s">
         <v>139</v>
       </c>
-      <c r="D33" s="168"/>
-      <c r="E33" s="169" t="s">
+      <c r="D33" s="161"/>
+      <c r="E33" s="162" t="s">
         <v>140</v>
       </c>
-      <c r="F33" s="170" t="s">
+      <c r="F33" s="163" t="s">
         <v>141</v>
       </c>
-      <c r="G33" s="171"/>
-      <c r="H33" s="84"/>
-      <c r="I33" s="84"/>
-      <c r="J33" s="161"/>
-      <c r="K33" s="162"/>
-      <c r="L33" s="162"/>
-      <c r="M33" s="162"/>
-      <c r="N33" s="162"/>
-      <c r="O33" s="162"/>
-      <c r="P33" s="90"/>
-      <c r="Q33" s="161"/>
-      <c r="R33" s="161"/>
-      <c r="S33" s="162"/>
-      <c r="T33" s="162"/>
-      <c r="U33" s="162"/>
-      <c r="V33" s="90"/>
-      <c r="W33" s="161"/>
-      <c r="X33" s="161"/>
-      <c r="Y33" s="109"/>
-      <c r="Z33" s="146"/>
-    </row>
-    <row r="34" s="140" customFormat="1" ht="45.649999999999999" customHeight="1">
-      <c r="B34" s="164"/>
-      <c r="C34" s="165" t="s">
+      <c r="G33" s="164"/>
+      <c r="H33" s="78"/>
+      <c r="I33" s="78"/>
+      <c r="J33" s="154"/>
+      <c r="K33" s="155"/>
+      <c r="L33" s="155"/>
+      <c r="M33" s="155"/>
+      <c r="N33" s="155"/>
+      <c r="O33" s="155"/>
+      <c r="P33" s="84"/>
+      <c r="Q33" s="154"/>
+      <c r="R33" s="154"/>
+      <c r="S33" s="155"/>
+      <c r="T33" s="155"/>
+      <c r="U33" s="155"/>
+      <c r="V33" s="84"/>
+      <c r="W33" s="154"/>
+      <c r="X33" s="154"/>
+      <c r="Y33" s="103"/>
+      <c r="Z33" s="139"/>
+    </row>
+    <row r="34" s="133" customFormat="1" ht="45.649999999999999" customHeight="1">
+      <c r="B34" s="157"/>
+      <c r="C34" s="158" t="s">
         <v>142</v>
       </c>
-      <c r="D34" s="172"/>
-      <c r="E34" s="173"/>
-      <c r="F34" s="174" t="s">
+      <c r="D34" s="165"/>
+      <c r="E34" s="166"/>
+      <c r="F34" s="167" t="s">
         <v>143</v>
       </c>
-      <c r="G34" s="160"/>
-      <c r="H34" s="84"/>
-      <c r="I34" s="84"/>
-      <c r="J34" s="161"/>
-      <c r="K34" s="162"/>
-      <c r="L34" s="162"/>
-      <c r="M34" s="162"/>
-      <c r="N34" s="162"/>
-      <c r="O34" s="162"/>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="161"/>
-      <c r="R34" s="161"/>
-      <c r="S34" s="162"/>
-      <c r="T34" s="162"/>
-      <c r="U34" s="162"/>
-      <c r="V34" s="90"/>
-      <c r="W34" s="161"/>
-      <c r="X34" s="161"/>
-      <c r="Y34" s="109"/>
-      <c r="Z34" s="146"/>
-    </row>
-    <row r="35" s="140" customFormat="1" ht="31.5" customHeight="1">
-      <c r="B35" s="153" t="s">
+      <c r="G34" s="153"/>
+      <c r="H34" s="78"/>
+      <c r="I34" s="78"/>
+      <c r="J34" s="154"/>
+      <c r="K34" s="155"/>
+      <c r="L34" s="155"/>
+      <c r="M34" s="155"/>
+      <c r="N34" s="155"/>
+      <c r="O34" s="155"/>
+      <c r="P34" s="84"/>
+      <c r="Q34" s="154"/>
+      <c r="R34" s="154"/>
+      <c r="S34" s="155"/>
+      <c r="T34" s="155"/>
+      <c r="U34" s="155"/>
+      <c r="V34" s="84"/>
+      <c r="W34" s="154"/>
+      <c r="X34" s="154"/>
+      <c r="Y34" s="103"/>
+      <c r="Z34" s="139"/>
+    </row>
+    <row r="35" s="133" customFormat="1" ht="31.5" customHeight="1">
+      <c r="B35" s="146" t="s">
         <v>144</v>
       </c>
-      <c r="C35" s="170" t="s">
+      <c r="C35" s="163" t="s">
         <v>145</v>
       </c>
-      <c r="D35" s="149"/>
-      <c r="E35" s="169" t="s">
+      <c r="D35" s="142"/>
+      <c r="E35" s="162" t="s">
         <v>146</v>
       </c>
-      <c r="F35" s="175" t="s">
+      <c r="F35" s="168" t="s">
         <v>147</v>
       </c>
-      <c r="G35" s="176"/>
-      <c r="H35" s="84"/>
-      <c r="I35" s="84"/>
-      <c r="J35" s="161"/>
-      <c r="K35" s="162"/>
-      <c r="L35" s="162"/>
-      <c r="M35" s="162"/>
-      <c r="N35" s="162"/>
-      <c r="O35" s="162"/>
-      <c r="P35" s="90"/>
-      <c r="Q35" s="161"/>
-      <c r="R35" s="161"/>
-      <c r="S35" s="162"/>
-      <c r="T35" s="162"/>
-      <c r="U35" s="162"/>
-      <c r="V35" s="90"/>
-      <c r="W35" s="161"/>
-      <c r="X35" s="161"/>
-      <c r="Y35" s="109"/>
-      <c r="Z35" s="146"/>
-    </row>
-    <row r="36" s="140" customFormat="1" ht="46.5" customHeight="1">
-      <c r="B36" s="167"/>
-      <c r="C36" s="177" t="s">
+      <c r="G35" s="169"/>
+      <c r="H35" s="78"/>
+      <c r="I35" s="78"/>
+      <c r="J35" s="154"/>
+      <c r="K35" s="155"/>
+      <c r="L35" s="155"/>
+      <c r="M35" s="155"/>
+      <c r="N35" s="155"/>
+      <c r="O35" s="155"/>
+      <c r="P35" s="84"/>
+      <c r="Q35" s="154"/>
+      <c r="R35" s="154"/>
+      <c r="S35" s="155"/>
+      <c r="T35" s="155"/>
+      <c r="U35" s="155"/>
+      <c r="V35" s="84"/>
+      <c r="W35" s="154"/>
+      <c r="X35" s="154"/>
+      <c r="Y35" s="103"/>
+      <c r="Z35" s="139"/>
+    </row>
+    <row r="36" s="133" customFormat="1" ht="46.5" customHeight="1">
+      <c r="B36" s="160"/>
+      <c r="C36" s="170" t="s">
         <v>148</v>
       </c>
-      <c r="D36" s="160"/>
-      <c r="E36" s="178"/>
-      <c r="F36" s="174" t="s">
+      <c r="D36" s="153"/>
+      <c r="E36" s="171"/>
+      <c r="F36" s="167" t="s">
         <v>149</v>
       </c>
-      <c r="G36" s="160"/>
-      <c r="H36" s="84"/>
-      <c r="I36" s="84"/>
-      <c r="J36" s="161"/>
-      <c r="K36" s="162"/>
-      <c r="L36" s="162"/>
-      <c r="M36" s="162"/>
-      <c r="N36" s="162"/>
-      <c r="O36" s="162"/>
-      <c r="P36" s="90"/>
-      <c r="Q36" s="161"/>
-      <c r="R36" s="161"/>
-      <c r="S36" s="162"/>
-      <c r="T36" s="162"/>
-      <c r="U36" s="162"/>
-      <c r="V36" s="90"/>
-      <c r="W36" s="161"/>
-      <c r="X36" s="161"/>
-      <c r="Y36" s="109"/>
-      <c r="Z36" s="146"/>
-    </row>
-    <row r="37" s="140" customFormat="1" ht="9.75" customHeight="1">
-      <c r="H37" s="84"/>
-      <c r="I37" s="84"/>
-      <c r="J37" s="161"/>
-      <c r="K37" s="162"/>
-      <c r="L37" s="162"/>
-      <c r="M37" s="162"/>
-      <c r="N37" s="162"/>
-      <c r="O37" s="162"/>
-      <c r="P37" s="90"/>
-      <c r="Q37" s="161"/>
-      <c r="R37" s="161"/>
-      <c r="S37" s="162"/>
-      <c r="T37" s="162"/>
-      <c r="U37" s="162"/>
-      <c r="V37" s="90"/>
-      <c r="W37" s="161"/>
-      <c r="X37" s="161"/>
-      <c r="Y37" s="109"/>
-      <c r="Z37" s="146"/>
+      <c r="G36" s="153"/>
+      <c r="H36" s="78"/>
+      <c r="I36" s="78"/>
+      <c r="J36" s="154"/>
+      <c r="K36" s="155"/>
+      <c r="L36" s="155"/>
+      <c r="M36" s="155"/>
+      <c r="N36" s="155"/>
+      <c r="O36" s="155"/>
+      <c r="P36" s="84"/>
+      <c r="Q36" s="154"/>
+      <c r="R36" s="154"/>
+      <c r="S36" s="155"/>
+      <c r="T36" s="155"/>
+      <c r="U36" s="155"/>
+      <c r="V36" s="84"/>
+      <c r="W36" s="154"/>
+      <c r="X36" s="154"/>
+      <c r="Y36" s="103"/>
+      <c r="Z36" s="139"/>
+    </row>
+    <row r="37" s="133" customFormat="1" ht="9.75" customHeight="1">
+      <c r="H37" s="78"/>
+      <c r="I37" s="78"/>
+      <c r="J37" s="154"/>
+      <c r="K37" s="155"/>
+      <c r="L37" s="155"/>
+      <c r="M37" s="155"/>
+      <c r="N37" s="155"/>
+      <c r="O37" s="155"/>
+      <c r="P37" s="84"/>
+      <c r="Q37" s="154"/>
+      <c r="R37" s="154"/>
+      <c r="S37" s="155"/>
+      <c r="T37" s="155"/>
+      <c r="U37" s="155"/>
+      <c r="V37" s="84"/>
+      <c r="W37" s="154"/>
+      <c r="X37" s="154"/>
+      <c r="Y37" s="103"/>
+      <c r="Z37" s="139"/>
     </row>
     <row r="38" ht="68.25" customHeight="1">
-      <c r="B38" s="179" t="s">
+      <c r="B38" s="172" t="s">
         <v>150</v>
       </c>
-      <c r="C38" s="180" t="s">
+      <c r="C38" s="173" t="s">
         <v>151</v>
       </c>
-      <c r="D38" s="181" t="s">
+      <c r="D38" s="174" t="s">
         <v>152</v>
       </c>
-      <c r="E38" s="181" t="s">
+      <c r="E38" s="174" t="s">
         <v>153</v>
       </c>
-      <c r="F38" s="181" t="s">
+      <c r="F38" s="174" t="s">
         <v>154</v>
       </c>
-      <c r="G38" s="182" t="s">
+      <c r="G38" s="175" t="s">
         <v>155</v>
       </c>
-      <c r="H38" s="84"/>
-      <c r="I38" s="84"/>
-      <c r="J38" s="84"/>
-      <c r="K38" s="84"/>
-      <c r="L38" s="84"/>
-      <c r="M38" s="84"/>
-      <c r="N38" s="84"/>
-      <c r="O38" s="84"/>
-      <c r="P38" s="84"/>
-      <c r="Q38" s="84"/>
-      <c r="R38" s="84"/>
-      <c r="S38" s="84"/>
-      <c r="T38" s="84"/>
-      <c r="U38" s="84"/>
-      <c r="V38" s="84"/>
-      <c r="W38" s="84"/>
-      <c r="X38" s="84"/>
-      <c r="Y38" s="84"/>
+      <c r="H38" s="78"/>
+      <c r="I38" s="78"/>
+      <c r="J38" s="78"/>
+      <c r="K38" s="78"/>
+      <c r="L38" s="78"/>
+      <c r="M38" s="78"/>
+      <c r="N38" s="78"/>
+      <c r="O38" s="78"/>
+      <c r="P38" s="78"/>
+      <c r="Q38" s="78"/>
+      <c r="R38" s="78"/>
+      <c r="S38" s="78"/>
+      <c r="T38" s="78"/>
+      <c r="U38" s="78"/>
+      <c r="V38" s="78"/>
+      <c r="W38" s="78"/>
+      <c r="X38" s="78"/>
+      <c r="Y38" s="78"/>
     </row>
     <row r="39" ht="52.5" customHeight="1">
-      <c r="B39" s="183" t="s">
+      <c r="B39" s="176" t="s">
         <v>156</v>
       </c>
-      <c r="C39" s="184" t="s">
+      <c r="C39" s="177" t="s">
         <v>157</v>
       </c>
-      <c r="D39" s="185"/>
-      <c r="E39" s="185"/>
-      <c r="F39" s="186" t="s">
+      <c r="D39" s="178"/>
+      <c r="E39" s="178"/>
+      <c r="F39" s="179" t="s">
         <v>158</v>
       </c>
-      <c r="G39" s="187" t="s">
+      <c r="G39" s="180" t="s">
         <v>159</v>
       </c>
-      <c r="H39" s="84"/>
-      <c r="I39" s="84"/>
-      <c r="J39" s="84"/>
-      <c r="K39" s="84"/>
-      <c r="L39" s="84"/>
-      <c r="M39" s="84"/>
-      <c r="N39" s="84"/>
-      <c r="O39" s="84"/>
-      <c r="P39" s="84"/>
-      <c r="Q39" s="84"/>
-      <c r="R39" s="84"/>
-      <c r="S39" s="84"/>
-      <c r="T39" s="84"/>
-      <c r="U39" s="84"/>
-      <c r="V39" s="84"/>
-      <c r="W39" s="84"/>
-      <c r="X39" s="84"/>
-      <c r="Y39" s="84"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
+      <c r="J39" s="78"/>
+      <c r="K39" s="78"/>
+      <c r="L39" s="78"/>
+      <c r="M39" s="78"/>
+      <c r="N39" s="78"/>
+      <c r="O39" s="78"/>
+      <c r="P39" s="78"/>
+      <c r="Q39" s="78"/>
+      <c r="R39" s="78"/>
+      <c r="S39" s="78"/>
+      <c r="T39" s="78"/>
+      <c r="U39" s="78"/>
+      <c r="V39" s="78"/>
+      <c r="W39" s="78"/>
+      <c r="X39" s="78"/>
+      <c r="Y39" s="78"/>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="B40" s="188"/>
-      <c r="C40" s="189"/>
-      <c r="D40" s="190"/>
-      <c r="E40" s="190"/>
-      <c r="F40" s="190"/>
-      <c r="G40" s="191"/>
-      <c r="H40" s="90"/>
-      <c r="I40" s="84"/>
-      <c r="J40" s="84"/>
-      <c r="K40" s="84"/>
-      <c r="L40" s="84"/>
-      <c r="M40" s="84"/>
-      <c r="N40" s="84"/>
-      <c r="O40" s="84"/>
-      <c r="P40" s="84"/>
-      <c r="Q40" s="84"/>
-      <c r="R40" s="84"/>
-      <c r="S40" s="84"/>
-      <c r="T40" s="84"/>
-      <c r="U40" s="84"/>
-      <c r="V40" s="84"/>
-      <c r="W40" s="84"/>
-      <c r="X40" s="84"/>
-      <c r="Y40" s="84"/>
+      <c r="B40" s="181"/>
+      <c r="C40" s="182"/>
+      <c r="D40" s="183"/>
+      <c r="E40" s="183"/>
+      <c r="F40" s="183"/>
+      <c r="G40" s="184"/>
+      <c r="H40" s="84"/>
+      <c r="I40" s="78"/>
+      <c r="J40" s="78"/>
+      <c r="K40" s="78"/>
+      <c r="L40" s="78"/>
+      <c r="M40" s="78"/>
+      <c r="N40" s="78"/>
+      <c r="O40" s="78"/>
+      <c r="P40" s="78"/>
+      <c r="Q40" s="78"/>
+      <c r="R40" s="78"/>
+      <c r="S40" s="78"/>
+      <c r="T40" s="78"/>
+      <c r="U40" s="78"/>
+      <c r="V40" s="78"/>
+      <c r="W40" s="78"/>
+      <c r="X40" s="78"/>
+      <c r="Y40" s="78"/>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="B41" s="192"/>
-      <c r="C41" s="193"/>
-      <c r="D41" s="194"/>
-      <c r="E41" s="194"/>
-      <c r="F41" s="194"/>
-      <c r="G41" s="195"/>
-      <c r="H41" s="90"/>
-      <c r="I41" s="84"/>
-      <c r="J41" s="84"/>
-      <c r="K41" s="84"/>
-      <c r="L41" s="84"/>
-      <c r="M41" s="84"/>
-      <c r="N41" s="84"/>
-      <c r="O41" s="84"/>
-      <c r="P41" s="84"/>
-      <c r="Q41" s="84"/>
-      <c r="R41" s="84"/>
-      <c r="S41" s="84"/>
-      <c r="T41" s="84"/>
-      <c r="U41" s="84"/>
-      <c r="V41" s="84"/>
-      <c r="W41" s="84"/>
-      <c r="X41" s="84"/>
-      <c r="Y41" s="84"/>
+      <c r="B41" s="185"/>
+      <c r="C41" s="186"/>
+      <c r="D41" s="187"/>
+      <c r="E41" s="187"/>
+      <c r="F41" s="187"/>
+      <c r="G41" s="188"/>
+      <c r="H41" s="84"/>
+      <c r="I41" s="78"/>
+      <c r="J41" s="78"/>
+      <c r="K41" s="78"/>
+      <c r="L41" s="78"/>
+      <c r="M41" s="78"/>
+      <c r="N41" s="78"/>
+      <c r="O41" s="78"/>
+      <c r="P41" s="78"/>
+      <c r="Q41" s="78"/>
+      <c r="R41" s="78"/>
+      <c r="S41" s="78"/>
+      <c r="T41" s="78"/>
+      <c r="U41" s="78"/>
+      <c r="V41" s="78"/>
+      <c r="W41" s="78"/>
+      <c r="X41" s="78"/>
+      <c r="Y41" s="78"/>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="B42" s="196"/>
-      <c r="C42" s="197"/>
-      <c r="D42" s="198"/>
-      <c r="E42" s="198"/>
-      <c r="F42" s="198"/>
-      <c r="G42" s="199"/>
-      <c r="H42" s="90"/>
-      <c r="I42" s="84"/>
-      <c r="J42" s="84"/>
-      <c r="K42" s="84"/>
-      <c r="L42" s="84"/>
-      <c r="M42" s="84"/>
-      <c r="N42" s="84"/>
-      <c r="O42" s="84"/>
-      <c r="P42" s="84"/>
-      <c r="Q42" s="84"/>
-      <c r="R42" s="84"/>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
-      <c r="V42" s="84"/>
-      <c r="W42" s="84"/>
-      <c r="X42" s="84"/>
-      <c r="Y42" s="84"/>
+      <c r="B42" s="189"/>
+      <c r="C42" s="190"/>
+      <c r="D42" s="191"/>
+      <c r="E42" s="191"/>
+      <c r="F42" s="191"/>
+      <c r="G42" s="192"/>
+      <c r="H42" s="84"/>
+      <c r="I42" s="78"/>
+      <c r="J42" s="78"/>
+      <c r="K42" s="78"/>
+      <c r="L42" s="78"/>
+      <c r="M42" s="78"/>
+      <c r="N42" s="78"/>
+      <c r="O42" s="78"/>
+      <c r="P42" s="78"/>
+      <c r="Q42" s="78"/>
+      <c r="R42" s="78"/>
+      <c r="S42" s="78"/>
+      <c r="T42" s="78"/>
+      <c r="U42" s="78"/>
+      <c r="V42" s="78"/>
+      <c r="W42" s="78"/>
+      <c r="X42" s="78"/>
+      <c r="Y42" s="78"/>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="B43" s="192"/>
-      <c r="C43" s="193"/>
-      <c r="D43" s="194"/>
-      <c r="E43" s="194"/>
-      <c r="F43" s="194"/>
-      <c r="G43" s="195"/>
-      <c r="H43" s="90"/>
-      <c r="I43" s="84"/>
-      <c r="J43" s="84"/>
-      <c r="K43" s="84"/>
-      <c r="L43" s="84"/>
-      <c r="M43" s="84"/>
-      <c r="N43" s="84"/>
-      <c r="O43" s="84"/>
-      <c r="P43" s="84"/>
-      <c r="Q43" s="84"/>
-      <c r="R43" s="84"/>
-      <c r="S43" s="84"/>
-      <c r="T43" s="84"/>
-      <c r="U43" s="84"/>
-      <c r="V43" s="84"/>
-      <c r="W43" s="84"/>
-      <c r="X43" s="84"/>
-      <c r="Y43" s="84"/>
+      <c r="B43" s="185"/>
+      <c r="C43" s="186"/>
+      <c r="D43" s="187"/>
+      <c r="E43" s="187"/>
+      <c r="F43" s="187"/>
+      <c r="G43" s="188"/>
+      <c r="H43" s="84"/>
+      <c r="I43" s="78"/>
+      <c r="J43" s="78"/>
+      <c r="K43" s="78"/>
+      <c r="L43" s="78"/>
+      <c r="M43" s="78"/>
+      <c r="N43" s="78"/>
+      <c r="O43" s="78"/>
+      <c r="P43" s="78"/>
+      <c r="Q43" s="78"/>
+      <c r="R43" s="78"/>
+      <c r="S43" s="78"/>
+      <c r="T43" s="78"/>
+      <c r="U43" s="78"/>
+      <c r="V43" s="78"/>
+      <c r="W43" s="78"/>
+      <c r="X43" s="78"/>
+      <c r="Y43" s="78"/>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="B44" s="196"/>
-      <c r="C44" s="197"/>
-      <c r="D44" s="198"/>
-      <c r="E44" s="198"/>
-      <c r="F44" s="198"/>
-      <c r="G44" s="199"/>
-      <c r="H44" s="90"/>
-      <c r="I44" s="84"/>
-      <c r="J44" s="84"/>
-      <c r="K44" s="84"/>
-      <c r="L44" s="84"/>
-      <c r="M44" s="84"/>
-      <c r="N44" s="84"/>
-      <c r="O44" s="84"/>
-      <c r="P44" s="84"/>
-      <c r="Q44" s="84"/>
-      <c r="R44" s="84"/>
-      <c r="S44" s="84"/>
-      <c r="T44" s="84"/>
-      <c r="U44" s="84"/>
-      <c r="V44" s="84"/>
-      <c r="W44" s="84"/>
-      <c r="X44" s="84"/>
-      <c r="Y44" s="84"/>
+      <c r="B44" s="189"/>
+      <c r="C44" s="190"/>
+      <c r="D44" s="191"/>
+      <c r="E44" s="191"/>
+      <c r="F44" s="191"/>
+      <c r="G44" s="192"/>
+      <c r="H44" s="84"/>
+      <c r="I44" s="78"/>
+      <c r="J44" s="78"/>
+      <c r="K44" s="78"/>
+      <c r="L44" s="78"/>
+      <c r="M44" s="78"/>
+      <c r="N44" s="78"/>
+      <c r="O44" s="78"/>
+      <c r="P44" s="78"/>
+      <c r="Q44" s="78"/>
+      <c r="R44" s="78"/>
+      <c r="S44" s="78"/>
+      <c r="T44" s="78"/>
+      <c r="U44" s="78"/>
+      <c r="V44" s="78"/>
+      <c r="W44" s="78"/>
+      <c r="X44" s="78"/>
+      <c r="Y44" s="78"/>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="B45" s="192"/>
-      <c r="C45" s="193"/>
-      <c r="D45" s="194"/>
-      <c r="E45" s="194"/>
-      <c r="F45" s="194"/>
-      <c r="G45" s="195"/>
-      <c r="H45" s="90"/>
-      <c r="I45" s="84"/>
-      <c r="J45" s="84"/>
-      <c r="K45" s="84"/>
-      <c r="L45" s="84"/>
-      <c r="M45" s="84"/>
-      <c r="N45" s="84"/>
-      <c r="O45" s="84"/>
-      <c r="P45" s="84"/>
-      <c r="Q45" s="84"/>
-      <c r="R45" s="84"/>
-      <c r="S45" s="84"/>
-      <c r="T45" s="84"/>
-      <c r="U45" s="84"/>
-      <c r="V45" s="84"/>
-      <c r="W45" s="84"/>
-      <c r="X45" s="84"/>
-      <c r="Y45" s="84"/>
+      <c r="B45" s="185"/>
+      <c r="C45" s="186"/>
+      <c r="D45" s="187"/>
+      <c r="E45" s="187"/>
+      <c r="F45" s="187"/>
+      <c r="G45" s="188"/>
+      <c r="H45" s="84"/>
+      <c r="I45" s="78"/>
+      <c r="J45" s="78"/>
+      <c r="K45" s="78"/>
+      <c r="L45" s="78"/>
+      <c r="M45" s="78"/>
+      <c r="N45" s="78"/>
+      <c r="O45" s="78"/>
+      <c r="P45" s="78"/>
+      <c r="Q45" s="78"/>
+      <c r="R45" s="78"/>
+      <c r="S45" s="78"/>
+      <c r="T45" s="78"/>
+      <c r="U45" s="78"/>
+      <c r="V45" s="78"/>
+      <c r="W45" s="78"/>
+      <c r="X45" s="78"/>
+      <c r="Y45" s="78"/>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="B46" s="196"/>
-      <c r="C46" s="197"/>
-      <c r="D46" s="198"/>
-      <c r="E46" s="198"/>
-      <c r="F46" s="198"/>
-      <c r="G46" s="199"/>
-      <c r="H46" s="90"/>
-      <c r="I46" s="84"/>
-      <c r="J46" s="84"/>
-      <c r="K46" s="84"/>
-      <c r="L46" s="84"/>
-      <c r="M46" s="84"/>
-      <c r="N46" s="84"/>
-      <c r="O46" s="84"/>
-      <c r="P46" s="84"/>
-      <c r="Q46" s="84"/>
-      <c r="R46" s="84"/>
-      <c r="S46" s="84"/>
-      <c r="T46" s="84"/>
-      <c r="U46" s="84"/>
-      <c r="V46" s="84"/>
-      <c r="W46" s="84"/>
-      <c r="X46" s="84"/>
-      <c r="Y46" s="84"/>
+      <c r="B46" s="189"/>
+      <c r="C46" s="190"/>
+      <c r="D46" s="191"/>
+      <c r="E46" s="191"/>
+      <c r="F46" s="191"/>
+      <c r="G46" s="192"/>
+      <c r="H46" s="84"/>
+      <c r="I46" s="78"/>
+      <c r="J46" s="78"/>
+      <c r="K46" s="78"/>
+      <c r="L46" s="78"/>
+      <c r="M46" s="78"/>
+      <c r="N46" s="78"/>
+      <c r="O46" s="78"/>
+      <c r="P46" s="78"/>
+      <c r="Q46" s="78"/>
+      <c r="R46" s="78"/>
+      <c r="S46" s="78"/>
+      <c r="T46" s="78"/>
+      <c r="U46" s="78"/>
+      <c r="V46" s="78"/>
+      <c r="W46" s="78"/>
+      <c r="X46" s="78"/>
+      <c r="Y46" s="78"/>
     </row>
     <row r="47" ht="15" customHeight="1">
-      <c r="B47" s="192"/>
-      <c r="C47" s="193"/>
-      <c r="D47" s="194"/>
-      <c r="E47" s="194"/>
-      <c r="F47" s="194"/>
-      <c r="G47" s="195"/>
-      <c r="H47" s="90"/>
-      <c r="I47" s="84"/>
-      <c r="J47" s="84"/>
-      <c r="K47" s="84"/>
-      <c r="L47" s="84"/>
-      <c r="M47" s="84"/>
-      <c r="N47" s="84"/>
-      <c r="O47" s="84"/>
-      <c r="P47" s="84"/>
-      <c r="Q47" s="84"/>
-      <c r="R47" s="84"/>
-      <c r="S47" s="84"/>
-      <c r="T47" s="84"/>
-      <c r="U47" s="84"/>
-      <c r="V47" s="84"/>
-      <c r="W47" s="84"/>
-      <c r="X47" s="84"/>
-      <c r="Y47" s="84"/>
+      <c r="B47" s="185"/>
+      <c r="C47" s="186"/>
+      <c r="D47" s="187"/>
+      <c r="E47" s="187"/>
+      <c r="F47" s="187"/>
+      <c r="G47" s="188"/>
+      <c r="H47" s="84"/>
+      <c r="I47" s="78"/>
+      <c r="J47" s="78"/>
+      <c r="K47" s="78"/>
+      <c r="L47" s="78"/>
+      <c r="M47" s="78"/>
+      <c r="N47" s="78"/>
+      <c r="O47" s="78"/>
+      <c r="P47" s="78"/>
+      <c r="Q47" s="78"/>
+      <c r="R47" s="78"/>
+      <c r="S47" s="78"/>
+      <c r="T47" s="78"/>
+      <c r="U47" s="78"/>
+      <c r="V47" s="78"/>
+      <c r="W47" s="78"/>
+      <c r="X47" s="78"/>
+      <c r="Y47" s="78"/>
     </row>
     <row r="48" ht="15" customHeight="1">
-      <c r="B48" s="196"/>
-      <c r="C48" s="197"/>
-      <c r="D48" s="198"/>
-      <c r="E48" s="198"/>
-      <c r="F48" s="198"/>
-      <c r="G48" s="199"/>
-      <c r="H48" s="90"/>
-      <c r="I48" s="84"/>
-      <c r="J48" s="84"/>
-      <c r="K48" s="84"/>
-      <c r="L48" s="84"/>
-      <c r="M48" s="84"/>
-      <c r="N48" s="84"/>
-      <c r="O48" s="84"/>
-      <c r="P48" s="84"/>
-      <c r="Q48" s="84"/>
-      <c r="R48" s="84"/>
-      <c r="S48" s="84"/>
-      <c r="T48" s="84"/>
-      <c r="U48" s="84"/>
-      <c r="V48" s="84"/>
-      <c r="W48" s="84"/>
-      <c r="X48" s="84"/>
-      <c r="Y48" s="84"/>
+      <c r="B48" s="189"/>
+      <c r="C48" s="190"/>
+      <c r="D48" s="191"/>
+      <c r="E48" s="191"/>
+      <c r="F48" s="191"/>
+      <c r="G48" s="192"/>
+      <c r="H48" s="84"/>
+      <c r="I48" s="78"/>
+      <c r="J48" s="78"/>
+      <c r="K48" s="78"/>
+      <c r="L48" s="78"/>
+      <c r="M48" s="78"/>
+      <c r="N48" s="78"/>
+      <c r="O48" s="78"/>
+      <c r="P48" s="78"/>
+      <c r="Q48" s="78"/>
+      <c r="R48" s="78"/>
+      <c r="S48" s="78"/>
+      <c r="T48" s="78"/>
+      <c r="U48" s="78"/>
+      <c r="V48" s="78"/>
+      <c r="W48" s="78"/>
+      <c r="X48" s="78"/>
+      <c r="Y48" s="78"/>
     </row>
     <row r="49" ht="15" customHeight="1">
-      <c r="B49" s="192"/>
-      <c r="C49" s="193"/>
-      <c r="D49" s="194"/>
-      <c r="E49" s="194"/>
-      <c r="F49" s="194"/>
-      <c r="G49" s="195"/>
-      <c r="H49" s="90"/>
-      <c r="I49" s="84"/>
-      <c r="J49" s="84"/>
-      <c r="K49" s="84"/>
-      <c r="L49" s="84"/>
-      <c r="M49" s="84"/>
-      <c r="N49" s="84"/>
-      <c r="O49" s="84"/>
-      <c r="P49" s="84"/>
-      <c r="Q49" s="84"/>
-      <c r="R49" s="84"/>
-      <c r="S49" s="84"/>
-      <c r="T49" s="84"/>
-      <c r="U49" s="84"/>
-      <c r="V49" s="84"/>
-      <c r="W49" s="84"/>
-      <c r="X49" s="84"/>
-      <c r="Y49" s="84"/>
+      <c r="B49" s="185"/>
+      <c r="C49" s="186"/>
+      <c r="D49" s="187"/>
+      <c r="E49" s="187"/>
+      <c r="F49" s="187"/>
+      <c r="G49" s="188"/>
+      <c r="H49" s="84"/>
+      <c r="I49" s="78"/>
+      <c r="J49" s="78"/>
+      <c r="K49" s="78"/>
+      <c r="L49" s="78"/>
+      <c r="M49" s="78"/>
+      <c r="N49" s="78"/>
+      <c r="O49" s="78"/>
+      <c r="P49" s="78"/>
+      <c r="Q49" s="78"/>
+      <c r="R49" s="78"/>
+      <c r="S49" s="78"/>
+      <c r="T49" s="78"/>
+      <c r="U49" s="78"/>
+      <c r="V49" s="78"/>
+      <c r="W49" s="78"/>
+      <c r="X49" s="78"/>
+      <c r="Y49" s="78"/>
     </row>
     <row r="50" ht="15" customHeight="1">
-      <c r="B50" s="196"/>
-      <c r="C50" s="197"/>
-      <c r="D50" s="198"/>
-      <c r="E50" s="198"/>
-      <c r="F50" s="198"/>
-      <c r="G50" s="199"/>
-      <c r="H50" s="90"/>
-      <c r="I50" s="84"/>
-      <c r="J50" s="84"/>
-      <c r="K50" s="84"/>
-      <c r="L50" s="84"/>
-      <c r="M50" s="84"/>
-      <c r="N50" s="84"/>
-      <c r="O50" s="84"/>
-      <c r="P50" s="84"/>
-      <c r="Q50" s="84"/>
-      <c r="R50" s="84"/>
-      <c r="S50" s="84"/>
-      <c r="T50" s="84"/>
-      <c r="U50" s="84"/>
-      <c r="V50" s="84"/>
-      <c r="W50" s="84"/>
-      <c r="X50" s="84"/>
-      <c r="Y50" s="84"/>
+      <c r="B50" s="189"/>
+      <c r="C50" s="190"/>
+      <c r="D50" s="191"/>
+      <c r="E50" s="191"/>
+      <c r="F50" s="191"/>
+      <c r="G50" s="192"/>
+      <c r="H50" s="84"/>
+      <c r="I50" s="78"/>
+      <c r="J50" s="78"/>
+      <c r="K50" s="78"/>
+      <c r="L50" s="78"/>
+      <c r="M50" s="78"/>
+      <c r="N50" s="78"/>
+      <c r="O50" s="78"/>
+      <c r="P50" s="78"/>
+      <c r="Q50" s="78"/>
+      <c r="R50" s="78"/>
+      <c r="S50" s="78"/>
+      <c r="T50" s="78"/>
+      <c r="U50" s="78"/>
+      <c r="V50" s="78"/>
+      <c r="W50" s="78"/>
+      <c r="X50" s="78"/>
+      <c r="Y50" s="78"/>
     </row>
     <row r="51" ht="15" customHeight="1">
-      <c r="B51" s="192"/>
-      <c r="C51" s="193"/>
-      <c r="D51" s="194"/>
-      <c r="E51" s="194"/>
-      <c r="F51" s="194"/>
-      <c r="G51" s="195"/>
-      <c r="H51" s="90"/>
-      <c r="I51" s="84"/>
-      <c r="J51" s="84"/>
-      <c r="K51" s="84"/>
-      <c r="L51" s="84"/>
-      <c r="M51" s="84"/>
-      <c r="N51" s="84"/>
-      <c r="O51" s="84"/>
-      <c r="P51" s="84"/>
-      <c r="Q51" s="84"/>
-      <c r="R51" s="84"/>
-      <c r="S51" s="84"/>
-      <c r="T51" s="84"/>
-      <c r="U51" s="84"/>
-      <c r="V51" s="84"/>
-      <c r="W51" s="84"/>
-      <c r="X51" s="84"/>
-      <c r="Y51" s="84"/>
+      <c r="B51" s="185"/>
+      <c r="C51" s="186"/>
+      <c r="D51" s="187"/>
+      <c r="E51" s="187"/>
+      <c r="F51" s="187"/>
+      <c r="G51" s="188"/>
+      <c r="H51" s="84"/>
+      <c r="I51" s="78"/>
+      <c r="J51" s="78"/>
+      <c r="K51" s="78"/>
+      <c r="L51" s="78"/>
+      <c r="M51" s="78"/>
+      <c r="N51" s="78"/>
+      <c r="O51" s="78"/>
+      <c r="P51" s="78"/>
+      <c r="Q51" s="78"/>
+      <c r="R51" s="78"/>
+      <c r="S51" s="78"/>
+      <c r="T51" s="78"/>
+      <c r="U51" s="78"/>
+      <c r="V51" s="78"/>
+      <c r="W51" s="78"/>
+      <c r="X51" s="78"/>
+      <c r="Y51" s="78"/>
     </row>
     <row r="52" ht="15" customHeight="1">
-      <c r="B52" s="196"/>
-      <c r="C52" s="197"/>
-      <c r="D52" s="198"/>
-      <c r="E52" s="198"/>
-      <c r="F52" s="198"/>
-      <c r="G52" s="199"/>
-      <c r="H52" s="90"/>
-      <c r="I52" s="84"/>
-      <c r="J52" s="84"/>
-      <c r="K52" s="84"/>
-      <c r="L52" s="84"/>
-      <c r="M52" s="84"/>
-      <c r="N52" s="84"/>
-      <c r="O52" s="84"/>
-      <c r="P52" s="84"/>
-      <c r="Q52" s="84"/>
-      <c r="R52" s="84"/>
-      <c r="S52" s="84"/>
-      <c r="T52" s="84"/>
-      <c r="U52" s="84"/>
-      <c r="V52" s="84"/>
-      <c r="W52" s="84"/>
-      <c r="X52" s="84"/>
-      <c r="Y52" s="84"/>
+      <c r="B52" s="189"/>
+      <c r="C52" s="190"/>
+      <c r="D52" s="191"/>
+      <c r="E52" s="191"/>
+      <c r="F52" s="191"/>
+      <c r="G52" s="192"/>
+      <c r="H52" s="84"/>
+      <c r="I52" s="78"/>
+      <c r="J52" s="78"/>
+      <c r="K52" s="78"/>
+      <c r="L52" s="78"/>
+      <c r="M52" s="78"/>
+      <c r="N52" s="78"/>
+      <c r="O52" s="78"/>
+      <c r="P52" s="78"/>
+      <c r="Q52" s="78"/>
+      <c r="R52" s="78"/>
+      <c r="S52" s="78"/>
+      <c r="T52" s="78"/>
+      <c r="U52" s="78"/>
+      <c r="V52" s="78"/>
+      <c r="W52" s="78"/>
+      <c r="X52" s="78"/>
+      <c r="Y52" s="78"/>
     </row>
     <row r="53" ht="15" customHeight="1">
-      <c r="B53" s="200"/>
-      <c r="C53" s="201"/>
-      <c r="D53" s="202"/>
-      <c r="E53" s="202"/>
-      <c r="F53" s="202"/>
-      <c r="G53" s="203"/>
-      <c r="H53" s="90"/>
-      <c r="I53" s="84"/>
-      <c r="J53" s="84"/>
-      <c r="K53" s="84"/>
-      <c r="L53" s="84"/>
-      <c r="M53" s="84"/>
-      <c r="N53" s="84"/>
-      <c r="O53" s="84"/>
-      <c r="P53" s="84"/>
-      <c r="Q53" s="84"/>
-      <c r="R53" s="84"/>
-      <c r="S53" s="84"/>
-      <c r="T53" s="84"/>
-      <c r="U53" s="84"/>
-      <c r="V53" s="84"/>
-      <c r="W53" s="84"/>
-      <c r="X53" s="84"/>
-      <c r="Y53" s="84"/>
+      <c r="B53" s="193"/>
+      <c r="C53" s="194"/>
+      <c r="D53" s="195"/>
+      <c r="E53" s="195"/>
+      <c r="F53" s="195"/>
+      <c r="G53" s="196"/>
+      <c r="H53" s="84"/>
+      <c r="I53" s="78"/>
+      <c r="J53" s="78"/>
+      <c r="K53" s="78"/>
+      <c r="L53" s="78"/>
+      <c r="M53" s="78"/>
+      <c r="N53" s="78"/>
+      <c r="O53" s="78"/>
+      <c r="P53" s="78"/>
+      <c r="Q53" s="78"/>
+      <c r="R53" s="78"/>
+      <c r="S53" s="78"/>
+      <c r="T53" s="78"/>
+      <c r="U53" s="78"/>
+      <c r="V53" s="78"/>
+      <c r="W53" s="78"/>
+      <c r="X53" s="78"/>
+      <c r="Y53" s="78"/>
     </row>
     <row r="54" ht="15" customHeight="1">
-      <c r="B54" s="204"/>
-      <c r="C54" s="90"/>
-      <c r="D54" s="90"/>
-      <c r="E54" s="90"/>
-      <c r="F54" s="90"/>
-      <c r="G54" s="90"/>
-      <c r="H54" s="90"/>
-      <c r="I54" s="84"/>
-      <c r="J54" s="84"/>
-      <c r="K54" s="84"/>
-      <c r="L54" s="84"/>
-      <c r="M54" s="84"/>
-      <c r="N54" s="84"/>
-      <c r="O54" s="84"/>
-      <c r="P54" s="84"/>
-      <c r="Q54" s="84"/>
-      <c r="R54" s="84"/>
-      <c r="S54" s="84"/>
-      <c r="T54" s="84"/>
-      <c r="U54" s="84"/>
-      <c r="V54" s="84"/>
-      <c r="W54" s="84"/>
-      <c r="X54" s="84"/>
-      <c r="Y54" s="84"/>
+      <c r="B54" s="197"/>
+      <c r="C54" s="84"/>
+      <c r="D54" s="84"/>
+      <c r="E54" s="84"/>
+      <c r="F54" s="84"/>
+      <c r="G54" s="84"/>
+      <c r="H54" s="84"/>
+      <c r="I54" s="78"/>
+      <c r="J54" s="78"/>
+      <c r="K54" s="78"/>
+      <c r="L54" s="78"/>
+      <c r="M54" s="78"/>
+      <c r="N54" s="78"/>
+      <c r="O54" s="78"/>
+      <c r="P54" s="78"/>
+      <c r="Q54" s="78"/>
+      <c r="R54" s="78"/>
+      <c r="S54" s="78"/>
+      <c r="T54" s="78"/>
+      <c r="U54" s="78"/>
+      <c r="V54" s="78"/>
+      <c r="W54" s="78"/>
+      <c r="X54" s="78"/>
+      <c r="Y54" s="78"/>
     </row>
     <row r="55" ht="23.25" customHeight="1">
-      <c r="B55" s="205"/>
-      <c r="C55" s="206" t="s">
+      <c r="B55" s="198"/>
+      <c r="C55" s="199" t="s">
         <v>160</v>
       </c>
-      <c r="D55" s="207"/>
-      <c r="E55" s="207"/>
-      <c r="F55" s="207"/>
-      <c r="G55" s="208"/>
-      <c r="H55" s="134"/>
-      <c r="I55" s="134"/>
-      <c r="J55" s="134"/>
-      <c r="K55" s="134"/>
-      <c r="L55" s="134"/>
-      <c r="M55" s="134"/>
-      <c r="N55" s="134"/>
-      <c r="O55" s="134"/>
-      <c r="P55" s="134"/>
-      <c r="Q55" s="134"/>
-      <c r="R55" s="134"/>
-      <c r="S55" s="134"/>
-      <c r="T55" s="134"/>
-      <c r="U55" s="134"/>
-      <c r="V55" s="134"/>
-      <c r="W55" s="134"/>
-      <c r="X55" s="134"/>
-      <c r="Y55" s="134"/>
+      <c r="D55" s="200"/>
+      <c r="E55" s="200"/>
+      <c r="F55" s="200"/>
+      <c r="G55" s="201"/>
+      <c r="H55" s="127"/>
+      <c r="I55" s="127"/>
+      <c r="J55" s="127"/>
+      <c r="K55" s="127"/>
+      <c r="L55" s="127"/>
+      <c r="M55" s="127"/>
+      <c r="N55" s="127"/>
+      <c r="O55" s="127"/>
+      <c r="P55" s="127"/>
+      <c r="Q55" s="127"/>
+      <c r="R55" s="127"/>
+      <c r="S55" s="127"/>
+      <c r="T55" s="127"/>
+      <c r="U55" s="127"/>
+      <c r="V55" s="127"/>
+      <c r="W55" s="127"/>
+      <c r="X55" s="127"/>
+      <c r="Y55" s="127"/>
     </row>
     <row r="56" ht="19.5" customHeight="1">
-      <c r="B56" s="209" t="s">
+      <c r="B56" s="202" t="s">
         <v>161</v>
       </c>
-      <c r="C56" s="210"/>
-      <c r="D56" s="210"/>
-      <c r="E56" s="210"/>
-      <c r="F56" s="210"/>
-      <c r="G56" s="211"/>
-      <c r="H56" s="134"/>
-      <c r="I56" s="134"/>
-      <c r="J56" s="134"/>
-      <c r="K56" s="134"/>
-      <c r="L56" s="134"/>
-      <c r="M56" s="134"/>
-      <c r="N56" s="134"/>
-      <c r="O56" s="134"/>
-      <c r="P56" s="134"/>
-      <c r="Q56" s="134"/>
-      <c r="R56" s="134"/>
-      <c r="S56" s="134"/>
-      <c r="T56" s="134"/>
-      <c r="U56" s="134"/>
-      <c r="V56" s="134"/>
-      <c r="W56" s="134"/>
-      <c r="X56" s="134"/>
-      <c r="Y56" s="134"/>
+      <c r="C56" s="203"/>
+      <c r="D56" s="203"/>
+      <c r="E56" s="203"/>
+      <c r="F56" s="203"/>
+      <c r="G56" s="52"/>
+      <c r="H56" s="127"/>
+      <c r="I56" s="127"/>
+      <c r="J56" s="127"/>
+      <c r="K56" s="127"/>
+      <c r="L56" s="127"/>
+      <c r="M56" s="127"/>
+      <c r="N56" s="127"/>
+      <c r="O56" s="127"/>
+      <c r="P56" s="127"/>
+      <c r="Q56" s="127"/>
+      <c r="R56" s="127"/>
+      <c r="S56" s="127"/>
+      <c r="T56" s="127"/>
+      <c r="U56" s="127"/>
+      <c r="V56" s="127"/>
+      <c r="W56" s="127"/>
+      <c r="X56" s="127"/>
+      <c r="Y56" s="127"/>
     </row>
     <row r="57" ht="16.5" customHeight="1">
-      <c r="B57" s="212" t="s">
+      <c r="B57" s="204" t="s">
         <v>162</v>
       </c>
-      <c r="C57" s="213"/>
-      <c r="D57" s="213"/>
-      <c r="E57" s="213"/>
-      <c r="F57" s="213"/>
-      <c r="G57" s="214"/>
-      <c r="H57" s="215"/>
-      <c r="I57" s="215"/>
-      <c r="J57" s="215"/>
-      <c r="K57" s="215"/>
-      <c r="L57" s="215"/>
-      <c r="M57" s="215"/>
-      <c r="N57" s="215"/>
-      <c r="O57" s="215"/>
-      <c r="P57" s="215"/>
-      <c r="Q57" s="215"/>
-      <c r="R57" s="215"/>
-      <c r="S57" s="215"/>
-      <c r="T57" s="215"/>
-      <c r="U57" s="215"/>
-      <c r="V57" s="215"/>
-      <c r="W57" s="215"/>
-      <c r="X57" s="215"/>
-      <c r="Y57" s="215"/>
+      <c r="C57" s="205"/>
+      <c r="D57" s="205"/>
+      <c r="E57" s="205"/>
+      <c r="F57" s="205"/>
+      <c r="G57" s="206"/>
+      <c r="H57" s="207"/>
+      <c r="I57" s="207"/>
+      <c r="J57" s="207"/>
+      <c r="K57" s="207"/>
+      <c r="L57" s="207"/>
+      <c r="M57" s="207"/>
+      <c r="N57" s="207"/>
+      <c r="O57" s="207"/>
+      <c r="P57" s="207"/>
+      <c r="Q57" s="207"/>
+      <c r="R57" s="207"/>
+      <c r="S57" s="207"/>
+      <c r="T57" s="207"/>
+      <c r="U57" s="207"/>
+      <c r="V57" s="207"/>
+      <c r="W57" s="207"/>
+      <c r="X57" s="207"/>
+      <c r="Y57" s="207"/>
     </row>
     <row r="58" ht="16.5" customHeight="1">
-      <c r="B58" s="216" t="s">
+      <c r="B58" s="208" t="s">
         <v>163</v>
       </c>
-      <c r="C58" s="215"/>
-      <c r="D58" s="215"/>
-      <c r="E58" s="215"/>
-      <c r="F58" s="215"/>
-      <c r="G58" s="217"/>
-      <c r="H58" s="215"/>
-      <c r="I58" s="215"/>
-      <c r="J58" s="215"/>
-      <c r="K58" s="215"/>
-      <c r="L58" s="215"/>
-      <c r="M58" s="215"/>
-      <c r="N58" s="215"/>
-      <c r="O58" s="215"/>
-      <c r="P58" s="215"/>
-      <c r="Q58" s="215"/>
-      <c r="R58" s="215"/>
-      <c r="S58" s="215"/>
-      <c r="T58" s="215"/>
-      <c r="U58" s="215"/>
-      <c r="V58" s="215"/>
-      <c r="W58" s="215"/>
-      <c r="X58" s="215"/>
-      <c r="Y58" s="215"/>
+      <c r="C58" s="207"/>
+      <c r="D58" s="207"/>
+      <c r="E58" s="207"/>
+      <c r="F58" s="207"/>
+      <c r="G58" s="209"/>
+      <c r="H58" s="207"/>
+      <c r="I58" s="207"/>
+      <c r="J58" s="207"/>
+      <c r="K58" s="207"/>
+      <c r="L58" s="207"/>
+      <c r="M58" s="207"/>
+      <c r="N58" s="207"/>
+      <c r="O58" s="207"/>
+      <c r="P58" s="207"/>
+      <c r="Q58" s="207"/>
+      <c r="R58" s="207"/>
+      <c r="S58" s="207"/>
+      <c r="T58" s="207"/>
+      <c r="U58" s="207"/>
+      <c r="V58" s="207"/>
+      <c r="W58" s="207"/>
+      <c r="X58" s="207"/>
+      <c r="Y58" s="207"/>
     </row>
     <row r="59" ht="16.5" customHeight="1">
-      <c r="B59" s="216" t="s">
+      <c r="B59" s="208" t="s">
         <v>164</v>
       </c>
-      <c r="C59" s="215"/>
-      <c r="D59" s="215"/>
-      <c r="E59" s="215"/>
-      <c r="F59" s="215"/>
-      <c r="G59" s="217"/>
-      <c r="H59" s="215"/>
-      <c r="I59" s="215"/>
-      <c r="J59" s="215"/>
-      <c r="K59" s="215"/>
-      <c r="L59" s="215"/>
-      <c r="M59" s="215"/>
-      <c r="N59" s="215"/>
-      <c r="O59" s="215"/>
-      <c r="P59" s="215"/>
-      <c r="Q59" s="215"/>
-      <c r="R59" s="215"/>
-      <c r="S59" s="215"/>
-      <c r="T59" s="215"/>
-      <c r="U59" s="215"/>
-      <c r="V59" s="215"/>
-      <c r="W59" s="215"/>
-      <c r="X59" s="215"/>
-      <c r="Y59" s="215"/>
+      <c r="C59" s="207"/>
+      <c r="D59" s="207"/>
+      <c r="E59" s="207"/>
+      <c r="F59" s="207"/>
+      <c r="G59" s="209"/>
+      <c r="H59" s="207"/>
+      <c r="I59" s="207"/>
+      <c r="J59" s="207"/>
+      <c r="K59" s="207"/>
+      <c r="L59" s="207"/>
+      <c r="M59" s="207"/>
+      <c r="N59" s="207"/>
+      <c r="O59" s="207"/>
+      <c r="P59" s="207"/>
+      <c r="Q59" s="207"/>
+      <c r="R59" s="207"/>
+      <c r="S59" s="207"/>
+      <c r="T59" s="207"/>
+      <c r="U59" s="207"/>
+      <c r="V59" s="207"/>
+      <c r="W59" s="207"/>
+      <c r="X59" s="207"/>
+      <c r="Y59" s="207"/>
     </row>
     <row r="60" ht="16.5" customHeight="1">
-      <c r="B60" s="216" t="s">
+      <c r="B60" s="208" t="s">
         <v>165</v>
       </c>
-      <c r="C60" s="215"/>
-      <c r="D60" s="215"/>
-      <c r="E60" s="215"/>
-      <c r="F60" s="215"/>
-      <c r="G60" s="217"/>
-      <c r="H60" s="215"/>
-      <c r="I60" s="215"/>
-      <c r="J60" s="215"/>
-      <c r="K60" s="215"/>
-      <c r="L60" s="215"/>
-      <c r="M60" s="215"/>
-      <c r="N60" s="215"/>
-      <c r="O60" s="215"/>
-      <c r="P60" s="215"/>
-      <c r="Q60" s="215"/>
-      <c r="R60" s="215"/>
-      <c r="S60" s="215"/>
-      <c r="T60" s="215"/>
-      <c r="U60" s="215"/>
-      <c r="V60" s="215"/>
-      <c r="W60" s="215"/>
-      <c r="X60" s="215"/>
-      <c r="Y60" s="215"/>
+      <c r="C60" s="207"/>
+      <c r="D60" s="207"/>
+      <c r="E60" s="207"/>
+      <c r="F60" s="207"/>
+      <c r="G60" s="209"/>
+      <c r="H60" s="207"/>
+      <c r="I60" s="207"/>
+      <c r="J60" s="207"/>
+      <c r="K60" s="207"/>
+      <c r="L60" s="207"/>
+      <c r="M60" s="207"/>
+      <c r="N60" s="207"/>
+      <c r="O60" s="207"/>
+      <c r="P60" s="207"/>
+      <c r="Q60" s="207"/>
+      <c r="R60" s="207"/>
+      <c r="S60" s="207"/>
+      <c r="T60" s="207"/>
+      <c r="U60" s="207"/>
+      <c r="V60" s="207"/>
+      <c r="W60" s="207"/>
+      <c r="X60" s="207"/>
+      <c r="Y60" s="207"/>
     </row>
     <row r="61" ht="79.5" customHeight="1">
-      <c r="B61" s="218" t="s">
+      <c r="B61" s="210" t="s">
         <v>77</v>
       </c>
-      <c r="C61" s="219" t="s">
+      <c r="C61" s="211" t="s">
         <v>80</v>
       </c>
-      <c r="D61" s="220" t="s">
+      <c r="D61" s="212" t="s">
         <v>84</v>
       </c>
-      <c r="E61" s="221" t="s">
+      <c r="E61" s="213" t="s">
         <v>166</v>
       </c>
-      <c r="F61" s="220" t="s">
+      <c r="F61" s="212" t="s">
         <v>167</v>
       </c>
-      <c r="G61" s="222" t="s">
+      <c r="G61" s="214" t="s">
         <v>168</v>
       </c>
-      <c r="H61" s="84"/>
-      <c r="I61" s="84"/>
-      <c r="J61" s="84"/>
-      <c r="K61" s="84"/>
-      <c r="L61" s="84"/>
-      <c r="M61" s="84"/>
-      <c r="N61" s="84"/>
-      <c r="O61" s="84"/>
-      <c r="P61" s="84"/>
-      <c r="Q61" s="84"/>
-      <c r="R61" s="84"/>
-      <c r="S61" s="84"/>
-      <c r="T61" s="84"/>
-      <c r="U61" s="84"/>
-      <c r="V61" s="84"/>
-      <c r="W61" s="84"/>
-      <c r="X61" s="84"/>
-      <c r="Y61" s="84"/>
-      <c r="Z61" s="84"/>
+      <c r="H61" s="78"/>
+      <c r="I61" s="78"/>
+      <c r="J61" s="78"/>
+      <c r="K61" s="78"/>
+      <c r="L61" s="78"/>
+      <c r="M61" s="78"/>
+      <c r="N61" s="78"/>
+      <c r="O61" s="78"/>
+      <c r="P61" s="78"/>
+      <c r="Q61" s="78"/>
+      <c r="R61" s="78"/>
+      <c r="S61" s="78"/>
+      <c r="T61" s="78"/>
+      <c r="U61" s="78"/>
+      <c r="V61" s="78"/>
+      <c r="W61" s="78"/>
+      <c r="X61" s="78"/>
+      <c r="Y61" s="78"/>
+      <c r="Z61" s="78"/>
     </row>
     <row r="62" ht="32.25" customHeight="1">
-      <c r="B62" s="223" t="s">
+      <c r="B62" s="215" t="s">
         <v>166</v>
       </c>
-      <c r="C62" s="224" t="s">
+      <c r="C62" s="216" t="s">
         <v>169</v>
       </c>
-      <c r="D62" s="225"/>
-      <c r="E62" s="226"/>
-      <c r="F62" s="225"/>
-      <c r="G62" s="227"/>
-      <c r="H62" s="84"/>
-      <c r="I62" s="84"/>
-      <c r="J62" s="84"/>
-      <c r="K62" s="84"/>
-      <c r="L62" s="84"/>
-      <c r="M62" s="84"/>
-      <c r="N62" s="84"/>
-      <c r="O62" s="84"/>
-      <c r="P62" s="84"/>
-      <c r="Q62" s="84"/>
-      <c r="R62" s="84"/>
-      <c r="S62" s="84"/>
-      <c r="T62" s="84"/>
-      <c r="U62" s="84"/>
-      <c r="V62" s="84"/>
-      <c r="W62" s="84"/>
-      <c r="X62" s="84"/>
-      <c r="Y62" s="84"/>
-      <c r="Z62" s="84"/>
+      <c r="D62" s="217"/>
+      <c r="E62" s="218"/>
+      <c r="F62" s="217"/>
+      <c r="G62" s="219"/>
+      <c r="H62" s="78"/>
+      <c r="I62" s="78"/>
+      <c r="J62" s="78"/>
+      <c r="K62" s="78"/>
+      <c r="L62" s="78"/>
+      <c r="M62" s="78"/>
+      <c r="N62" s="78"/>
+      <c r="O62" s="78"/>
+      <c r="P62" s="78"/>
+      <c r="Q62" s="78"/>
+      <c r="R62" s="78"/>
+      <c r="S62" s="78"/>
+      <c r="T62" s="78"/>
+      <c r="U62" s="78"/>
+      <c r="V62" s="78"/>
+      <c r="W62" s="78"/>
+      <c r="X62" s="78"/>
+      <c r="Y62" s="78"/>
+      <c r="Z62" s="78"/>
     </row>
     <row r="63" ht="17.25" customHeight="1">
-      <c r="B63" s="161"/>
-      <c r="C63" s="161"/>
-      <c r="D63" s="161"/>
-      <c r="E63" s="161"/>
-      <c r="F63" s="161"/>
-      <c r="G63" s="161"/>
-      <c r="H63" s="84"/>
-      <c r="I63" s="84"/>
-      <c r="J63" s="84"/>
-      <c r="K63" s="84"/>
-      <c r="L63" s="84"/>
-      <c r="M63" s="84"/>
-      <c r="N63" s="84"/>
-      <c r="O63" s="84"/>
-      <c r="P63" s="84"/>
-      <c r="Q63" s="84"/>
-      <c r="R63" s="84"/>
-      <c r="S63" s="84"/>
-      <c r="T63" s="84"/>
-      <c r="U63" s="84"/>
-      <c r="V63" s="84"/>
-      <c r="W63" s="84"/>
-      <c r="X63" s="84"/>
-      <c r="Y63" s="84"/>
-      <c r="Z63" s="84"/>
+      <c r="B63" s="154"/>
+      <c r="C63" s="154"/>
+      <c r="D63" s="154"/>
+      <c r="E63" s="154"/>
+      <c r="F63" s="154"/>
+      <c r="G63" s="154"/>
+      <c r="H63" s="78"/>
+      <c r="I63" s="78"/>
+      <c r="J63" s="78"/>
+      <c r="K63" s="78"/>
+      <c r="L63" s="78"/>
+      <c r="M63" s="78"/>
+      <c r="N63" s="78"/>
+      <c r="O63" s="78"/>
+      <c r="P63" s="78"/>
+      <c r="Q63" s="78"/>
+      <c r="R63" s="78"/>
+      <c r="S63" s="78"/>
+      <c r="T63" s="78"/>
+      <c r="U63" s="78"/>
+      <c r="V63" s="78"/>
+      <c r="W63" s="78"/>
+      <c r="X63" s="78"/>
+      <c r="Y63" s="78"/>
+      <c r="Z63" s="78"/>
     </row>
     <row r="64" ht="15" customHeight="1">
-      <c r="C64" s="228"/>
-      <c r="D64" s="229" t="s">
+      <c r="C64" s="220"/>
+      <c r="D64" s="221" t="s">
         <v>170</v>
       </c>
-      <c r="E64" s="228"/>
-      <c r="F64" s="228"/>
-      <c r="G64" s="228"/>
-      <c r="H64" s="84"/>
-      <c r="I64" s="84"/>
-      <c r="J64" s="84"/>
-      <c r="K64" s="84"/>
-      <c r="L64" s="84"/>
-      <c r="M64" s="84"/>
-      <c r="N64" s="84"/>
-      <c r="O64" s="84"/>
-      <c r="P64" s="84"/>
-      <c r="Q64" s="84"/>
-      <c r="R64" s="84"/>
-      <c r="S64" s="84"/>
-      <c r="T64" s="84"/>
-      <c r="U64" s="84"/>
-      <c r="V64" s="84"/>
-      <c r="W64" s="84"/>
-      <c r="X64" s="84"/>
-      <c r="Y64" s="84"/>
-      <c r="Z64" s="84"/>
+      <c r="E64" s="220"/>
+      <c r="F64" s="220"/>
+      <c r="G64" s="220"/>
+      <c r="H64" s="78"/>
+      <c r="I64" s="78"/>
+      <c r="J64" s="78"/>
+      <c r="K64" s="78"/>
+      <c r="L64" s="78"/>
+      <c r="M64" s="78"/>
+      <c r="N64" s="78"/>
+      <c r="O64" s="78"/>
+      <c r="P64" s="78"/>
+      <c r="Q64" s="78"/>
+      <c r="R64" s="78"/>
+      <c r="S64" s="78"/>
+      <c r="T64" s="78"/>
+      <c r="U64" s="78"/>
+      <c r="V64" s="78"/>
+      <c r="W64" s="78"/>
+      <c r="X64" s="78"/>
+      <c r="Y64" s="78"/>
+      <c r="Z64" s="78"/>
     </row>
     <row r="65" ht="15" customHeight="1">
-      <c r="B65" s="230"/>
-      <c r="C65" s="230"/>
-      <c r="D65" s="230"/>
-      <c r="E65" s="230"/>
-      <c r="F65" s="230"/>
-      <c r="G65" s="230"/>
-      <c r="H65" s="84"/>
-      <c r="I65" s="84"/>
-      <c r="J65" s="84"/>
-      <c r="K65" s="84"/>
-      <c r="L65" s="84"/>
-      <c r="M65" s="84"/>
-      <c r="N65" s="84"/>
-      <c r="O65" s="84"/>
-      <c r="P65" s="84"/>
-      <c r="Q65" s="84"/>
-      <c r="R65" s="84"/>
-      <c r="S65" s="84"/>
-      <c r="T65" s="84"/>
-      <c r="U65" s="84"/>
-      <c r="V65" s="84"/>
-      <c r="W65" s="84"/>
-      <c r="X65" s="84"/>
-      <c r="Y65" s="84"/>
-      <c r="Z65" s="84"/>
+      <c r="B65" s="222"/>
+      <c r="C65" s="222"/>
+      <c r="D65" s="222"/>
+      <c r="E65" s="222"/>
+      <c r="F65" s="222"/>
+      <c r="G65" s="222"/>
+      <c r="H65" s="78"/>
+      <c r="I65" s="78"/>
+      <c r="J65" s="78"/>
+      <c r="K65" s="78"/>
+      <c r="L65" s="78"/>
+      <c r="M65" s="78"/>
+      <c r="N65" s="78"/>
+      <c r="O65" s="78"/>
+      <c r="P65" s="78"/>
+      <c r="Q65" s="78"/>
+      <c r="R65" s="78"/>
+      <c r="S65" s="78"/>
+      <c r="T65" s="78"/>
+      <c r="U65" s="78"/>
+      <c r="V65" s="78"/>
+      <c r="W65" s="78"/>
+      <c r="X65" s="78"/>
+      <c r="Y65" s="78"/>
+      <c r="Z65" s="78"/>
     </row>
     <row r="66" ht="15" customHeight="1">
-      <c r="B66" s="230"/>
-      <c r="C66" s="230"/>
-      <c r="D66" s="230"/>
-      <c r="E66" s="230"/>
-      <c r="F66" s="230"/>
-      <c r="G66" s="230"/>
-      <c r="H66" s="84"/>
-      <c r="I66" s="84"/>
-      <c r="J66" s="84"/>
-      <c r="K66" s="84"/>
-      <c r="L66" s="84"/>
-      <c r="M66" s="84"/>
-      <c r="N66" s="84"/>
-      <c r="O66" s="84"/>
-      <c r="P66" s="84"/>
-      <c r="Q66" s="84"/>
-      <c r="R66" s="84"/>
-      <c r="S66" s="84"/>
-      <c r="T66" s="84"/>
-      <c r="U66" s="84"/>
-      <c r="V66" s="84"/>
-      <c r="W66" s="84"/>
-      <c r="X66" s="84"/>
-      <c r="Y66" s="84"/>
-      <c r="Z66" s="84"/>
+      <c r="B66" s="222"/>
+      <c r="C66" s="222"/>
+      <c r="D66" s="222"/>
+      <c r="E66" s="222"/>
+      <c r="F66" s="222"/>
+      <c r="G66" s="222"/>
+      <c r="H66" s="78"/>
+      <c r="I66" s="78"/>
+      <c r="J66" s="78"/>
+      <c r="K66" s="78"/>
+      <c r="L66" s="78"/>
+      <c r="M66" s="78"/>
+      <c r="N66" s="78"/>
+      <c r="O66" s="78"/>
+      <c r="P66" s="78"/>
+      <c r="Q66" s="78"/>
+      <c r="R66" s="78"/>
+      <c r="S66" s="78"/>
+      <c r="T66" s="78"/>
+      <c r="U66" s="78"/>
+      <c r="V66" s="78"/>
+      <c r="W66" s="78"/>
+      <c r="X66" s="78"/>
+      <c r="Y66" s="78"/>
+      <c r="Z66" s="78"/>
     </row>
     <row r="67" ht="15" customHeight="1">
-      <c r="B67" s="231"/>
-      <c r="C67" s="232"/>
-      <c r="D67" s="231"/>
-      <c r="F67" s="233">
+      <c r="B67" s="223"/>
+      <c r="C67" s="224"/>
+      <c r="D67" s="223"/>
+      <c r="F67" s="225">
         <v>46134</v>
       </c>
-      <c r="G67" s="84"/>
-      <c r="H67" s="84"/>
-      <c r="I67" s="84"/>
-      <c r="J67" s="84"/>
-      <c r="K67" s="84"/>
-      <c r="L67" s="84"/>
-      <c r="M67" s="84"/>
-      <c r="N67" s="84"/>
-      <c r="O67" s="84"/>
-      <c r="P67" s="84"/>
-      <c r="Q67" s="84"/>
-      <c r="R67" s="84"/>
-      <c r="S67" s="84"/>
-      <c r="T67" s="84"/>
-      <c r="U67" s="84"/>
-      <c r="V67" s="84"/>
-      <c r="W67" s="84"/>
-      <c r="X67" s="84"/>
-      <c r="Y67" s="84"/>
-      <c r="Z67" s="84"/>
+      <c r="G67" s="78"/>
+      <c r="H67" s="78"/>
+      <c r="I67" s="78"/>
+      <c r="J67" s="78"/>
+      <c r="K67" s="78"/>
+      <c r="L67" s="78"/>
+      <c r="M67" s="78"/>
+      <c r="N67" s="78"/>
+      <c r="O67" s="78"/>
+      <c r="P67" s="78"/>
+      <c r="Q67" s="78"/>
+      <c r="R67" s="78"/>
+      <c r="S67" s="78"/>
+      <c r="T67" s="78"/>
+      <c r="U67" s="78"/>
+      <c r="V67" s="78"/>
+      <c r="W67" s="78"/>
+      <c r="X67" s="78"/>
+      <c r="Y67" s="78"/>
+      <c r="Z67" s="78"/>
     </row>
     <row r="68" ht="15" customHeight="1">
-      <c r="B68" s="234" t="s">
+      <c r="B68" s="226" t="s">
         <v>89</v>
       </c>
-      <c r="C68" s="234"/>
-      <c r="D68" s="234"/>
-      <c r="F68" s="161" t="s">
+      <c r="C68" s="226"/>
+      <c r="D68" s="226"/>
+      <c r="F68" s="154" t="s">
         <v>91</v>
       </c>
-      <c r="G68" s="84"/>
-      <c r="H68" s="84"/>
-      <c r="I68" s="84"/>
-      <c r="J68" s="84"/>
-      <c r="K68" s="84"/>
-      <c r="L68" s="84"/>
-      <c r="M68" s="84"/>
-      <c r="N68" s="84"/>
-      <c r="O68" s="84"/>
-      <c r="P68" s="84"/>
-      <c r="Q68" s="84"/>
-      <c r="R68" s="84"/>
-      <c r="S68" s="84"/>
-      <c r="T68" s="84"/>
-      <c r="U68" s="84"/>
-      <c r="V68" s="84"/>
-      <c r="W68" s="84"/>
-      <c r="X68" s="84"/>
-      <c r="Y68" s="84"/>
-      <c r="Z68" s="84"/>
+      <c r="G68" s="78"/>
+      <c r="H68" s="78"/>
+      <c r="I68" s="78"/>
+      <c r="J68" s="78"/>
+      <c r="K68" s="78"/>
+      <c r="L68" s="78"/>
+      <c r="M68" s="78"/>
+      <c r="N68" s="78"/>
+      <c r="O68" s="78"/>
+      <c r="P68" s="78"/>
+      <c r="Q68" s="78"/>
+      <c r="R68" s="78"/>
+      <c r="S68" s="78"/>
+      <c r="T68" s="78"/>
+      <c r="U68" s="78"/>
+      <c r="V68" s="78"/>
+      <c r="W68" s="78"/>
+      <c r="X68" s="78"/>
+      <c r="Y68" s="78"/>
+      <c r="Z68" s="78"/>
     </row>
     <row r="69">
-      <c r="B69" s="77"/>
-      <c r="C69" s="84"/>
-      <c r="D69" s="77"/>
-      <c r="F69" s="84"/>
-      <c r="G69" s="84"/>
-      <c r="H69" s="84"/>
-      <c r="I69" s="84"/>
-      <c r="J69" s="84"/>
-      <c r="K69" s="84"/>
-      <c r="L69" s="84"/>
-      <c r="M69" s="84"/>
-      <c r="N69" s="84"/>
-      <c r="O69" s="84"/>
-      <c r="P69" s="84"/>
-      <c r="Q69" s="84"/>
-      <c r="R69" s="84"/>
-      <c r="S69" s="84"/>
-      <c r="T69" s="84"/>
-      <c r="U69" s="84"/>
-      <c r="V69" s="84"/>
-      <c r="W69" s="84"/>
-      <c r="X69" s="84"/>
-      <c r="Y69" s="84"/>
-      <c r="Z69" s="84"/>
+      <c r="B69" s="71"/>
+      <c r="C69" s="78"/>
+      <c r="D69" s="71"/>
+      <c r="F69" s="78"/>
+      <c r="G69" s="78"/>
+      <c r="H69" s="78"/>
+      <c r="I69" s="78"/>
+      <c r="J69" s="78"/>
+      <c r="K69" s="78"/>
+      <c r="L69" s="78"/>
+      <c r="M69" s="78"/>
+      <c r="N69" s="78"/>
+      <c r="O69" s="78"/>
+      <c r="P69" s="78"/>
+      <c r="Q69" s="78"/>
+      <c r="R69" s="78"/>
+      <c r="S69" s="78"/>
+      <c r="T69" s="78"/>
+      <c r="U69" s="78"/>
+      <c r="V69" s="78"/>
+      <c r="W69" s="78"/>
+      <c r="X69" s="78"/>
+      <c r="Y69" s="78"/>
+      <c r="Z69" s="78"/>
     </row>
     <row r="70" ht="15" customHeight="1">
-      <c r="B70" s="77"/>
-      <c r="C70" s="84"/>
-      <c r="D70" s="77"/>
-      <c r="F70" s="90"/>
-      <c r="G70" s="84"/>
-      <c r="H70" s="84"/>
-      <c r="I70" s="84"/>
-      <c r="J70" s="84"/>
-      <c r="K70" s="84"/>
-      <c r="L70" s="84"/>
-      <c r="M70" s="84"/>
-      <c r="N70" s="84"/>
-      <c r="O70" s="84"/>
-      <c r="P70" s="84"/>
-      <c r="Q70" s="84"/>
-      <c r="R70" s="84"/>
-      <c r="S70" s="84"/>
-      <c r="T70" s="84"/>
-      <c r="U70" s="84"/>
-      <c r="V70" s="84"/>
-      <c r="W70" s="84"/>
-      <c r="X70" s="84"/>
-      <c r="Y70" s="84"/>
-      <c r="Z70" s="84"/>
+      <c r="B70" s="71"/>
+      <c r="C70" s="78"/>
+      <c r="D70" s="71"/>
+      <c r="F70" s="84"/>
+      <c r="G70" s="78"/>
+      <c r="H70" s="78"/>
+      <c r="I70" s="78"/>
+      <c r="J70" s="78"/>
+      <c r="K70" s="78"/>
+      <c r="L70" s="78"/>
+      <c r="M70" s="78"/>
+      <c r="N70" s="78"/>
+      <c r="O70" s="78"/>
+      <c r="P70" s="78"/>
+      <c r="Q70" s="78"/>
+      <c r="R70" s="78"/>
+      <c r="S70" s="78"/>
+      <c r="T70" s="78"/>
+      <c r="U70" s="78"/>
+      <c r="V70" s="78"/>
+      <c r="W70" s="78"/>
+      <c r="X70" s="78"/>
+      <c r="Y70" s="78"/>
+      <c r="Z70" s="78"/>
     </row>
     <row r="71" ht="15" customHeight="1">
-      <c r="B71" s="231"/>
-      <c r="C71" s="232"/>
-      <c r="D71" s="231"/>
-      <c r="F71" s="235"/>
-      <c r="G71" s="232"/>
-      <c r="H71" s="84"/>
-      <c r="I71" s="84"/>
-      <c r="J71" s="84"/>
-      <c r="K71" s="84"/>
-      <c r="L71" s="84"/>
-      <c r="M71" s="84"/>
-      <c r="N71" s="84"/>
-      <c r="O71" s="84"/>
-      <c r="P71" s="84"/>
-      <c r="Q71" s="84"/>
-      <c r="R71" s="84"/>
-      <c r="S71" s="84"/>
-      <c r="T71" s="84"/>
-      <c r="U71" s="84"/>
-      <c r="V71" s="84"/>
-      <c r="W71" s="84"/>
-      <c r="X71" s="84"/>
-      <c r="Y71" s="84"/>
-      <c r="Z71" s="84"/>
+      <c r="B71" s="223"/>
+      <c r="C71" s="224"/>
+      <c r="D71" s="223"/>
+      <c r="F71" s="227"/>
+      <c r="G71" s="224"/>
+      <c r="H71" s="78"/>
+      <c r="I71" s="78"/>
+      <c r="J71" s="78"/>
+      <c r="K71" s="78"/>
+      <c r="L71" s="78"/>
+      <c r="M71" s="78"/>
+      <c r="N71" s="78"/>
+      <c r="O71" s="78"/>
+      <c r="P71" s="78"/>
+      <c r="Q71" s="78"/>
+      <c r="R71" s="78"/>
+      <c r="S71" s="78"/>
+      <c r="T71" s="78"/>
+      <c r="U71" s="78"/>
+      <c r="V71" s="78"/>
+      <c r="W71" s="78"/>
+      <c r="X71" s="78"/>
+      <c r="Y71" s="78"/>
+      <c r="Z71" s="78"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="B72" s="77"/>
-      <c r="C72" s="236" t="s">
+      <c r="B72" s="71"/>
+      <c r="C72" s="228" t="s">
         <v>93</v>
       </c>
-      <c r="D72" s="77"/>
-      <c r="F72" s="234" t="s">
+      <c r="D72" s="71"/>
+      <c r="F72" s="226" t="s">
         <v>171</v>
       </c>
-      <c r="G72" s="234"/>
-      <c r="H72" s="84"/>
-      <c r="I72" s="84"/>
-      <c r="J72" s="84"/>
-      <c r="K72" s="84"/>
-      <c r="L72" s="84"/>
-      <c r="M72" s="84"/>
-      <c r="N72" s="84"/>
-      <c r="O72" s="84"/>
-      <c r="P72" s="84"/>
-      <c r="Q72" s="84"/>
-      <c r="R72" s="84"/>
-      <c r="S72" s="84"/>
-      <c r="T72" s="84"/>
-      <c r="U72" s="84"/>
-      <c r="V72" s="84"/>
-      <c r="W72" s="84"/>
-      <c r="X72" s="84"/>
-      <c r="Y72" s="84"/>
-      <c r="Z72" s="84"/>
+      <c r="G72" s="226"/>
+      <c r="H72" s="78"/>
+      <c r="I72" s="78"/>
+      <c r="J72" s="78"/>
+      <c r="K72" s="78"/>
+      <c r="L72" s="78"/>
+      <c r="M72" s="78"/>
+      <c r="N72" s="78"/>
+      <c r="O72" s="78"/>
+      <c r="P72" s="78"/>
+      <c r="Q72" s="78"/>
+      <c r="R72" s="78"/>
+      <c r="S72" s="78"/>
+      <c r="T72" s="78"/>
+      <c r="U72" s="78"/>
+      <c r="V72" s="78"/>
+      <c r="W72" s="78"/>
+      <c r="X72" s="78"/>
+      <c r="Y72" s="78"/>
+      <c r="Z72" s="78"/>
     </row>
     <row r="73" ht="18" customHeight="1">
-      <c r="B73" s="237" t="s">
+      <c r="B73" s="229" t="s">
         <v>172</v>
       </c>
-      <c r="C73" s="238"/>
-      <c r="D73" s="238"/>
-      <c r="E73" s="238"/>
-      <c r="F73" s="238"/>
-      <c r="G73" s="238"/>
-      <c r="H73" s="84"/>
-      <c r="I73" s="84"/>
-      <c r="J73" s="84"/>
-      <c r="K73" s="84"/>
-      <c r="L73" s="84"/>
-      <c r="M73" s="84"/>
-      <c r="N73" s="84"/>
-      <c r="O73" s="84"/>
-      <c r="P73" s="84"/>
-      <c r="Q73" s="84"/>
-      <c r="R73" s="84"/>
-      <c r="S73" s="84"/>
-      <c r="T73" s="84"/>
-      <c r="U73" s="84"/>
-      <c r="V73" s="84"/>
-      <c r="W73" s="84"/>
-      <c r="X73" s="84"/>
-      <c r="Y73" s="84"/>
-      <c r="Z73" s="84"/>
+      <c r="C73" s="229"/>
+      <c r="D73" s="229"/>
+      <c r="E73" s="229"/>
+      <c r="F73" s="229"/>
+      <c r="G73" s="229"/>
+      <c r="H73" s="78"/>
+      <c r="I73" s="78"/>
+      <c r="J73" s="78"/>
+      <c r="K73" s="78"/>
+      <c r="L73" s="78"/>
+      <c r="M73" s="78"/>
+      <c r="N73" s="78"/>
+      <c r="O73" s="78"/>
+      <c r="P73" s="78"/>
+      <c r="Q73" s="78"/>
+      <c r="R73" s="78"/>
+      <c r="S73" s="78"/>
+      <c r="T73" s="78"/>
+      <c r="U73" s="78"/>
+      <c r="V73" s="78"/>
+      <c r="W73" s="78"/>
+      <c r="X73" s="78"/>
+      <c r="Y73" s="78"/>
+      <c r="Z73" s="78"/>
     </row>
     <row r="74" ht="15">
-      <c r="B74" s="238"/>
-      <c r="C74" s="238"/>
-      <c r="D74" s="238"/>
-      <c r="E74" s="238"/>
-      <c r="F74" s="238"/>
-      <c r="G74" s="238"/>
-      <c r="H74" s="84"/>
-      <c r="I74" s="84"/>
-      <c r="J74" s="84"/>
-      <c r="K74" s="84"/>
-      <c r="L74" s="84"/>
-      <c r="M74" s="84"/>
-      <c r="N74" s="84"/>
-      <c r="O74" s="84"/>
-      <c r="P74" s="84"/>
-      <c r="Q74" s="84"/>
-      <c r="R74" s="84"/>
-      <c r="S74" s="84"/>
-      <c r="T74" s="84"/>
-      <c r="U74" s="84"/>
-      <c r="V74" s="84"/>
-      <c r="W74" s="84"/>
-      <c r="X74" s="84"/>
-      <c r="Y74" s="84"/>
-      <c r="Z74" s="84"/>
+      <c r="B74" s="229"/>
+      <c r="C74" s="229"/>
+      <c r="D74" s="229"/>
+      <c r="E74" s="229"/>
+      <c r="F74" s="229"/>
+      <c r="G74" s="229"/>
+      <c r="H74" s="78"/>
+      <c r="I74" s="78"/>
+      <c r="J74" s="78"/>
+      <c r="K74" s="78"/>
+      <c r="L74" s="78"/>
+      <c r="M74" s="78"/>
+      <c r="N74" s="78"/>
+      <c r="O74" s="78"/>
+      <c r="P74" s="78"/>
+      <c r="Q74" s="78"/>
+      <c r="R74" s="78"/>
+      <c r="S74" s="78"/>
+      <c r="T74" s="78"/>
+      <c r="U74" s="78"/>
+      <c r="V74" s="78"/>
+      <c r="W74" s="78"/>
+      <c r="X74" s="78"/>
+      <c r="Y74" s="78"/>
+      <c r="Z74" s="78"/>
     </row>
     <row r="75" ht="24" customHeight="1">
-      <c r="B75" s="239" t="s">
+      <c r="B75" s="230" t="s">
         <v>173</v>
       </c>
-      <c r="C75" s="240"/>
-      <c r="D75" s="240"/>
-      <c r="E75" s="240"/>
-      <c r="F75" s="240"/>
-      <c r="G75" s="241"/>
-      <c r="H75" s="79"/>
-      <c r="I75" s="77"/>
-      <c r="J75" s="77"/>
-      <c r="K75" s="77"/>
-      <c r="L75" s="77"/>
-      <c r="M75" s="77"/>
-      <c r="N75" s="77"/>
-      <c r="O75" s="77"/>
-      <c r="P75" s="77"/>
-      <c r="Q75" s="77"/>
-      <c r="R75" s="77"/>
-      <c r="S75" s="77"/>
-      <c r="T75" s="77"/>
-      <c r="U75" s="77"/>
-      <c r="V75" s="77"/>
-      <c r="W75" s="77"/>
-      <c r="X75" s="77"/>
-      <c r="Y75" s="77"/>
-      <c r="Z75" s="77"/>
+      <c r="C75" s="231"/>
+      <c r="D75" s="231"/>
+      <c r="E75" s="231"/>
+      <c r="F75" s="231"/>
+      <c r="G75" s="232"/>
+      <c r="H75" s="73"/>
+      <c r="I75" s="71"/>
+      <c r="J75" s="71"/>
+      <c r="K75" s="71"/>
+      <c r="L75" s="71"/>
+      <c r="M75" s="71"/>
+      <c r="N75" s="71"/>
+      <c r="O75" s="71"/>
+      <c r="P75" s="71"/>
+      <c r="Q75" s="71"/>
+      <c r="R75" s="71"/>
+      <c r="S75" s="71"/>
+      <c r="T75" s="71"/>
+      <c r="U75" s="71"/>
+      <c r="V75" s="71"/>
+      <c r="W75" s="71"/>
+      <c r="X75" s="71"/>
+      <c r="Y75" s="71"/>
+      <c r="Z75" s="71"/>
     </row>
     <row r="76" ht="13.5" customHeight="1">
-      <c r="B76" s="242" t="s">
+      <c r="B76" s="233" t="s">
         <v>174</v>
       </c>
-      <c r="C76" s="243"/>
-      <c r="D76" s="243"/>
-      <c r="E76" s="243"/>
-      <c r="F76" s="243"/>
-      <c r="G76" s="244"/>
-      <c r="H76" s="79"/>
-      <c r="I76" s="245"/>
-      <c r="J76" s="77"/>
-      <c r="K76" s="77"/>
-      <c r="L76" s="77"/>
-      <c r="M76" s="77"/>
-      <c r="N76" s="77"/>
-      <c r="O76" s="77"/>
-      <c r="P76" s="77"/>
-      <c r="Q76" s="77"/>
-      <c r="R76" s="77"/>
-      <c r="S76" s="77"/>
-      <c r="T76" s="77"/>
-      <c r="U76" s="77"/>
-      <c r="V76" s="77"/>
-      <c r="W76" s="77"/>
-      <c r="X76" s="77"/>
-      <c r="Y76" s="77"/>
-      <c r="Z76" s="77"/>
-    </row>
-    <row r="77" s="79" customFormat="1" ht="156" customHeight="1">
-      <c r="B77" s="246"/>
-      <c r="C77" s="106"/>
-      <c r="D77" s="106"/>
-      <c r="E77" s="106"/>
-      <c r="F77" s="106"/>
-      <c r="G77" s="108"/>
+      <c r="C76" s="234"/>
+      <c r="D76" s="234"/>
+      <c r="E76" s="234"/>
+      <c r="F76" s="234"/>
+      <c r="G76" s="235"/>
+      <c r="H76" s="73"/>
+      <c r="I76" s="236"/>
+      <c r="J76" s="71"/>
+      <c r="K76" s="71"/>
+      <c r="L76" s="71"/>
+      <c r="M76" s="71"/>
+      <c r="N76" s="71"/>
+      <c r="O76" s="71"/>
+      <c r="P76" s="71"/>
+      <c r="Q76" s="71"/>
+      <c r="R76" s="71"/>
+      <c r="S76" s="71"/>
+      <c r="T76" s="71"/>
+      <c r="U76" s="71"/>
+      <c r="V76" s="71"/>
+      <c r="W76" s="71"/>
+      <c r="X76" s="71"/>
+      <c r="Y76" s="71"/>
+      <c r="Z76" s="71"/>
+    </row>
+    <row r="77" s="73" customFormat="1" ht="156" customHeight="1">
+      <c r="B77" s="237"/>
+      <c r="C77" s="100"/>
+      <c r="D77" s="100"/>
+      <c r="E77" s="100"/>
+      <c r="F77" s="100"/>
+      <c r="G77" s="102"/>
     </row>
     <row r="78">
-      <c r="H78" s="79"/>
-      <c r="I78" s="77"/>
-      <c r="J78" s="77"/>
-      <c r="K78" s="77"/>
-      <c r="L78" s="77"/>
-      <c r="M78" s="77"/>
-      <c r="N78" s="77"/>
-      <c r="O78" s="77"/>
-      <c r="P78" s="77"/>
-      <c r="Q78" s="77"/>
-      <c r="R78" s="77"/>
-      <c r="S78" s="77"/>
-      <c r="T78" s="77"/>
-      <c r="U78" s="77"/>
-      <c r="V78" s="77"/>
-      <c r="W78" s="77"/>
-      <c r="X78" s="77"/>
-      <c r="Y78" s="77"/>
-      <c r="Z78" s="77"/>
+      <c r="H78" s="73"/>
+      <c r="I78" s="71"/>
+      <c r="J78" s="71"/>
+      <c r="K78" s="71"/>
+      <c r="L78" s="71"/>
+      <c r="M78" s="71"/>
+      <c r="N78" s="71"/>
+      <c r="O78" s="71"/>
+      <c r="P78" s="71"/>
+      <c r="Q78" s="71"/>
+      <c r="R78" s="71"/>
+      <c r="S78" s="71"/>
+      <c r="T78" s="71"/>
+      <c r="U78" s="71"/>
+      <c r="V78" s="71"/>
+      <c r="W78" s="71"/>
+      <c r="X78" s="71"/>
+      <c r="Y78" s="71"/>
+      <c r="Z78" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -6980,572 +6593,572 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.5">
-      <c r="A1" s="247" t="s">
+      <c r="A1" s="238" t="s">
         <v>175</v>
       </c>
-      <c r="B1" s="247"/>
-      <c r="C1" s="247"/>
-      <c r="D1" s="247"/>
-      <c r="E1" s="247"/>
-      <c r="F1" s="247"/>
-      <c r="G1" s="247"/>
-      <c r="H1" s="247"/>
-      <c r="I1" s="247"/>
-      <c r="J1" s="247"/>
-      <c r="K1" s="247"/>
-      <c r="L1" s="247"/>
-      <c r="M1" s="247"/>
-      <c r="N1" s="247"/>
-      <c r="O1" s="247"/>
-      <c r="P1" s="247"/>
-      <c r="Q1" s="247"/>
-      <c r="R1" s="247"/>
-      <c r="S1" s="247"/>
-      <c r="T1" s="247"/>
-      <c r="U1" s="247" t="s">
+      <c r="B1" s="238"/>
+      <c r="C1" s="238"/>
+      <c r="D1" s="238"/>
+      <c r="E1" s="238"/>
+      <c r="F1" s="238"/>
+      <c r="G1" s="238"/>
+      <c r="H1" s="238"/>
+      <c r="I1" s="238"/>
+      <c r="J1" s="238"/>
+      <c r="K1" s="238"/>
+      <c r="L1" s="238"/>
+      <c r="M1" s="238"/>
+      <c r="N1" s="238"/>
+      <c r="O1" s="238"/>
+      <c r="P1" s="238"/>
+      <c r="Q1" s="238"/>
+      <c r="R1" s="238"/>
+      <c r="S1" s="238"/>
+      <c r="T1" s="238"/>
+      <c r="U1" s="238" t="s">
         <v>176</v>
       </c>
-      <c r="V1" s="247"/>
-      <c r="W1" s="247"/>
-      <c r="X1" s="247"/>
+      <c r="V1" s="238"/>
+      <c r="W1" s="238"/>
+      <c r="X1" s="238"/>
     </row>
     <row r="2" ht="33" customHeight="1">
-      <c r="A2" s="247"/>
-      <c r="B2" s="247"/>
-      <c r="C2" s="247"/>
-      <c r="D2" s="247"/>
-      <c r="E2" s="247"/>
-      <c r="F2" s="247"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="247"/>
-      <c r="I2" s="247"/>
-      <c r="J2" s="247"/>
-      <c r="K2" s="247"/>
-      <c r="L2" s="247"/>
-      <c r="M2" s="247"/>
-      <c r="N2" s="247"/>
-      <c r="O2" s="247"/>
-      <c r="P2" s="247"/>
-      <c r="Q2" s="247"/>
-      <c r="R2" s="247"/>
-      <c r="S2" s="247"/>
-      <c r="T2" s="247"/>
-      <c r="U2" s="248" t="s">
+      <c r="A2" s="238"/>
+      <c r="B2" s="238"/>
+      <c r="C2" s="238"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="238"/>
+      <c r="G2" s="238"/>
+      <c r="H2" s="238"/>
+      <c r="I2" s="238"/>
+      <c r="J2" s="238"/>
+      <c r="K2" s="238"/>
+      <c r="L2" s="238"/>
+      <c r="M2" s="238"/>
+      <c r="N2" s="238"/>
+      <c r="O2" s="238"/>
+      <c r="P2" s="238"/>
+      <c r="Q2" s="238"/>
+      <c r="R2" s="238"/>
+      <c r="S2" s="238"/>
+      <c r="T2" s="238"/>
+      <c r="U2" s="239" t="s">
         <v>177</v>
       </c>
-      <c r="V2" s="248"/>
-      <c r="W2" s="248"/>
-      <c r="X2" s="248"/>
+      <c r="V2" s="239"/>
+      <c r="W2" s="239"/>
+      <c r="X2" s="239"/>
     </row>
     <row r="3" ht="33" customHeight="1">
-      <c r="U3" s="249"/>
-      <c r="V3" s="249"/>
-      <c r="W3" s="249"/>
-      <c r="X3" s="249"/>
-    </row>
-    <row r="4" s="250" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="251" t="s">
+      <c r="U3" s="240"/>
+      <c r="V3" s="240"/>
+      <c r="W3" s="240"/>
+      <c r="X3" s="240"/>
+    </row>
+    <row r="4" s="241" customFormat="1" ht="18" customHeight="1">
+      <c r="A4" s="242" t="s">
         <v>178</v>
       </c>
-      <c r="B4" s="252"/>
-      <c r="C4" s="252"/>
-      <c r="D4" s="252"/>
-      <c r="E4" s="252"/>
-      <c r="F4" s="252"/>
-      <c r="G4" s="252"/>
-      <c r="H4" s="252"/>
-      <c r="I4" s="252"/>
-      <c r="J4" s="252"/>
-      <c r="K4" s="252"/>
-      <c r="L4" s="252"/>
-      <c r="M4" s="253"/>
-      <c r="N4" s="251" t="s">
+      <c r="B4" s="243"/>
+      <c r="C4" s="243"/>
+      <c r="D4" s="243"/>
+      <c r="E4" s="243"/>
+      <c r="F4" s="243"/>
+      <c r="G4" s="243"/>
+      <c r="H4" s="243"/>
+      <c r="I4" s="243"/>
+      <c r="J4" s="243"/>
+      <c r="K4" s="243"/>
+      <c r="L4" s="243"/>
+      <c r="M4" s="244"/>
+      <c r="N4" s="242" t="s">
         <v>179</v>
       </c>
-      <c r="O4" s="252"/>
-      <c r="P4" s="252"/>
-      <c r="Q4" s="252"/>
-      <c r="R4" s="252"/>
-      <c r="S4" s="252"/>
-      <c r="T4" s="252"/>
-      <c r="U4" s="252"/>
-      <c r="V4" s="252"/>
-      <c r="W4" s="252"/>
-      <c r="X4" s="253"/>
+      <c r="O4" s="243"/>
+      <c r="P4" s="243"/>
+      <c r="Q4" s="243"/>
+      <c r="R4" s="243"/>
+      <c r="S4" s="243"/>
+      <c r="T4" s="243"/>
+      <c r="U4" s="243"/>
+      <c r="V4" s="243"/>
+      <c r="W4" s="243"/>
+      <c r="X4" s="244"/>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="254"/>
-      <c r="B5" s="255"/>
-      <c r="C5" s="255"/>
-      <c r="D5" s="255"/>
-      <c r="E5" s="255"/>
-      <c r="F5" s="255"/>
-      <c r="G5" s="255"/>
-      <c r="H5" s="255"/>
-      <c r="I5" s="255"/>
-      <c r="J5" s="255"/>
-      <c r="K5" s="255"/>
-      <c r="L5" s="255"/>
-      <c r="M5" s="256"/>
-      <c r="N5" s="254"/>
-      <c r="O5" s="255"/>
-      <c r="P5" s="255"/>
-      <c r="Q5" s="255"/>
-      <c r="R5" s="255"/>
-      <c r="S5" s="255"/>
-      <c r="T5" s="255"/>
-      <c r="U5" s="255"/>
-      <c r="V5" s="255"/>
-      <c r="W5" s="255"/>
-      <c r="X5" s="256"/>
+      <c r="A5" s="245"/>
+      <c r="B5" s="246"/>
+      <c r="C5" s="246"/>
+      <c r="D5" s="246"/>
+      <c r="E5" s="246"/>
+      <c r="F5" s="246"/>
+      <c r="G5" s="246"/>
+      <c r="H5" s="246"/>
+      <c r="I5" s="246"/>
+      <c r="J5" s="246"/>
+      <c r="K5" s="246"/>
+      <c r="L5" s="246"/>
+      <c r="M5" s="247"/>
+      <c r="N5" s="245"/>
+      <c r="O5" s="246"/>
+      <c r="P5" s="246"/>
+      <c r="Q5" s="246"/>
+      <c r="R5" s="246"/>
+      <c r="S5" s="246"/>
+      <c r="T5" s="246"/>
+      <c r="U5" s="246"/>
+      <c r="V5" s="246"/>
+      <c r="W5" s="246"/>
+      <c r="X5" s="247"/>
     </row>
     <row r="6" ht="10" customHeight="1">
-      <c r="A6" s="257"/>
-      <c r="B6" s="257"/>
-      <c r="C6" s="257"/>
-      <c r="D6" s="257"/>
-      <c r="E6" s="257"/>
-      <c r="F6" s="257"/>
-      <c r="G6" s="257"/>
-      <c r="H6" s="257"/>
-      <c r="I6" s="257"/>
-      <c r="J6" s="257"/>
-      <c r="K6" s="257"/>
-      <c r="L6" s="257"/>
-      <c r="M6" s="257"/>
-      <c r="N6" s="257"/>
-      <c r="O6" s="257"/>
-      <c r="P6" s="257"/>
-      <c r="Q6" s="257"/>
-      <c r="R6" s="257"/>
-      <c r="S6" s="257"/>
-      <c r="T6" s="257"/>
-      <c r="U6" s="257"/>
-      <c r="V6" s="257"/>
-      <c r="W6" s="257"/>
-      <c r="X6" s="257"/>
-    </row>
-    <row r="7" s="250" customFormat="1" ht="18" customHeight="1">
-      <c r="A7" s="258" t="s">
+      <c r="A6" s="248"/>
+      <c r="B6" s="248"/>
+      <c r="C6" s="248"/>
+      <c r="D6" s="248"/>
+      <c r="E6" s="248"/>
+      <c r="F6" s="248"/>
+      <c r="G6" s="248"/>
+      <c r="H6" s="248"/>
+      <c r="I6" s="248"/>
+      <c r="J6" s="248"/>
+      <c r="K6" s="248"/>
+      <c r="L6" s="248"/>
+      <c r="M6" s="248"/>
+      <c r="N6" s="248"/>
+      <c r="O6" s="248"/>
+      <c r="P6" s="248"/>
+      <c r="Q6" s="248"/>
+      <c r="R6" s="248"/>
+      <c r="S6" s="248"/>
+      <c r="T6" s="248"/>
+      <c r="U6" s="248"/>
+      <c r="V6" s="248"/>
+      <c r="W6" s="248"/>
+      <c r="X6" s="248"/>
+    </row>
+    <row r="7" s="241" customFormat="1" ht="18" customHeight="1">
+      <c r="A7" s="249" t="s">
         <v>180</v>
       </c>
-      <c r="B7" s="258"/>
-      <c r="C7" s="258"/>
-      <c r="D7" s="258"/>
-      <c r="E7" s="258"/>
-      <c r="F7" s="258"/>
-      <c r="G7" s="258"/>
-      <c r="H7" s="258"/>
-      <c r="I7" s="258"/>
-      <c r="J7" s="258" t="s">
+      <c r="B7" s="249"/>
+      <c r="C7" s="249"/>
+      <c r="D7" s="249"/>
+      <c r="E7" s="249"/>
+      <c r="F7" s="249"/>
+      <c r="G7" s="249"/>
+      <c r="H7" s="249"/>
+      <c r="I7" s="249"/>
+      <c r="J7" s="249" t="s">
         <v>32</v>
       </c>
-      <c r="K7" s="258"/>
-      <c r="L7" s="258"/>
-      <c r="M7" s="258"/>
-      <c r="N7" s="258"/>
-      <c r="O7" s="258"/>
-      <c r="P7" s="258" t="s">
+      <c r="K7" s="249"/>
+      <c r="L7" s="249"/>
+      <c r="M7" s="249"/>
+      <c r="N7" s="249"/>
+      <c r="O7" s="249"/>
+      <c r="P7" s="249" t="s">
         <v>58</v>
       </c>
-      <c r="Q7" s="258"/>
-      <c r="R7" s="258"/>
-      <c r="S7" s="258"/>
-      <c r="T7" s="258"/>
-      <c r="U7" s="258"/>
-      <c r="V7" s="258"/>
-      <c r="W7" s="258"/>
-      <c r="X7" s="258"/>
+      <c r="Q7" s="249"/>
+      <c r="R7" s="249"/>
+      <c r="S7" s="249"/>
+      <c r="T7" s="249"/>
+      <c r="U7" s="249"/>
+      <c r="V7" s="249"/>
+      <c r="W7" s="249"/>
+      <c r="X7" s="249"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="259"/>
-      <c r="B8" s="259"/>
-      <c r="C8" s="259"/>
-      <c r="D8" s="259"/>
-      <c r="E8" s="259"/>
-      <c r="F8" s="259"/>
-      <c r="G8" s="259"/>
-      <c r="H8" s="259"/>
-      <c r="I8" s="259"/>
-      <c r="J8" s="260" t="s">
+      <c r="A8" s="250"/>
+      <c r="B8" s="250"/>
+      <c r="C8" s="250"/>
+      <c r="D8" s="250"/>
+      <c r="E8" s="250"/>
+      <c r="F8" s="250"/>
+      <c r="G8" s="250"/>
+      <c r="H8" s="250"/>
+      <c r="I8" s="250"/>
+      <c r="J8" s="251" t="s">
         <v>181</v>
       </c>
-      <c r="K8" s="261"/>
-      <c r="L8" s="261"/>
-      <c r="M8" s="261"/>
-      <c r="N8" s="261"/>
-      <c r="O8" s="262"/>
-      <c r="P8" s="260" t="s">
+      <c r="K8" s="252"/>
+      <c r="L8" s="252"/>
+      <c r="M8" s="252"/>
+      <c r="N8" s="252"/>
+      <c r="O8" s="253"/>
+      <c r="P8" s="251" t="s">
         <v>182</v>
       </c>
-      <c r="Q8" s="261"/>
-      <c r="R8" s="261"/>
-      <c r="S8" s="261"/>
-      <c r="T8" s="261"/>
-      <c r="U8" s="261"/>
-      <c r="V8" s="261"/>
-      <c r="W8" s="261"/>
-      <c r="X8" s="262"/>
+      <c r="Q8" s="252"/>
+      <c r="R8" s="252"/>
+      <c r="S8" s="252"/>
+      <c r="T8" s="252"/>
+      <c r="U8" s="252"/>
+      <c r="V8" s="252"/>
+      <c r="W8" s="252"/>
+      <c r="X8" s="253"/>
     </row>
     <row r="9" ht="10" customHeight="1">
-      <c r="A9" s="257"/>
-      <c r="B9" s="257"/>
-      <c r="C9" s="257"/>
-      <c r="D9" s="257"/>
-      <c r="E9" s="257"/>
-      <c r="F9" s="257"/>
-      <c r="G9" s="257"/>
-      <c r="H9" s="257"/>
-      <c r="I9" s="257"/>
-      <c r="J9" s="257"/>
-      <c r="K9" s="257"/>
-      <c r="L9" s="257"/>
-      <c r="M9" s="257"/>
-      <c r="N9" s="257"/>
-      <c r="O9" s="257"/>
-      <c r="P9" s="257"/>
-      <c r="Q9" s="257"/>
-      <c r="R9" s="257"/>
-      <c r="S9" s="257"/>
-      <c r="T9" s="257"/>
-      <c r="U9" s="257"/>
-      <c r="V9" s="257"/>
-      <c r="W9" s="257"/>
-      <c r="X9" s="257"/>
+      <c r="A9" s="248"/>
+      <c r="B9" s="248"/>
+      <c r="C9" s="248"/>
+      <c r="D9" s="248"/>
+      <c r="E9" s="248"/>
+      <c r="F9" s="248"/>
+      <c r="G9" s="248"/>
+      <c r="H9" s="248"/>
+      <c r="I9" s="248"/>
+      <c r="J9" s="248"/>
+      <c r="K9" s="248"/>
+      <c r="L9" s="248"/>
+      <c r="M9" s="248"/>
+      <c r="N9" s="248"/>
+      <c r="O9" s="248"/>
+      <c r="P9" s="248"/>
+      <c r="Q9" s="248"/>
+      <c r="R9" s="248"/>
+      <c r="S9" s="248"/>
+      <c r="T9" s="248"/>
+      <c r="U9" s="248"/>
+      <c r="V9" s="248"/>
+      <c r="W9" s="248"/>
+      <c r="X9" s="248"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="263" t="s">
+      <c r="A10" s="254" t="s">
         <v>183</v>
       </c>
-      <c r="B10" s="263"/>
-      <c r="C10" s="263"/>
-      <c r="D10" s="263"/>
-      <c r="E10" s="263"/>
-      <c r="F10" s="263"/>
-      <c r="G10" s="263"/>
-      <c r="H10" s="263"/>
-      <c r="I10" s="263"/>
-      <c r="J10" s="263"/>
-      <c r="K10" s="263"/>
-      <c r="L10" s="263"/>
-      <c r="M10" s="263"/>
-      <c r="N10" s="263"/>
-      <c r="O10" s="263"/>
-      <c r="P10" s="263"/>
-      <c r="Q10" s="263"/>
-      <c r="R10" s="263"/>
-      <c r="S10" s="263"/>
-      <c r="T10" s="263"/>
-      <c r="U10" s="263"/>
-      <c r="V10" s="263"/>
-      <c r="W10" s="263"/>
-      <c r="X10" s="263"/>
+      <c r="B10" s="254"/>
+      <c r="C10" s="254"/>
+      <c r="D10" s="254"/>
+      <c r="E10" s="254"/>
+      <c r="F10" s="254"/>
+      <c r="G10" s="254"/>
+      <c r="H10" s="254"/>
+      <c r="I10" s="254"/>
+      <c r="J10" s="254"/>
+      <c r="K10" s="254"/>
+      <c r="L10" s="254"/>
+      <c r="M10" s="254"/>
+      <c r="N10" s="254"/>
+      <c r="O10" s="254"/>
+      <c r="P10" s="254"/>
+      <c r="Q10" s="254"/>
+      <c r="R10" s="254"/>
+      <c r="S10" s="254"/>
+      <c r="T10" s="254"/>
+      <c r="U10" s="254"/>
+      <c r="V10" s="254"/>
+      <c r="W10" s="254"/>
+      <c r="X10" s="254"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="264" t="s">
+      <c r="A11" s="255" t="s">
         <v>140</v>
       </c>
-      <c r="B11" s="264"/>
-      <c r="C11" s="264"/>
-      <c r="D11" s="264"/>
-      <c r="E11" s="264"/>
-      <c r="F11" s="264"/>
-      <c r="G11" s="264" t="s">
+      <c r="B11" s="255"/>
+      <c r="C11" s="255"/>
+      <c r="D11" s="255"/>
+      <c r="E11" s="255"/>
+      <c r="F11" s="255"/>
+      <c r="G11" s="255" t="s">
         <v>184</v>
       </c>
-      <c r="H11" s="264"/>
-      <c r="I11" s="264"/>
-      <c r="J11" s="264"/>
-      <c r="K11" s="264"/>
-      <c r="L11" s="264"/>
-      <c r="M11" s="264" t="s">
+      <c r="H11" s="255"/>
+      <c r="I11" s="255"/>
+      <c r="J11" s="255"/>
+      <c r="K11" s="255"/>
+      <c r="L11" s="255"/>
+      <c r="M11" s="255" t="s">
         <v>185</v>
       </c>
-      <c r="N11" s="264"/>
-      <c r="O11" s="264"/>
-      <c r="P11" s="264"/>
-      <c r="Q11" s="264"/>
-      <c r="R11" s="264"/>
-      <c r="S11" s="264" t="s">
+      <c r="N11" s="255"/>
+      <c r="O11" s="255"/>
+      <c r="P11" s="255"/>
+      <c r="Q11" s="255"/>
+      <c r="R11" s="255"/>
+      <c r="S11" s="255" t="s">
         <v>186</v>
       </c>
-      <c r="T11" s="264"/>
-      <c r="U11" s="264"/>
-      <c r="V11" s="264"/>
-      <c r="W11" s="264"/>
-      <c r="X11" s="264"/>
+      <c r="T11" s="255"/>
+      <c r="U11" s="255"/>
+      <c r="V11" s="255"/>
+      <c r="W11" s="255"/>
+      <c r="X11" s="255"/>
     </row>
     <row r="12" ht="10" customHeight="1">
-      <c r="A12" s="257"/>
-      <c r="B12" s="257"/>
-      <c r="C12" s="257"/>
-      <c r="D12" s="257"/>
-      <c r="E12" s="257"/>
-      <c r="F12" s="257"/>
-      <c r="G12" s="257"/>
-      <c r="H12" s="257"/>
-      <c r="I12" s="257"/>
-      <c r="J12" s="257"/>
-      <c r="K12" s="257"/>
-      <c r="L12" s="257"/>
-      <c r="M12" s="257"/>
-      <c r="N12" s="257"/>
-      <c r="O12" s="257"/>
-      <c r="P12" s="257"/>
-      <c r="Q12" s="257"/>
-      <c r="R12" s="257"/>
-      <c r="S12" s="257"/>
-      <c r="T12" s="257"/>
-      <c r="U12" s="257"/>
-      <c r="V12" s="257"/>
-      <c r="W12" s="257"/>
-      <c r="X12" s="257"/>
-    </row>
-    <row r="13" s="250" customFormat="1" ht="18" customHeight="1">
-      <c r="A13" s="258" t="s">
+      <c r="A12" s="248"/>
+      <c r="B12" s="248"/>
+      <c r="C12" s="248"/>
+      <c r="D12" s="248"/>
+      <c r="E12" s="248"/>
+      <c r="F12" s="248"/>
+      <c r="G12" s="248"/>
+      <c r="H12" s="248"/>
+      <c r="I12" s="248"/>
+      <c r="J12" s="248"/>
+      <c r="K12" s="248"/>
+      <c r="L12" s="248"/>
+      <c r="M12" s="248"/>
+      <c r="N12" s="248"/>
+      <c r="O12" s="248"/>
+      <c r="P12" s="248"/>
+      <c r="Q12" s="248"/>
+      <c r="R12" s="248"/>
+      <c r="S12" s="248"/>
+      <c r="T12" s="248"/>
+      <c r="U12" s="248"/>
+      <c r="V12" s="248"/>
+      <c r="W12" s="248"/>
+      <c r="X12" s="248"/>
+    </row>
+    <row r="13" s="241" customFormat="1" ht="18" customHeight="1">
+      <c r="A13" s="249" t="s">
         <v>187</v>
       </c>
-      <c r="B13" s="258"/>
-      <c r="C13" s="258"/>
-      <c r="D13" s="258"/>
-      <c r="E13" s="258"/>
-      <c r="F13" s="258"/>
-      <c r="G13" s="258"/>
-      <c r="H13" s="258"/>
-      <c r="I13" s="258"/>
-      <c r="J13" s="258" t="s">
+      <c r="B13" s="249"/>
+      <c r="C13" s="249"/>
+      <c r="D13" s="249"/>
+      <c r="E13" s="249"/>
+      <c r="F13" s="249"/>
+      <c r="G13" s="249"/>
+      <c r="H13" s="249"/>
+      <c r="I13" s="249"/>
+      <c r="J13" s="249" t="s">
         <v>32</v>
       </c>
-      <c r="K13" s="258"/>
-      <c r="L13" s="258"/>
-      <c r="M13" s="258"/>
-      <c r="N13" s="258"/>
-      <c r="O13" s="258"/>
-      <c r="P13" s="258" t="s">
+      <c r="K13" s="249"/>
+      <c r="L13" s="249"/>
+      <c r="M13" s="249"/>
+      <c r="N13" s="249"/>
+      <c r="O13" s="249"/>
+      <c r="P13" s="249" t="s">
         <v>58</v>
       </c>
-      <c r="Q13" s="258"/>
-      <c r="R13" s="258"/>
-      <c r="S13" s="258"/>
-      <c r="T13" s="258"/>
-      <c r="U13" s="258"/>
-      <c r="V13" s="258"/>
-      <c r="W13" s="258"/>
-      <c r="X13" s="258"/>
+      <c r="Q13" s="249"/>
+      <c r="R13" s="249"/>
+      <c r="S13" s="249"/>
+      <c r="T13" s="249"/>
+      <c r="U13" s="249"/>
+      <c r="V13" s="249"/>
+      <c r="W13" s="249"/>
+      <c r="X13" s="249"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="259"/>
-      <c r="B14" s="259"/>
-      <c r="C14" s="259"/>
-      <c r="D14" s="259"/>
-      <c r="E14" s="259"/>
-      <c r="F14" s="259"/>
-      <c r="G14" s="259"/>
-      <c r="H14" s="259"/>
-      <c r="I14" s="259"/>
-      <c r="J14" s="260" t="s">
+      <c r="A14" s="250"/>
+      <c r="B14" s="250"/>
+      <c r="C14" s="250"/>
+      <c r="D14" s="250"/>
+      <c r="E14" s="250"/>
+      <c r="F14" s="250"/>
+      <c r="G14" s="250"/>
+      <c r="H14" s="250"/>
+      <c r="I14" s="250"/>
+      <c r="J14" s="251" t="s">
         <v>188</v>
       </c>
-      <c r="K14" s="261"/>
-      <c r="L14" s="261"/>
-      <c r="M14" s="261"/>
-      <c r="N14" s="261"/>
-      <c r="O14" s="262"/>
-      <c r="P14" s="260" t="s">
+      <c r="K14" s="252"/>
+      <c r="L14" s="252"/>
+      <c r="M14" s="252"/>
+      <c r="N14" s="252"/>
+      <c r="O14" s="253"/>
+      <c r="P14" s="251" t="s">
         <v>189</v>
       </c>
-      <c r="Q14" s="261"/>
-      <c r="R14" s="261"/>
-      <c r="S14" s="261"/>
-      <c r="T14" s="261"/>
-      <c r="U14" s="261"/>
-      <c r="V14" s="261"/>
-      <c r="W14" s="261"/>
-      <c r="X14" s="262"/>
+      <c r="Q14" s="252"/>
+      <c r="R14" s="252"/>
+      <c r="S14" s="252"/>
+      <c r="T14" s="252"/>
+      <c r="U14" s="252"/>
+      <c r="V14" s="252"/>
+      <c r="W14" s="252"/>
+      <c r="X14" s="253"/>
     </row>
     <row r="15" ht="10" customHeight="1">
-      <c r="A15" s="257"/>
-      <c r="B15" s="257"/>
-      <c r="C15" s="257"/>
-      <c r="D15" s="257"/>
-      <c r="E15" s="257"/>
-      <c r="F15" s="257"/>
-      <c r="G15" s="257"/>
-      <c r="H15" s="257"/>
-      <c r="I15" s="257"/>
-      <c r="J15" s="257"/>
-      <c r="K15" s="257"/>
-      <c r="L15" s="257"/>
-      <c r="M15" s="257"/>
-      <c r="N15" s="257"/>
-      <c r="O15" s="257"/>
-      <c r="P15" s="257"/>
-      <c r="Q15" s="257"/>
-      <c r="R15" s="257"/>
-      <c r="S15" s="257"/>
-      <c r="T15" s="257"/>
-      <c r="U15" s="257"/>
-      <c r="V15" s="257"/>
-      <c r="W15" s="257"/>
-      <c r="X15" s="257"/>
-    </row>
-    <row r="16" s="265" customFormat="1" ht="24.75" customHeight="1">
-      <c r="A16" s="266" t="s">
+      <c r="A15" s="248"/>
+      <c r="B15" s="248"/>
+      <c r="C15" s="248"/>
+      <c r="D15" s="248"/>
+      <c r="E15" s="248"/>
+      <c r="F15" s="248"/>
+      <c r="G15" s="248"/>
+      <c r="H15" s="248"/>
+      <c r="I15" s="248"/>
+      <c r="J15" s="248"/>
+      <c r="K15" s="248"/>
+      <c r="L15" s="248"/>
+      <c r="M15" s="248"/>
+      <c r="N15" s="248"/>
+      <c r="O15" s="248"/>
+      <c r="P15" s="248"/>
+      <c r="Q15" s="248"/>
+      <c r="R15" s="248"/>
+      <c r="S15" s="248"/>
+      <c r="T15" s="248"/>
+      <c r="U15" s="248"/>
+      <c r="V15" s="248"/>
+      <c r="W15" s="248"/>
+      <c r="X15" s="248"/>
+    </row>
+    <row r="16" s="256" customFormat="1" ht="24.75" customHeight="1">
+      <c r="A16" s="257" t="s">
         <v>190</v>
       </c>
-      <c r="B16" s="266"/>
-      <c r="C16" s="266"/>
-      <c r="D16" s="266"/>
-      <c r="E16" s="266"/>
-      <c r="F16" s="266"/>
-      <c r="G16" s="266"/>
-      <c r="H16" s="266"/>
-      <c r="I16" s="266"/>
-      <c r="J16" s="267" t="s">
+      <c r="B16" s="257"/>
+      <c r="C16" s="257"/>
+      <c r="D16" s="257"/>
+      <c r="E16" s="257"/>
+      <c r="F16" s="257"/>
+      <c r="G16" s="257"/>
+      <c r="H16" s="257"/>
+      <c r="I16" s="257"/>
+      <c r="J16" s="258" t="s">
         <v>191</v>
       </c>
-      <c r="K16" s="267"/>
-      <c r="L16" s="267"/>
-      <c r="M16" s="267"/>
-      <c r="N16" s="266" t="s">
+      <c r="K16" s="258"/>
+      <c r="L16" s="258"/>
+      <c r="M16" s="258"/>
+      <c r="N16" s="257" t="s">
         <v>192</v>
       </c>
-      <c r="O16" s="266"/>
-      <c r="P16" s="266"/>
-      <c r="Q16" s="266"/>
-      <c r="R16" s="266"/>
-      <c r="S16" s="266"/>
-      <c r="T16" s="268" t="s">
+      <c r="O16" s="257"/>
+      <c r="P16" s="257"/>
+      <c r="Q16" s="257"/>
+      <c r="R16" s="257"/>
+      <c r="S16" s="257"/>
+      <c r="T16" s="259" t="s">
         <v>193</v>
       </c>
-      <c r="U16" s="268"/>
-      <c r="V16" s="268"/>
-      <c r="W16" s="268"/>
-      <c r="X16" s="268"/>
+      <c r="U16" s="259"/>
+      <c r="V16" s="259"/>
+      <c r="W16" s="259"/>
+      <c r="X16" s="259"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="269" t="s">
+      <c r="A17" s="260" t="s">
         <v>194</v>
       </c>
-      <c r="B17" s="248"/>
-      <c r="C17" s="248"/>
-      <c r="D17" s="248"/>
-      <c r="E17" s="248"/>
-      <c r="F17" s="248"/>
-      <c r="G17" s="248"/>
-      <c r="H17" s="248"/>
-      <c r="I17" s="270"/>
-      <c r="J17" s="271" t="s">
+      <c r="B17" s="239"/>
+      <c r="C17" s="239"/>
+      <c r="D17" s="239"/>
+      <c r="E17" s="239"/>
+      <c r="F17" s="239"/>
+      <c r="G17" s="239"/>
+      <c r="H17" s="239"/>
+      <c r="I17" s="261"/>
+      <c r="J17" s="262" t="s">
         <v>195</v>
       </c>
-      <c r="K17" s="272"/>
-      <c r="L17" s="272"/>
-      <c r="M17" s="273"/>
-      <c r="N17" s="269" t="s">
+      <c r="K17" s="263"/>
+      <c r="L17" s="263"/>
+      <c r="M17" s="264"/>
+      <c r="N17" s="260" t="s">
         <v>196</v>
       </c>
-      <c r="O17" s="248"/>
-      <c r="P17" s="248"/>
-      <c r="Q17" s="248"/>
-      <c r="R17" s="248"/>
-      <c r="S17" s="270"/>
-      <c r="T17" s="269" t="s">
+      <c r="O17" s="239"/>
+      <c r="P17" s="239"/>
+      <c r="Q17" s="239"/>
+      <c r="R17" s="239"/>
+      <c r="S17" s="261"/>
+      <c r="T17" s="260" t="s">
         <v>197</v>
       </c>
-      <c r="U17" s="248"/>
-      <c r="V17" s="248"/>
-      <c r="W17" s="248"/>
-      <c r="X17" s="270"/>
+      <c r="U17" s="239"/>
+      <c r="V17" s="239"/>
+      <c r="W17" s="239"/>
+      <c r="X17" s="261"/>
     </row>
     <row r="18" ht="48.75" customHeight="1">
-      <c r="A18" s="274"/>
-      <c r="B18" s="275"/>
-      <c r="C18" s="275"/>
-      <c r="D18" s="275"/>
-      <c r="E18" s="275"/>
-      <c r="F18" s="275"/>
-      <c r="G18" s="275"/>
-      <c r="H18" s="275"/>
-      <c r="I18" s="276"/>
-      <c r="J18" s="277"/>
-      <c r="K18" s="278"/>
-      <c r="L18" s="278"/>
-      <c r="M18" s="279"/>
-      <c r="N18" s="274"/>
-      <c r="O18" s="275"/>
-      <c r="P18" s="275"/>
-      <c r="Q18" s="275"/>
-      <c r="R18" s="275"/>
-      <c r="S18" s="276"/>
-      <c r="T18" s="274"/>
-      <c r="U18" s="275"/>
-      <c r="V18" s="275"/>
-      <c r="W18" s="275"/>
-      <c r="X18" s="276"/>
+      <c r="A18" s="265"/>
+      <c r="B18" s="266"/>
+      <c r="C18" s="266"/>
+      <c r="D18" s="266"/>
+      <c r="E18" s="266"/>
+      <c r="F18" s="266"/>
+      <c r="G18" s="266"/>
+      <c r="H18" s="266"/>
+      <c r="I18" s="267"/>
+      <c r="J18" s="268"/>
+      <c r="K18" s="269"/>
+      <c r="L18" s="269"/>
+      <c r="M18" s="270"/>
+      <c r="N18" s="265"/>
+      <c r="O18" s="266"/>
+      <c r="P18" s="266"/>
+      <c r="Q18" s="266"/>
+      <c r="R18" s="266"/>
+      <c r="S18" s="267"/>
+      <c r="T18" s="265"/>
+      <c r="U18" s="266"/>
+      <c r="V18" s="266"/>
+      <c r="W18" s="266"/>
+      <c r="X18" s="267"/>
     </row>
     <row r="19" ht="39" customHeight="1"/>
     <row r="20" ht="39" customHeight="1"/>
     <row r="21">
-      <c r="A21" s="280" t="s">
+      <c r="A21" s="271" t="s">
         <v>198</v>
       </c>
-      <c r="B21" s="280"/>
-      <c r="C21" s="280"/>
-      <c r="D21" s="280"/>
-      <c r="E21" s="280"/>
-      <c r="F21" s="280"/>
-      <c r="G21" s="280"/>
-      <c r="H21" s="280"/>
-      <c r="I21" s="281"/>
-      <c r="J21" s="280" t="s">
+      <c r="B21" s="271"/>
+      <c r="C21" s="271"/>
+      <c r="D21" s="271"/>
+      <c r="E21" s="271"/>
+      <c r="F21" s="271"/>
+      <c r="G21" s="271"/>
+      <c r="H21" s="271"/>
+      <c r="I21" s="272"/>
+      <c r="J21" s="271" t="s">
         <v>199</v>
       </c>
-      <c r="K21" s="280"/>
-      <c r="L21" s="280"/>
-      <c r="M21" s="280"/>
-      <c r="N21" s="280"/>
-      <c r="O21" s="280"/>
-      <c r="P21" s="280"/>
-      <c r="Q21" s="282"/>
-      <c r="R21" s="280" t="s">
+      <c r="K21" s="271"/>
+      <c r="L21" s="271"/>
+      <c r="M21" s="271"/>
+      <c r="N21" s="271"/>
+      <c r="O21" s="271"/>
+      <c r="P21" s="271"/>
+      <c r="Q21" s="273"/>
+      <c r="R21" s="271" t="s">
         <v>200</v>
       </c>
-      <c r="S21" s="280"/>
-      <c r="T21" s="280"/>
-      <c r="U21" s="280"/>
-      <c r="V21" s="280"/>
-      <c r="W21" s="280"/>
-      <c r="X21" s="280"/>
+      <c r="S21" s="271"/>
+      <c r="T21" s="271"/>
+      <c r="U21" s="271"/>
+      <c r="V21" s="271"/>
+      <c r="W21" s="271"/>
+      <c r="X21" s="271"/>
     </row>
     <row r="23" ht="38.25" customHeight="1">
-      <c r="P23" s="283" t="s">
+      <c r="P23" s="274" t="s">
         <v>201</v>
       </c>
-      <c r="Q23" s="283"/>
-      <c r="R23" s="283"/>
-      <c r="S23" s="283"/>
-      <c r="T23" s="283"/>
-      <c r="U23" s="284" t="s">
+      <c r="Q23" s="274"/>
+      <c r="R23" s="274"/>
+      <c r="S23" s="274"/>
+      <c r="T23" s="274"/>
+      <c r="U23" s="275" t="s">
         <v>202</v>
       </c>
-      <c r="V23" s="284"/>
-      <c r="W23" s="284"/>
-      <c r="X23" s="284"/>
+      <c r="V23" s="275"/>
+      <c r="W23" s="275"/>
+      <c r="X23" s="275"/>
     </row>
     <row r="24" ht="38.25" customHeight="1">
-      <c r="P24" s="283" t="s">
+      <c r="P24" s="274" t="s">
         <v>203</v>
       </c>
-      <c r="Q24" s="283"/>
-      <c r="R24" s="283"/>
-      <c r="S24" s="283"/>
-      <c r="T24" s="283"/>
-      <c r="U24" s="285" t="s">
+      <c r="Q24" s="274"/>
+      <c r="R24" s="274"/>
+      <c r="S24" s="274"/>
+      <c r="T24" s="274"/>
+      <c r="U24" s="276" t="s">
         <v>204</v>
       </c>
-      <c r="V24" s="285"/>
-      <c r="W24" s="285"/>
-      <c r="X24" s="285"/>
+      <c r="V24" s="276"/>
+      <c r="W24" s="276"/>
+      <c r="X24" s="276"/>
     </row>
   </sheetData>
   <mergeCells count="40">
